--- a/workspaces/nasdaq_hourly_24hrs/vix/vix_ret_1.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/vix/vix_ret_1.xlsx
@@ -618,1887 +618,1887 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.06867</t>
+          <t>X ≈ -0.06862</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>12</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>29.46266067622942</v>
+        <v>29.49594941078978</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>29.13998392183648</v>
+        <v>29.17366213525682</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>19.43279386708068</v>
+        <v>19.46807640351108</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.44315321058104</v>
+        <v>10.47921191328977</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.08385688086844</v>
+        <v>10.14923651298965</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>18.56435059213189</v>
+        <v>18.62960012797622</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.507060684650575</v>
+        <v>9.573184853649799</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.9368314048663322</v>
+        <v>1.003267320005008</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.320214324963835</v>
+        <v>-7.253828246942582</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2076213208449005</v>
+        <v>0.274981618154392</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.784870996530572</v>
+        <v>8.851989174516198</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.509330570162447</v>
+        <v>8.576808266820123</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.390712875875515</v>
+        <v>7.459529243473902</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.48309867341768</v>
+        <v>15.55223653908128</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>23.14366826700655</v>
+        <v>23.21362986328342</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>7.112583168854194</v>
+        <v>7.181846029168469</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>15.29476285919301</v>
+        <v>15.36884055723847</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>6.87604998455646</v>
+        <v>6.947766743236457</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>7.093915180946915</v>
+        <v>7.165481248754425</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>15.60619611101023</v>
+        <v>15.68014462086121</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>15.0681365460479</v>
+        <v>15.13802565619903</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>23.32512429867352</v>
+        <v>23.395144175955</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>15.2760107812563</v>
+        <v>15.34574031066471</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.06333</t>
+          <t>X ≈ -0.06327</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>13</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.809537208179997</v>
+        <v>7.84265689971312</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.480484399269749</v>
+        <v>7.51400106122437</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>13.69716423254249</v>
+        <v>13.73240611174408</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.343623068467615</v>
+        <v>5.379646514288474</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.982846417652325</v>
+        <v>5.048191368292954</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.170558859701309</v>
+        <v>5.235725750303565</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.40306416881964</v>
+        <v>4.469157395944372</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.530233427932153</v>
+        <v>-3.463823803392998</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.489953142704401</v>
+        <v>-3.423550448839784</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-4.262095922292517</v>
+        <v>-4.194758506862868</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.989788564475553</v>
+        <v>-3.92272682591242</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.269130555908177</v>
+        <v>-4.201704651779451</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.277714508074766</v>
+        <v>2.346511288516567</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.057575737956185</v>
+        <v>2.126669408627102</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-6.273172420929818</v>
+        <v>-6.203295895188006</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-5.681116345778726</v>
+        <v>-5.61188660013827</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-5.814896201010669</v>
+        <v>-5.747165535599251</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-5.921470088703707</v>
+        <v>-5.853603217814396</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-5.707433763296045</v>
+        <v>-5.639714684665094</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-5.522381187762015</v>
+        <v>-5.454767211220336</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-6.066748970268108</v>
+        <v>-5.996882971524556</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-6.144440098441819</v>
+        <v>-6.074441561592991</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-5.871511770802854</v>
+        <v>-5.80178995310699</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>1.743139901034638</v>
+        <v>1.812994248741916</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.05797</t>
+          <t>X ≈ -0.05793</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>28.48605147849636</v>
+        <v>28.51933525501926</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.782234905635853</v>
+        <v>4.815730145599801</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.198699556318729</v>
+        <v>9.233908712703446</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.492671758950856</v>
+        <v>8.528715727090756</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>13.98340990377734</v>
+        <v>14.04881099332073</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>14.173833409669</v>
+        <v>14.23905338299249</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.555048052747644</v>
+        <v>7.621157135387044</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.280632850689869</v>
+        <v>7.34709826853171</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>13.18172555699415</v>
+        <v>13.24821015670676</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.555283131196909</v>
+        <v>6.622668874099503</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>6.830829218846915</v>
+        <v>6.897935619274257</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.554744207877988</v>
+        <v>6.622211045448026</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.4290998826231203</v>
+        <v>-0.3603147095944905</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>5.216353755090275</v>
+        <v>5.285456167298634</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-1.307667309221245</v>
+        <v>-1.237778197691846</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-6.584076401883749</v>
+        <v>-6.51485056084357</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-6.717853417804527</v>
+        <v>-6.650413864466231</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.9530079356663848</v>
+        <v>-0.8836495766925339</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.7374912671632003</v>
+        <v>-0.6682808300278893</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-6.426207383587467</v>
+        <v>-6.358882454995907</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-12.84788335744643</v>
+        <v>-12.77802547160675</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-7.048838555150937</v>
+        <v>-6.978841143798306</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-12.6567759936633</v>
+        <v>-12.5870568819721</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.9717922256621918</v>
+        <v>-0.9019378779535856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.05261</t>
+          <t>X ≈ -0.05257</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>18</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>23.9392329951515</v>
+        <v>23.97248269036424</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>29.13629432302302</v>
+        <v>29.16997555698391</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>27.71301688855819</v>
+        <v>27.74836102238806</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15.96533333401036</v>
+        <v>16.00142844033402</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>21.1330314033067</v>
+        <v>21.19847781915207</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>21.32565070205118</v>
+        <v>21.3909135463679</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9.505953297995056</v>
+        <v>9.572071324270233</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.701823169265538</v>
+        <v>3.768266444982729</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>14.80820094579457</v>
+        <v>14.87469227993513</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.55931559858584</v>
+        <v>-2.491975600815351</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.286516425866807</v>
+        <v>-2.219452247192656</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.971717551336461</v>
+        <v>3.039168017674776</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>7.390290558231321</v>
+        <v>7.459102195325421</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.909169377652496</v>
+        <v>-3.84009885482682</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-4.56768507205453</v>
+        <v>-4.497807469971114</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-3.97509948775928</v>
+        <v>-3.905868873142602</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.434890754377712</v>
+        <v>1.504798335635513</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.330428039139754</v>
+        <v>1.400479621222274</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.546631057359896</v>
+        <v>1.616535193288271</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-9.363732482101263</v>
+        <v>-9.297323454480157</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-15.45975928196067</v>
+        <v>-15.38990526767721</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-4.436003303405379</v>
+        <v>-4.366004531825105</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-9.716452757989117</v>
+        <v>-9.646732888504559</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-4.23976608187261</v>
+        <v>-4.169911734166597</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.04727</t>
+          <t>X ≈ -0.04723</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>25</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>18.19796400870773</v>
+        <v>18.23116902201024</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>25.82180099277235</v>
+        <v>25.85545943538875</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>28.37338408689797</v>
+        <v>28.40873574517233</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>15.74316468866001</v>
+        <v>15.77925844059585</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>11.40731894424428</v>
+        <v>11.47269905665654</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11.5970472405599</v>
+        <v>11.66224747371471</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6.851671688575635</v>
+        <v>6.917771052861809</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.577282280954783</v>
+        <v>6.643738087607218</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.637317937371087</v>
+        <v>2.703743923357521</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.851777857843381</v>
+        <v>5.91915474303444</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.127122487975917</v>
+        <v>6.194220774882517</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.864204620332472</v>
+        <v>1.931647810003867</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.731468382851453</v>
+        <v>4.800267982399475</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>8.50121437372399</v>
+        <v>8.570323724994878</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>11.83672074778918</v>
+        <v>11.90664473581885</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>16.42573102008401</v>
+        <v>16.49501274193611</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>8.309006406104459</v>
+        <v>8.381034789819594</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>12.19931646158304</v>
+        <v>12.2727156729654</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>8.424957670635173</v>
+        <v>8.496981170587908</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>8.614397335411013</v>
+        <v>8.686288201218488</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>4.078034019293291</v>
+        <v>4.14790865591317</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>11.99841138741672</v>
+        <v>12.06842180337852</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>12.27685176733379</v>
+        <v>12.34657949069658</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>8.204678362574917</v>
+        <v>8.274532710281285</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.04191</t>
+          <t>X ≈ -0.04187</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>37</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>24.53073948686331</v>
+        <v>24.5639992209957</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>13.46647906855332</v>
+        <v>13.50004244505911</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.980519281055159</v>
+        <v>4.015689299490582</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5872954773060783</v>
+        <v>0.6232798522465828</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.912889661540206</v>
+        <v>2.978207452847911</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.788598101452109</v>
+        <v>5.853756929766973</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10.40098834943186</v>
+        <v>10.46710459800222</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>10.1277726660424</v>
+        <v>10.1942441694689</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>15.55405955869166</v>
+        <v>15.6205494626553</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>12.09645409518203</v>
+        <v>12.16385775936182</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>15.06644013098432</v>
+        <v>15.13357554375644</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>9.405956886122013</v>
+        <v>9.473427553688026</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>13.6764576400418</v>
+        <v>13.74528792165774</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>10.76472319111898</v>
+        <v>10.83383765823615</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>10.11070798373211</v>
+        <v>10.1806246675339</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>10.70772162469932</v>
+        <v>10.77698674992835</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>2.483455540353567</v>
+        <v>2.553717254114119</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>7.774673385145988</v>
+        <v>7.846767098512018</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>5.294420484348713</v>
+        <v>5.365519901917303</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>5.482937788071865</v>
+        <v>5.553906393120201</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>2.241829859694192</v>
+        <v>2.31170128934027</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.5345091512970228</v>
+        <v>-0.4645088338169217</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>5.14385332668467</v>
+        <v>5.213578071028735</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2.366840524734023</v>
+        <v>2.436694872442537</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.03656</t>
+          <t>X ≈ -0.03653</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>25.76844127964267</v>
+        <v>26.16948314770446</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>25.44667118788858</v>
+        <v>25.84821854974366</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>20.34305644436859</v>
+        <v>20.81328232611629</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>19.64224384586199</v>
+        <v>20.1134363857557</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>19.28600168263375</v>
+        <v>19.78663632097246</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>13.95215958506137</v>
+        <v>14.5531951247284</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>13.18823138678865</v>
+        <v>13.79035964547038</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>9.229753580932467</v>
+        <v>9.899413376717888</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.742328709168731</v>
+        <v>4.512713439710197</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4.817540639326616</v>
+        <v>5.555553051204548</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>10.62715170944078</v>
+        <v>11.26448709299289</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>17.73453627816454</v>
+        <v>18.23821968930945</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>14.77288292382573</v>
+        <v>15.31160118723295</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>18.25014293047037</v>
+        <v>18.72216335551873</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>13.90422496447658</v>
+        <v>14.4443358882225</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>14.502486655036</v>
+        <v>15.04209370876059</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>12.52122678185734</v>
+        <v>13.09877910781995</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>10.57176823630095</v>
+        <v>11.18268459105775</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>10.79102914056154</v>
+        <v>11.40195185272754</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>12.83083940669863</v>
+        <v>13.40874764691995</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>10.44222855659637</v>
+        <v>11.05031726730139</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>10.36953842372473</v>
+        <v>10.97792568217623</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>14.35011617189827</v>
+        <v>14.89107478170423</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>14.27875243664759</v>
+        <v>14.81998725573492</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.03121</t>
+          <t>X ≈ -0.03118</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>76</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>17.24411072475132</v>
+        <v>16.60445566982289</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>9.07856784477211</v>
+        <v>8.426270620547847</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>8.958670279365904</v>
+        <v>6.981407852841734</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.639204681773407</v>
+        <v>3.646806001284389</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.970655483806247</v>
+        <v>2.727674264019043</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.541363935791004</v>
+        <v>0.2977775469878523</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-3.153268468291571</v>
+        <v>-4.396359545443502</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.12068675985423</v>
+        <v>-3.363825672200363</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.5396684148517394</v>
+        <v>-0.7038800387158375</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.471553604667996</v>
+        <v>-6.714603913086265</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.578796308531729</v>
+        <v>-3.822525738486007</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.791147110223903</v>
+        <v>-8.034940262532565</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-6.602622128271598</v>
+        <v>-7.845480740002728</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-9.449389707184153</v>
+        <v>-10.69237072091583</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-12.73415920384226</v>
+        <v>-13.97675362830385</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-10.83151586225213</v>
+        <v>-12.07516838879936</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-13.59054944165646</v>
+        <v>-14.83866458769219</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-8.446847793215539</v>
+        <v>-9.693514844889684</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-13.48826247705018</v>
+        <v>-14.73720629169748</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-9.363423059521899</v>
+        <v>-10.61162488922358</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-7.279823990954753</v>
+        <v>-8.524496852999697</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-8.673033050473279</v>
+        <v>-9.917990641153047</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-11.03174906133541</v>
+        <v>-12.27740071104735</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-7.163742690058186</v>
+        <v>-8.409677816035412</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.02585</t>
+          <t>X ≈ -0.02583</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>82</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>21.76125766775981</v>
+        <v>23.0134305108464</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>15.38530238274054</v>
+        <v>15.42442760879482</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>15.17204699918018</v>
+        <v>16.42487575699395</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>16.89484651985064</v>
+        <v>18.14933039123797</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>12.90180447031538</v>
+        <v>14.17952851590879</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>10.66771979378188</v>
+        <v>11.94564488803029</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8.690896070555404</v>
+        <v>9.970134973342546</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.99090375001839</v>
+        <v>7.270883557904426</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>7.247726527703477</v>
+        <v>8.52810014692966</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.052078998069135</v>
+        <v>5.333769419868197</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.540820333814189</v>
+        <v>5.607950960802263</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.619669956665902</v>
+        <v>1.687145721461</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.361319804333156</v>
+        <v>6.64563874104838</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>5.142580050438902</v>
+        <v>5.211704861303915</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>4.487553589465428</v>
+        <v>4.557479190365235</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>5.082719515042065</v>
+        <v>5.151992285709071</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3.73283089706041</v>
+        <v>3.803560440538654</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>7.280070151455064</v>
+        <v>7.352216105299476</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>9.933592211270401</v>
+        <v>10.00634247997952</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>11.34143961250918</v>
+        <v>11.41450865240002</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>8.366078229707007</v>
+        <v>8.435965822262482</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>9.511597107001784</v>
+        <v>9.581610976097487</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>11.00862147874847</v>
+        <v>11.07835136300771</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>6.058336899158185</v>
+        <v>6.128191246865747</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.0205</t>
+          <t>X ≈ -0.02048</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>18.96141804657081</v>
+        <v>19.24702130334729</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>10.67498437714625</v>
+        <v>10.38068881817597</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.865294052062239</v>
+        <v>2.733312808345964</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.937043309819465</v>
+        <v>2.796475888875008</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.771014454587593</v>
+        <v>1.682861673029024</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.551128813754609</v>
+        <v>3.424788214117811</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.564090181250066</v>
+        <v>3.428821709238619</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.916638712132269</v>
+        <v>6.260306774443947</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.368492823648324</v>
+        <v>4.749212050514565</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>6.185992160713546</v>
+        <v>5.530285201989152</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>6.464588498737569</v>
+        <v>6.586431076897064</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>7.780365015067119</v>
+        <v>8.311574896115047</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>9.04647572071233</v>
+        <v>8.751766003567191</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7.231521364354727</v>
+        <v>7.75594257050993</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>12.15720592439741</v>
+        <v>12.55654170622817</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>10.36533849307644</v>
+        <v>10.81573246936456</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>10.22870281595127</v>
+        <v>10.68660444777224</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>10.92743148467973</v>
+        <v>11.36495006545223</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>8.751537272860851</v>
+        <v>9.244236462270173</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>7.345772211102854</v>
+        <v>7.09270085259358</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>8.073097672874489</v>
+        <v>7.331314968735761</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>8.799433354203806</v>
+        <v>8.038762698272215</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>12.27621062227157</v>
+        <v>11.43999880384182</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>13.0046783625731</v>
+        <v>12.14953271028038</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.01515</t>
+          <t>X ≈ -0.01512</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>11.38894702108593</v>
+        <v>10.97293995238073</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.969594574256234</v>
+        <v>5.917719357973269</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.386068161250144</v>
+        <v>5.346777014901093</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.951486730964213</v>
+        <v>5.929504381348877</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.890249675791985</v>
+        <v>3.873554858725001</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.779757771558714</v>
+        <v>5.784287436251098</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.010209779854598</v>
+        <v>5.016002283778391</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>5.582470928092675</v>
+        <v>5.601894498156682</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.200926679110623</v>
+        <v>5.214806603587569</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.706001656557696</v>
+        <v>5.737329091684657</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>5.131486916780155</v>
+        <v>5.151491796558282</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6.799601294570436</v>
+        <v>6.597645593681534</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>8.236470852679396</v>
+        <v>8.065015583294844</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>9.723815847745009</v>
+        <v>9.573289969573437</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>7.791750668158237</v>
+        <v>7.622728546297004</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>7.109624083014616</v>
+        <v>7.175822112776288</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>8.255704495126636</v>
+        <v>8.341753535470232</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>6.447282721702138</v>
+        <v>6.511341400229384</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>6.666153680008698</v>
+        <v>6.730001231209222</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>4.721303289368208</v>
+        <v>5.189704220378005</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>5.459487640442582</v>
+        <v>5.945174829703653</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>4.104664095023402</v>
+        <v>4.57398836437148</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>4.808339227366027</v>
+        <v>5.28307218509299</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.879892037786767</v>
+        <v>4.343796779544441</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.009796</t>
+          <t>X ≈ -0.009773</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>10.04800212384075</v>
+        <v>10.00970077327381</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.509950318590846</v>
+        <v>3.504518741268924</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.822059410732578</v>
+        <v>1.561728539033865</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.9602677362663954</v>
+        <v>-1.209099093649563</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2353320197891122</v>
+        <v>0.006756613746581763</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.46112411123412</v>
+        <v>1.226306918752073</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.6928678151918461</v>
+        <v>0.4593933464935134</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.194584289133559</v>
+        <v>0.9583366992035423</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1976648351437333</v>
+        <v>-0.0333209088123354</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.7261475963838748</v>
+        <v>0.4892387864401044</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4805792574061059</v>
+        <v>0.2459614585432419</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.02231123341965</v>
+        <v>1.778586753029167</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.6398256897324828</v>
+        <v>0.3986808933800674</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.4196071595617639</v>
+        <v>0.1786347222565468</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.6072862551276259</v>
+        <v>-0.9967509168807709</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.288948846470696</v>
+        <v>0.8929023571121633</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.416252359827297</v>
+        <v>1.019073448500365</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>2.614717742245617</v>
+        <v>2.211810970235319</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.747544207451412</v>
+        <v>0.504145039537633</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.456855104443896</v>
+        <v>1.210440409718494</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.3929905236204334</v>
+        <v>0.149937573071746</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.204005004122962</v>
+        <v>-0.4443474410605646</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.5929982170045918</v>
+        <v>0.3495367684441533</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.57077855648695</v>
+        <v>-1.803389367641707</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.004445</t>
+          <t>X ≈ -0.004422</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.619621838311097</v>
+        <v>4.880229800639881</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.335022998247545</v>
+        <v>1.329288666820311</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.948099721732255</v>
+        <v>4.280173898998925</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.696734349208583</v>
+        <v>3.93219437618842</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5.643032288464362</v>
+        <v>5.608027900137891</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.514223810170257</v>
+        <v>2.686723914277998</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.851135966642815</v>
+        <v>2.828022329218172</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.94159229894565</v>
+        <v>3.016567377355216</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.532068318067452</v>
+        <v>2.60987878860373</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.500256950754434</v>
+        <v>2.571644898529073</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.769881470316044</v>
+        <v>1.747796753831445</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.490787566841142</v>
+        <v>1.469047350383448</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.5535966849483884</v>
+        <v>-0.4689079312554654</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.777130587426221</v>
+        <v>-1.791040595710726</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.5243485117489897</v>
+        <v>0.5952503712583166</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.193517902647244</v>
+        <v>0.2706096687581763</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.3089962630452376</v>
+        <v>-0.22929449057402</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.04434104867815591</v>
+        <v>0.1387977608287017</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.677192520443683</v>
+        <v>-1.481983555393874</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.305320440771929</v>
+        <v>-1.111587807645932</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.7358298047007779</v>
+        <v>-0.5496303903330357</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.6259557452125719</v>
+        <v>-0.4409300972840597</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.7219134248617536</v>
+        <v>-0.5343745733507319</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.7971769249964993</v>
+        <v>-0.6094451902721048</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.0009075</t>
+          <t>X ≈ 0.0009285</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.8821913817183002</v>
+        <v>-1.139883039008282</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.930464232184512</v>
+        <v>2.10059091838793</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.5001411994053839</v>
+        <v>-0.5300479721528291</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.03727364747615525</v>
+        <v>-0.04853947164546923</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.580566214725657</v>
+        <v>-2.579152658301211</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.206214411137076</v>
+        <v>-1.194435726749802</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2971855426919774</v>
+        <v>-0.1735124068858767</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.9730832063085373</v>
+        <v>-1.052623892105053</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.516490621590911</v>
+        <v>-2.610256555479637</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.511426859951847</v>
+        <v>-1.589557380684212</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.03755785102333</v>
+        <v>-1.004027057947177</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.307473196099231</v>
+        <v>-2.082435601826383</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.723228213387522</v>
+        <v>-3.610768110219048</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.549967537162026</v>
+        <v>-3.435428732300814</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-3.020846367758381</v>
+        <v>-2.89462638254529</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-3.103734924860447</v>
+        <v>-3.09701401977199</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.445632212926441</v>
+        <v>-2.318590033902126</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.428388167478488</v>
+        <v>-3.42216681174601</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-3.608835470523587</v>
+        <v>-3.608761126147662</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-5.209531958905501</v>
+        <v>-5.106931847680599</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-5.157549932519252</v>
+        <v>-5.049534971160561</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-6.030911152738781</v>
+        <v>-5.809344120054959</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-4.250572307253748</v>
+        <v>-4.137098211682833</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-4.526931975399052</v>
+        <v>-4.414846047234654</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.00626</t>
+          <t>X ≈ 0.006279</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>371</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.412656847338368</v>
+        <v>-6.379892385644624</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-3.497167540341216</v>
+        <v>-3.470723621585464</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6338216292716154</v>
+        <v>-0.6074834899328536</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.608127356764804</v>
+        <v>-1.572024085973034</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.969161357292741</v>
+        <v>-1.903591323273702</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.777661266974278</v>
+        <v>-1.847789293937353</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.474681829823098</v>
+        <v>-1.536076483397252</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.020282227068606</v>
+        <v>-1.810933930464564</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.7060782068838662</v>
+        <v>0.9180074312487179</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.06260209894568192</v>
+        <v>0.152478020804061</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.360233412159261</v>
+        <v>2.573721622159148</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.812848700007272</v>
+        <v>1.7588763508274</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.6901278841094793</v>
+        <v>0.6435556494143739</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.08098184303006</v>
+        <v>2.041056607056447</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.153443651996128</v>
+        <v>1.113994748486249</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>3.628120078954936</v>
+        <v>3.588940934955424</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>2.688648129463438</v>
+        <v>2.649577578690042</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>3.120436016714066</v>
+        <v>3.081264533167072</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>4.956308985234593</v>
+        <v>4.914221538592336</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>3.80377009077997</v>
+        <v>3.756848676092382</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>5.143934078997979</v>
+        <v>5.098603097455559</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>4.959628814696153</v>
+        <v>4.754586840017488</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>3.078596460162295</v>
+        <v>2.878969675574119</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>4.086079979823751</v>
+        <v>3.886392548555307</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.01161</t>
+          <t>X ≈ 0.01163</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-14.01618672459384</v>
+        <v>-13.85352635094142</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.935293938812883</v>
+        <v>-5.856281833301047</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-8.27763329032436</v>
+        <v>-8.201696853309308</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-7.572913656680896</v>
+        <v>-7.76144618697856</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-5.604611292918776</v>
+        <v>-5.312910901866744</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-8.20071279387011</v>
+        <v>-7.894391968689568</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-9.893215210736862</v>
+        <v>-9.58309309317584</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-7.378856552901951</v>
+        <v>-7.081359227870301</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-5.47823198971988</v>
+        <v>-5.189405608258056</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.922160294790039</v>
+        <v>-3.642803401523949</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-6.446077404381313</v>
+        <v>-6.154030975260433</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.466020627242116</v>
+        <v>-3.188777362117911</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.319640646215795</v>
+        <v>-1.056229427570663</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.469671826232855</v>
+        <v>-2.199790056869709</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-4.988615557530999</v>
+        <v>-4.712318249028762</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-5.332884894073608</v>
+        <v>-5.051348763259007</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-4.066242147292058</v>
+        <v>-3.790653307559609</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-4.176020321118813</v>
+        <v>-3.898695434235378</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-3.021598605642495</v>
+        <v>-2.750809471739863</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.365831080665323</v>
+        <v>-2.09778851416106</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.441926153941949</v>
+        <v>-2.175582389118269</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.050418786481991</v>
+        <v>-1.785964630217642</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-5.043952620525744</v>
+        <v>-4.763808899684804</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-6.057003880417533</v>
+        <v>-5.771978917626598</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.01697</t>
+          <t>X ≈ 0.01699</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-17.45417035008786</v>
+        <v>-17.84264053341447</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-5.045181565145228</v>
+        <v>-5.354952885275694</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.111684135988845</v>
+        <v>-3.397516448952302</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.479562512149172</v>
+        <v>-2.08061432779769</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.842565755856043</v>
+        <v>-3.089314420275315</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.658425932620538</v>
+        <v>-4.250859558104636</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.061467375831413</v>
+        <v>-1.639450136453313</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.358249275773566</v>
+        <v>-5.975371431141184</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-6.65979406301431</v>
+        <v>-7.286081569872479</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.746709505355845</v>
+        <v>-4.995262917256305</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.136387932612294</v>
+        <v>-3.376072288751978</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-5.431335400712669</v>
+        <v>-5.684404646733576</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.17835821255165</v>
+        <v>-3.407251134208977</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.395134213515604</v>
+        <v>-3.623373828249257</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-4.721130443352827</v>
+        <v>-4.956025803746584</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-6.826396027424664</v>
+        <v>-7.081083595000102</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-4.939139184863585</v>
+        <v>-5.178016982980175</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-5.052368059085687</v>
+        <v>-5.288363115766025</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.462947457480233</v>
+        <v>-1.677906629399075</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.7535913576585926</v>
+        <v>0.5453112152369428</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.486302035254447</v>
+        <v>-2.706280522325642</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.484935244126426</v>
+        <v>1.285723870965988</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.962424048661909</v>
+        <v>-3.186571846346361</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.687213529318797</v>
+        <v>-1.902338038018904</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.02232</t>
+          <t>X ≈ 0.02234</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>102</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-27.44795090930559</v>
+        <v>-28.08700976038719</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-17.72296065284635</v>
+        <v>-17.69022746932425</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-15.25408027999434</v>
+        <v>-15.21951071734468</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-13.97526892279527</v>
+        <v>-13.94004041772435</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-14.31684763935219</v>
+        <v>-14.25224540517224</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-9.258729669878399</v>
+        <v>-9.194284018547663</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-3.217394167713287</v>
+        <v>-3.144701918208703</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-8.331365566997945</v>
+        <v>-8.274966124364809</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.407301457882085</v>
+        <v>-4.341175752517422</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-6.15397985551207</v>
+        <v>-6.087167226037067</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.94837883739676</v>
+        <v>-3.881762906700772</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.17061317458829</v>
+        <v>-6.103702521556762</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.432961714454486</v>
+        <v>-1.364718735046644</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.619939400988855</v>
+        <v>-2.548172722777451</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.323831523592823</v>
+        <v>-1.249361838160716</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-4.63736237149859</v>
+        <v>-4.567891723719391</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.846334067695345</v>
+        <v>-1.771335371866016</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-4.883876158440714</v>
+        <v>-4.811607348983358</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.73222581265042</v>
+        <v>-1.663259365442016</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.536762278185776</v>
+        <v>-1.473438884794845</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.8568439295695427</v>
+        <v>0.9164715498560909</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.175981698653416</v>
+        <v>-1.112362366178239</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.07722875411888452</v>
+        <v>0.1467089991258703</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.9889920880632914</v>
+        <v>1.058846435770512</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.02767</t>
+          <t>X ≈ 0.02769</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-29.00412538783219</v>
+        <v>-29.28609568736912</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-26.74397732430795</v>
+        <v>-27.05837697236386</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-16.49210170095555</v>
+        <v>-16.4404649415235</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-13.31768424612648</v>
+        <v>-13.23204842570296</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-7.176095610702227</v>
+        <v>-7.117471533574623</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-9.600005181432557</v>
+        <v>-9.483859375202847</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.553849016066835</v>
+        <v>-2.536984813344944</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-10.66751957996926</v>
+        <v>-10.50332902085771</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-8.014929331209323</v>
+        <v>-7.897600110522085</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-14.0341029040311</v>
+        <v>-13.81507272216032</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-13.73908378556942</v>
+        <v>-13.56856761501565</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-15.33273162259906</v>
+        <v>-15.12484546017112</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-8.628435485239308</v>
+        <v>-8.504765694233193</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-8.860122221946774</v>
+        <v>-8.725962648911022</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-8.218272761660266</v>
+        <v>-8.087263876582156</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-11.53416308140456</v>
+        <v>-11.37570635700303</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-12.97764574627168</v>
+        <v>-12.79876875652575</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-9.149297287376044</v>
+        <v>-9.040791757130179</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-8.951281208036875</v>
+        <v>-8.820282291787208</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-10.10379567339399</v>
+        <v>-9.919503021418556</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-10.65688923632946</v>
+        <v>-10.45743110496605</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-9.417054818287859</v>
+        <v>-9.242592442357243</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-10.45806912548994</v>
+        <v>-10.27839946092637</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-11.11111111111111</v>
+        <v>-11.67351923777157</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.03302</t>
+          <t>X ≈ 0.03304</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>62</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-21.39356799913366</v>
+        <v>-21.36029370681483</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-16.87039353866572</v>
+        <v>-16.83672053005238</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-19.91010183871707</v>
+        <v>-19.85855717319188</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-12.5776639392372</v>
+        <v>-12.53158291720273</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.35133459604981</v>
+        <v>-3.304047672654121</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.737616284074342</v>
+        <v>-4.677660560494289</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-7.115516900838969</v>
+        <v>-7.049124849689022</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.9458552220219687</v>
+        <v>-0.8791199701065366</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.114408126420763</v>
+        <v>-4.047701757613261</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.677507176597182</v>
+        <v>-1.614058262414986</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.032011444279881</v>
+        <v>-2.97662128864318</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.299325119689499</v>
+        <v>-3.237821701158197</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-7.615574130607598</v>
+        <v>-7.535954755569563</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-9.423385655405234</v>
+        <v>-9.354107590572511</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-8.474657770161869</v>
+        <v>-8.404591763872403</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-6.288430915551181</v>
+        <v>-6.219038036940105</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-8.01840350591543</v>
+        <v>-7.948834070132904</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-8.144591332528137</v>
+        <v>-8.074879184471513</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-4.721114781117095</v>
+        <v>-4.650737691825064</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-4.536290322580648</v>
+        <v>-4.454467699404908</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-5.079490731578652</v>
+        <v>-4.989945730531723</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-5.155445787221211</v>
+        <v>-5.068147737553829</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.654864169126128</v>
+        <v>-1.586955600223256</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.495000943218258</v>
+        <v>1.564855290925536</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.03838</t>
+          <t>X ≈ 0.03839</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>51</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-14.55467507835087</v>
+        <v>-14.52140078603204</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-18.61684715346316</v>
+        <v>-18.58317414484982</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-22.0008781985043</v>
+        <v>-21.93092849218282</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-11.03035792687622</v>
+        <v>-10.98629587475139</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-11.39024712505755</v>
+        <v>-11.31497295990363</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-3.43326894059301</v>
+        <v>-3.382364769672108</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-6.149933612222206</v>
+        <v>-6.083541561072259</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.5432867705886935</v>
+        <v>-0.4765515186732614</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.275819044732444</v>
+        <v>5.342525413539946</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.553922641469882</v>
+        <v>4.585751498031513</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.730684633721381</v>
+        <v>6.733662050813756</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.469679800830036</v>
+        <v>6.48181558157917</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.424696786623173</v>
+        <v>3.457899669889322</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.113062035245797</v>
+        <v>7.18234010007852</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>8.40356510486199</v>
+        <v>8.473631111151455</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>12.86493344473987</v>
+        <v>12.93432632335094</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.972898471260947</v>
+        <v>5.042467907043473</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.9509573672752367</v>
+        <v>1.020669515331861</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.148818327006389</v>
+        <v>3.182377390792901</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.409313725490222</v>
+        <v>1.441495776807741</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.826897630217786</v>
+        <v>2.852001731611843</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.7901582608496298</v>
+        <v>0.8303392756660131</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>4.986502054782655</v>
+        <v>5.021796754610904</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>10.79291365669075</v>
+        <v>10.86276800439803</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.04372</t>
+          <t>X ≈ 0.04373</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>35</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-16.62742173205318</v>
+        <v>-16.59414743973435</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.797456590023373</v>
+        <v>-2.763783581410031</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-12.58271751788157</v>
+        <v>-12.54896425185486</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-13.21656199832767</v>
+        <v>-13.15641634588754</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-13.57383690007704</v>
+        <v>-13.48165662589373</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-13.3626876372462</v>
+        <v>-13.26303986217335</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-11.33483194555309</v>
+        <v>-11.26843989440314</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-5.892019694456962</v>
+        <v>-5.82528444254153</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2890343983136248</v>
+        <v>-0.222328029506123</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.632180650061507</v>
+        <v>4.646174358325112</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-9.28146402201196</v>
+        <v>-9.219288133918376</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-6.708954552556456</v>
+        <v>-6.649346413971081</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-4.971071178811179</v>
+        <v>-4.907827590882519</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-10.81485059094108</v>
+        <v>-10.74557252610836</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-5.819045570976726</v>
+        <v>-5.748979564687261</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-10.91103543826312</v>
+        <v>-10.84164255965204</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-8.182754540179616</v>
+        <v>-8.11318510439709</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-11.15011254850732</v>
+        <v>-11.0804004004507</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-10.96068325140277</v>
+        <v>-10.86450901952637</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-10.80357142857147</v>
+        <v>-10.65073516130326</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-11.34677183756938</v>
+        <v>-11.18251010996727</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-8.565584036069097</v>
+        <v>-8.43368074670105</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-8.290808869586968</v>
+        <v>-8.196573812006555</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-8.366750208855478</v>
+        <v>-8.296895861148201</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.04908</t>
+          <t>X ≈ 0.04909</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>25</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-25.56895874143414</v>
+        <v>-25.53568444911532</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.325959915181073</v>
+        <v>-2.292286906567732</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.225400474573149</v>
+        <v>4.148668855299441</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.623114743895627</v>
+        <v>3.582590065349322</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.573109546034772</v>
+        <v>-4.529362557451421</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.410665236463615</v>
+        <v>7.387940707297659</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10.53655021948534</v>
+        <v>10.60294227063529</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>10.38065391473404</v>
+        <v>10.44738916664947</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.479707892334709</v>
+        <v>2.54641426114221</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.174003843703431</v>
+        <v>-2.136403288221786</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-5.899343553108196</v>
+        <v>-5.861451585399671</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.148335108600079</v>
+        <v>-6.095597955841427</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.6663669299869071</v>
+        <v>0.6902497899697693</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.449330639626581</v>
+        <v>-3.380052574793858</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-4.115787465659693</v>
+        <v>-4.045721459370228</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-11.45239508611656</v>
+        <v>-11.38300220750548</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-7.594315390741137</v>
+        <v>-7.524745954958611</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-3.797432461261472</v>
+        <v>-3.727720313204848</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-3.569662843239392</v>
+        <v>-3.511828932280523</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.625</v>
+        <v>0.6596646802160677</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>4.081799591002046</v>
+        <v>4.079189553791359</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>4.00584453535938</v>
+        <v>3.995818005386433</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>4.280619701841566</v>
+        <v>4.300841153979789</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>4.204678362573098</v>
+        <v>4.274532710280376</v>
       </c>
     </row>
     <row r="29">
@@ -2511,76 +2511,76 @@
         <v>14</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-20.30932621231111</v>
+        <v>-20.27605191999228</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>7.054113951199902</v>
+        <v>7.087786959813243</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-22.53162182880376</v>
+        <v>-22.42639008864942</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-16.57385485441667</v>
+        <v>-16.46638506940425</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-10.01064925389664</v>
+        <v>-9.908983482519169</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-9.823484640889859</v>
+        <v>-9.722017296421789</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-31.60198987068821</v>
+        <v>-31.53559781953826</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.129940817178081</v>
+        <v>-4.063205565262649</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-24.94725522249195</v>
+        <v>-24.88054885368445</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-25.95569225657601</v>
+        <v>-25.7268688434248</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-32.51915089808116</v>
+        <v>-32.2711781162512</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-32.96659028544497</v>
+        <v>-32.69673614710713</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-20.07875471891344</v>
+        <v>-19.88954312917083</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-34.81747476663325</v>
+        <v>-34.74819670180053</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-42.5246557691521</v>
+        <v>-42.45458976286264</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-34.71300047216037</v>
+        <v>-34.64360759354931</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-35.05752602117028</v>
+        <v>-34.98795658538775</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-41.95824097491376</v>
+        <v>-41.88852882685714</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-34.89537712895367</v>
+        <v>-34.58230131147899</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-37.94642857142857</v>
+        <v>-41.65413711985368</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-31.34677183756938</v>
+        <v>-35.14843352433826</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-38.56558403606914</v>
+        <v>-42.27252924922881</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-38.2908088695869</v>
+        <v>-42.17344456030573</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-38.36675020885548</v>
+        <v>-38.2968958611482</v>
       </c>
     </row>
     <row r="30">
@@ -2593,76 +2593,76 @@
         <v>12</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-39.42629531879427</v>
+        <v>-39.39302102647544</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-39.95277518126476</v>
+        <v>-39.91910217265141</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-42.02040072801778</v>
+        <v>-41.73972991733449</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-26.69198777796633</v>
+        <v>-26.483118719386</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-18.90002893101482</v>
+        <v>-18.71456136584613</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.180606253491902</v>
+        <v>-2.127595179748724</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-11.21960141780399</v>
+        <v>-11.15320936665405</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-11.87930746431162</v>
+        <v>-11.81257221239619</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-11.61999059872375</v>
+        <v>-11.55328422991624</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.264341875364195</v>
+        <v>-4.168971273977228</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-12.0169433925624</v>
+        <v>-11.88878966336699</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-12.54113533525299</v>
+        <v>-12.38533986738</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-13.78817557334811</v>
+        <v>-13.61740233451898</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-14.62227748242159</v>
+        <v>-14.55299941758886</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-15.28120872145889</v>
+        <v>-15.21114271516942</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-22.77438396595503</v>
+        <v>-22.70499108734396</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-23.21485020912351</v>
+        <v>-23.14528077334099</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-22.95218656639548</v>
+        <v>-22.88247441833886</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-17.89537712895389</v>
+        <v>-22.60530852761055</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-9.374999999999879</v>
+        <v>-14.39150193332864</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-34.91820040899783</v>
+        <v>-39.93404810129466</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-26.66082213130735</v>
+        <v>-31.67656072937067</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-34.71938029815843</v>
+        <v>-34.64963503649635</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-34.79532163742702</v>
+        <v>-34.72546728971975</v>
       </c>
     </row>
     <row r="31">
@@ -2675,322 +2675,322 @@
         <v>20</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-23.59031188194129</v>
+        <v>-23.55703758962246</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-23.86453501563321</v>
+        <v>-23.83086200701987</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-20.35904701227284</v>
+        <v>-20.24221438938419</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-11.11471377459748</v>
+        <v>-11.03897793263647</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-6.52030614026669</v>
+        <v>-6.454768405183778</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-6.348650212123417</v>
+        <v>-6.298278409562563</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-12.06568507866877</v>
+        <v>-11.99929302751882</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.386113173318883</v>
+        <v>-2.319377921403451</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.576308598899779</v>
+        <v>2.643014967707281</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-8.124635993010997</v>
+        <v>-8.025992519743674</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-12.85027672589572</v>
+        <v>-12.73487332423176</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-13.12937062937052</v>
+        <v>-12.98260535795284</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-14.2538618478577</v>
+        <v>-14.09025873994531</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-9.475218658892196</v>
+        <v>-9.405940594059473</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-10.1341498979295</v>
+        <v>-10.06408389164003</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-9.539089848308116</v>
+        <v>-9.46969696969704</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-4.673183542457039</v>
+        <v>-4.603614106674513</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-9.778166958552134</v>
+        <v>-9.70845481049551</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-9.562043795620433</v>
+        <v>-9.492563429571298</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-4.375000000000142</v>
+        <v>-4.305717619603413</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-4.918200408998025</v>
+        <v>-4.848263787569373</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-4.994155464640556</v>
+        <v>-4.924109748978395</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-4.719380298158576</v>
+        <v>-4.649635036496491</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-4.795321637426895</v>
+        <v>-4.725467289719617</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.07049</t>
+          <t>X ≈ 0.07048</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>11</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-8.436947232406375</v>
+        <v>-8.403672940087546</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.2064164442544723</v>
+        <v>0.2400894528678137</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.993775187323557</v>
+        <v>-1.056085624532059</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>16.33044187620323</v>
+        <v>16.12724846507933</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>15.96517209117918</v>
+        <v>15.79145799253206</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.854656302807058</v>
+        <v>-1.857073656868458</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-11.60000156863039</v>
+        <v>-11.53360951748044</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-11.82686059793723</v>
+        <v>-11.7601253460218</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-29.82335490963468</v>
+        <v>-29.75664854082718</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-30.85190872028379</v>
+        <v>-30.49854684713656</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-21.48664036225943</v>
+        <v>-21.26234719444756</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-12.67482517482524</v>
+        <v>-12.50658272467184</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-13.79931639331232</v>
+        <v>-13.60906654504348</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.161144977471643</v>
+        <v>4.230423042304366</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-5.588695352474815</v>
+        <v>-5.51862934618535</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-4.993635302853306</v>
+        <v>-4.92424242424223</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-5.127728997002428</v>
+        <v>-5.058159561219902</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-14.32362150400679</v>
+        <v>-14.25390935595017</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-14.10749834107498</v>
+        <v>-14.03801797502584</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-13.92045454545441</v>
+        <v>-13.85117216505768</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-5.372745863543415</v>
+        <v>-5.302809242114762</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-5.448700919185953</v>
+        <v>-5.378655203523792</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-14.26483484361285</v>
+        <v>-14.19508958195076</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-5.249867091972291</v>
+        <v>-5.180012744265014</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.07584</t>
+          <t>X ≈ 0.07583</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>12</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-39.59479385124595</v>
+        <v>-39.56151955892712</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-31.92278960930154</v>
+        <v>-31.8891166006882</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-17.54577157802972</v>
+        <v>-17.38720044264448</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-18.52838209552382</v>
+        <v>-18.32342738039559</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-18.89365188054787</v>
+        <v>-18.65921785294287</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-27.03982060087436</v>
+        <v>-26.70270434174264</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-3.08150393722957</v>
+        <v>-3.015111886079623</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-3.808087256583207</v>
+        <v>-3.741352004667775</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-11.83108732059296</v>
+        <v>-11.76438095178545</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-8.124635993011061</v>
+        <v>-12.80611383212295</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-16.18361005922905</v>
+        <v>-20.50696458422635</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-8.12937062937057</v>
+        <v>-12.72119785864203</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.9205285145244346</v>
+        <v>-5.690238061698814</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-9.475218658892125</v>
+        <v>-9.405940594059402</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-1.800816564596033</v>
+        <v>-1.730750558306568</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-1.205756514974773</v>
+        <v>-1.136363636363697</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-9.673183542456968</v>
+        <v>-9.603614106674442</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-18.11150029188564</v>
+        <v>-18.04178814382902</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-17.89537712895376</v>
+        <v>-17.82589676290463</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-17.70833333333333</v>
+        <v>-17.6390509529366</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-18.25153374233128</v>
+        <v>-18.18159712090263</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-18.32748879797384</v>
+        <v>-18.25744308231168</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-18.05271363149176</v>
+        <v>-17.98296836982968</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-18.12865497076018</v>
+        <v>-18.0588006230529</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.0812</t>
+          <t>X ≈ 0.08119</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>12</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-36.71223198009326</v>
+        <v>-36.67895768777444</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-28.79906253141678</v>
+        <v>-28.76538952280344</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-47.11566405114799</v>
+        <v>-46.53906790266285</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-22.82945736434114</v>
+        <v>-22.56066389741425</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.805272850634871</v>
+        <v>1.741226789458793</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.992437463641593</v>
+        <v>1.946085263979832</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-32.11376200174576</v>
+        <v>-32.04736995059582</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-15.72564998059766</v>
+        <v>-15.65891472868223</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-24.0174672489083</v>
+        <v>-23.9507608801008</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-24.79130265967773</v>
+        <v>-24.72367655613729</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-24.5169433925624</v>
+        <v>-24.44961691397537</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-24.79603729603735</v>
+        <v>-24.72836631742341</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-25.92052851452444</v>
+        <v>-25.85152838427948</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-17.80855199222545</v>
+        <v>-17.73927392739273</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-18.46748323126275</v>
+        <v>-18.39741722497329</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-17.87242318164132</v>
+        <v>-17.80303030303025</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-9.673183542456968</v>
+        <v>-9.603614106674442</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-18.11150029188558</v>
+        <v>-18.04178814382895</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-17.89537712895376</v>
+        <v>-17.82589676290463</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-9.375</v>
+        <v>-9.305717619603271</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-18.25153374233128</v>
+        <v>-18.18159712090263</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-18.32748879797389</v>
+        <v>-18.25744308231173</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-18.05271363149176</v>
+        <v>-17.98296836982968</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-18.12865497076023</v>
+        <v>-18.05880062305295</v>
       </c>
     </row>
   </sheetData>
@@ -3180,1887 +3180,1887 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.07135</t>
+          <t>X &gt; -0.0713</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.3684587908678978</v>
+        <v>-0.368712082339286</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.12436216357424</v>
+        <v>-0.1249130113078536</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3021566843922656</v>
+        <v>-0.3025318497016585</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2280725967842017</v>
+        <v>-0.2285531154066689</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.07213884423007499</v>
+        <v>-0.07341621058517234</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.04635905258954409</v>
+        <v>-0.04766325958797069</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.06000494798864509</v>
+        <v>-0.06131240090724077</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.005187809063720294</v>
+        <v>0.003795459250575561</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.02539196411385092</v>
+        <v>-0.0267478198455251</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.06875014283270531</v>
+        <v>-0.07007402248725469</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.014724760872042</v>
+        <v>0.01330754894910058</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.02054013802973031</v>
+        <v>0.01910843005138219</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.01421312982744638</v>
+        <v>0.0127608678255271</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.01882896015549562</v>
+        <v>0.01736499452561446</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.02697514353823749</v>
+        <v>-0.02840146523497111</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.03938764461537403</v>
+        <v>-0.04078560741261583</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.005196445631177937</v>
+        <v>0.02149746726188795</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.05222117362523448</v>
+        <v>-0.03583576287658019</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.05668026761089351</v>
+        <v>-0.04034550757070576</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.09035022354694178</v>
+        <v>-0.07403209250380627</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1388324900951474</v>
+        <v>-0.1401041687485787</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1373108478794549</v>
+        <v>-0.1385869607746528</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.113175047561775</v>
+        <v>-0.1144741306560562</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1414869612108447</v>
+        <v>-0.1427549201220089</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.066</t>
+          <t>X &gt; -0.06595</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3339</v>
+        <v>3343</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.4756685643345548</v>
+        <v>-0.4759139782165107</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2295350156332177</v>
+        <v>-0.2300828891896316</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3730819334541664</v>
+        <v>-0.3735002311071511</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2664238126237848</v>
+        <v>-0.2669896036939434</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1086383796302499</v>
+        <v>-0.1101113445016821</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1132439030647419</v>
+        <v>-0.114706980991123</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.09438793319130667</v>
+        <v>-0.09589629772288077</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.001839584101269054</v>
+        <v>0.0002077648655784969</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.0008248278388904851</v>
+        <v>-0.0008055628532517289</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.06974339157907394</v>
+        <v>-0.07131263082937522</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.01679418337111116</v>
+        <v>-0.01841969589290215</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.009967644295997502</v>
+        <v>-0.01161020531841217</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.0122972016947358</v>
+        <v>-0.01396997887138696</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.03674793009881228</v>
+        <v>-0.03839882794961369</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1102478961367765</v>
+        <v>-0.1118308328515454</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.06509104376530672</v>
+        <v>-0.06671189507009956</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.04975258011387496</v>
+        <v>-0.03359320491271944</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.07712062073460402</v>
+        <v>-0.06090403391258548</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.08237872385009126</v>
+        <v>-0.06621147259490101</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1467618905174959</v>
+        <v>-0.1305831306612575</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1934846699195631</v>
+        <v>-0.1949463936661289</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.2216322679928524</v>
+        <v>-0.2230634111607586</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.1684820945656185</v>
+        <v>-0.1699699647260076</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1666903106823696</v>
+        <v>-0.1681834129622217</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.06065</t>
+          <t>X &gt; -0.0606</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3326</v>
+        <v>3330</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.5080521106492455</v>
+        <v>-0.508388879541755</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2596703891731309</v>
+        <v>-0.2603150487558139</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.428076882389206</v>
+        <v>-0.4285683339471049</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2883512357910121</v>
+        <v>-0.2890335284788605</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1285389515979816</v>
+        <v>-0.1302488625996787</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1338961688241938</v>
+        <v>-0.1355945562184004</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1119666696092665</v>
+        <v>-0.1137178286591194</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.01564504085305884</v>
+        <v>0.01373101122814546</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.01446887883620462</v>
+        <v>0.01255650426921306</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.05335716701524973</v>
+        <v>-0.05521509437639338</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.001265341833416755</v>
+        <v>-0.003177656045984634</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.006679715250285767</v>
+        <v>0.00474752074885032</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.02124793898487098</v>
+        <v>-0.02318507090623001</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.04493380132090863</v>
+        <v>-0.04685104629060532</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.0861594960098131</v>
+        <v>-0.08805033861419531</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.04314025334854676</v>
+        <v>-0.04506406589115386</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.02721894599732622</v>
+        <v>-0.01128796758571582</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.05427740272991599</v>
+        <v>-0.03828989295440266</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.06039263981136855</v>
+        <v>-0.04445305164688307</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.125750750750754</v>
+        <v>-0.109798027644068</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.170528435432324</v>
+        <v>-0.1722961908096323</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1984823877174904</v>
+        <v>-0.2002201931560705</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1461912389459314</v>
+        <v>-0.1479838806872849</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1741550709807171</v>
+        <v>-0.1759177401700711</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.05529</t>
+          <t>X &gt; -0.05525</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3309</v>
+        <v>3313</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6570094273659279</v>
+        <v>-0.6573388675549054</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2855731966713932</v>
+        <v>-0.2863617642112999</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.477534482708954</v>
+        <v>-0.4781494114578422</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3334637745974902</v>
+        <v>-0.3342800534848038</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2010391421514299</v>
+        <v>-0.2030058857058208</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2074021835822393</v>
+        <v>-0.2093552006393438</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1513559867081113</v>
+        <v>-0.1534077997997159</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.02167886146402509</v>
+        <v>-0.02389870304114794</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.05317795208815568</v>
+        <v>-0.05535961770224418</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.08730908151196104</v>
+        <v>-0.08948132663237374</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.03636525344766994</v>
+        <v>-0.03858934505305456</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.02696099081640568</v>
+        <v>-0.02920867602745147</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.01915259808374259</v>
+        <v>-0.02145515727577418</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.07196368601689329</v>
+        <v>-0.07421271928517115</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.07988399500509757</v>
+        <v>-0.08215073897510194</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.009536169176556086</v>
+        <v>-0.01186564439576898</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.007154213875963933</v>
+        <v>0.02277938534123081</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.04966017122193023</v>
+        <v>-0.03395209801822574</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.05691404305555636</v>
+        <v>-0.04125200358395631</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.09338213099909609</v>
+        <v>-0.07773209487468336</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1053984766308034</v>
+        <v>-0.1076124003557979</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.1632886570295682</v>
+        <v>-0.1654370491292312</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.08191806250888334</v>
+        <v>-0.08415525375645672</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.1700572070854065</v>
+        <v>-0.1721923123577227</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.04994</t>
+          <t>X &gt; -0.0499</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3291</v>
+        <v>3295</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.791537644809047</v>
+        <v>-0.7918872099046865</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4464949880279718</v>
+        <v>-0.447276505267908</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6317216369729479</v>
+        <v>-0.6323458265744577</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4226094287922422</v>
+        <v>-0.4235191287165847</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3177250339224003</v>
+        <v>-0.3199183915290149</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3251764017352059</v>
+        <v>-0.3273536338551679</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2041762745004689</v>
+        <v>-0.2065363655761203</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.04204441495936351</v>
+        <v>-0.04461462797723215</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.134461701757516</v>
+        <v>-0.1369198405117942</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.07378853538394026</v>
+        <v>-0.07635692695551199</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.02405813673435375</v>
+        <v>-0.02667567821283967</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.04336214966135543</v>
+        <v>-0.04597067314023917</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.05967826712466717</v>
+        <v>-0.06232011398194715</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.05097623464970269</v>
+        <v>-0.05364035192864947</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.05533813678968613</v>
+        <v>-0.05802879021700846</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.01215332937540126</v>
+        <v>0.009406603894795751</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.000654737120399318</v>
+        <v>0.01468337893597749</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.0572085114791534</v>
+        <v>-0.04178814382895268</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.06568457231945501</v>
+        <v>-0.05030820071406339</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.04267830045523624</v>
+        <v>-0.02736710413935128</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.02141838106837923</v>
+        <v>-0.02412794766632942</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1399192059099192</v>
+        <v>-0.1424900947472807</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.02922233947070652</v>
+        <v>-0.03191658989440782</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.1477980883536674</v>
+        <v>-0.1503534809184046</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.04459</t>
+          <t>X &gt; -0.04455</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3266</v>
+        <v>3270</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.9368951283785307</v>
+        <v>-0.9373234196288109</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6475689009244761</v>
+        <v>-0.6483677586368373</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.8537447977496697</v>
+        <v>-0.8543724440954463</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5463523415100298</v>
+        <v>-0.5473935749651488</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4074758298361019</v>
+        <v>-0.4100760172796711</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4164365337184819</v>
+        <v>-0.419017250885517</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2581861333727602</v>
+        <v>-0.2610035476742709</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.0927128679286966</v>
+        <v>-0.09574882305051347</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.155678631022127</v>
+        <v>-0.1586374533854098</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1191465145115203</v>
+        <v>-0.1221941721389115</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.0711431078359297</v>
+        <v>-0.07423604864934674</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.0579638548817627</v>
+        <v>-0.06109008050372466</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.09635269034860983</v>
+        <v>-0.09949586395428156</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1164400329379234</v>
+        <v>-0.1195727989999327</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1463673689129266</v>
+        <v>-0.1495018294068942</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.11348642637099</v>
+        <v>-0.116630140279824</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.06426206369131648</v>
+        <v>-0.04927955233988968</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1510275942490651</v>
+        <v>-0.1359357265261565</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.1306772410499661</v>
+        <v>-0.1156544497301297</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.1089449541284395</v>
+        <v>-0.09398526396624618</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.05279814530874916</v>
+        <v>-0.05602425197503891</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.2328335552158407</v>
+        <v>-0.2358456902986958</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.1234207021988425</v>
+        <v>-0.1265534100824084</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.2117331499804891</v>
+        <v>-0.2147639258052507</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.03924</t>
+          <t>X &gt; -0.0392</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3229</v>
+        <v>3233</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.228719990801551</v>
+        <v>-1.229172766273749</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.8092969203951199</v>
+        <v>-0.8102889394400421</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.9091389665064966</v>
+        <v>-0.9101077625342668</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5593424218123531</v>
+        <v>-0.5607913221989378</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4455227555657189</v>
+        <v>-0.4488531556634427</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4875378906405317</v>
+        <v>-0.4908058820900223</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3803259462757538</v>
+        <v>-0.3837811540429712</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2098258951064338</v>
+        <v>-0.2135124298315958</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.3356911156983102</v>
+        <v>-0.3392220237205521</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2591208788839765</v>
+        <v>-0.2628016331551635</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2445994657908201</v>
+        <v>-0.2482815261992997</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1664076664076646</v>
+        <v>-0.1702076655532494</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2541705851223597</v>
+        <v>-0.2579421986488839</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.241123538447404</v>
+        <v>-0.2449288728996279</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.2638996662334137</v>
+        <v>-0.2677247432289747</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.2374829261819613</v>
+        <v>-0.2413019079685697</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.09345548312446539</v>
+        <v>-0.07906949413970921</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.2418454747810017</v>
+        <v>-0.2272935998717784</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1928415692753447</v>
+        <v>-0.1783836334637954</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.1730204144757224</v>
+        <v>-0.1586224403696477</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.07909149810686245</v>
+        <v>-0.0831216367658385</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.2293767583576809</v>
+        <v>-0.2332287597975622</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.1837765829881519</v>
+        <v>-0.1876684316726056</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.2412801385108239</v>
+        <v>-0.2451084898433464</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.03388</t>
+          <t>X &gt; -0.03385</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3175</v>
+        <v>3178</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.6878843084721</v>
+        <v>-1.703347113431967</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.2558551181423</v>
+        <v>-1.271653921159711</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.270593628612716</v>
+        <v>-1.28606322347693</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.902928455971221</v>
+        <v>-0.9185894732176649</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.781114037349262</v>
+        <v>-0.7990582913509741</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.7331264461327862</v>
+        <v>-0.7511646156881966</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.6110982599719677</v>
+        <v>-0.6290856675650716</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.3703730735965536</v>
+        <v>-0.3885315989191369</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.4050495631133799</v>
+        <v>-0.4231919577950265</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.3454640984062962</v>
+        <v>-0.3634968841431387</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.4295048401097219</v>
+        <v>-0.4475270498165358</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.4708646657799136</v>
+        <v>-0.4887927834001502</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.5097488180304524</v>
+        <v>-0.5273962220042847</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.5556206689423817</v>
+        <v>-0.5731825143606244</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.5048693449919455</v>
+        <v>-0.5223387566744861</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.4881784718152673</v>
+        <v>-0.5058037200894319</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.3080044098359735</v>
+        <v>-0.3071316946141422</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.4257620544340455</v>
+        <v>-0.4247601827859171</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.3796538585135139</v>
+        <v>-0.3787985018528843</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.3941884240327127</v>
+        <v>-0.393425887443577</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2580367840766158</v>
+        <v>-0.2758022974718486</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.4096417724781389</v>
+        <v>-0.4272544030664562</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.4309671999216533</v>
+        <v>-0.4486284306454564</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.4882350232536723</v>
+        <v>-0.5058322991595219</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.02853</t>
+          <t>X &gt; -0.0285</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3099</v>
+        <v>3102</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.152173312191039</v>
+        <v>-2.151894183556848</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.509296920395123</v>
+        <v>-1.509256198777301</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.521456505994571</v>
+        <v>-1.488618930053399</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.063367990811038</v>
+        <v>-1.03044313410166</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.8976466232182005</v>
+        <v>-0.8854643758797067</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.7889061392680574</v>
+        <v>-0.7768640368240369</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.5487539760635229</v>
+        <v>-0.536786243090944</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.3274483107196247</v>
+        <v>-0.315635934970274</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.4282178646059123</v>
+        <v>-0.4163150093263042</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2197516742449892</v>
+        <v>-0.2078927145107485</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.376795530138736</v>
+        <v>-0.3648384939368299</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.3158658062194988</v>
+        <v>-0.3039097374897466</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.3603269491765246</v>
+        <v>-0.3481007921629384</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3375095211829873</v>
+        <v>-0.3252591411503687</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.2049577511640592</v>
+        <v>-0.1927012549840157</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.2345180517851944</v>
+        <v>-0.2223505560591406</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.01773725599763765</v>
+        <v>0.04889554583521516</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.2290526268292155</v>
+        <v>-0.1976727055712573</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.0581778162389881</v>
+        <v>-0.0270128822435467</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.17422655494682</v>
+        <v>-0.1430767178319385</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.08583419365302092</v>
+        <v>-0.07370662170779241</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.2069900341342787</v>
+        <v>-0.1947283056794333</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.1709932013842419</v>
+        <v>-0.1588196965027961</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.3245246061264879</v>
+        <v>-0.3121855360123433</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.02318</t>
+          <t>X &gt; -0.02315</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3017</v>
+        <v>3020</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.802124038195672</v>
+        <v>-2.835191079232693</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.968480593864506</v>
+        <v>-1.969044964413364</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.975174532983075</v>
+        <v>-1.975011832152035</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.551459999387198</v>
+        <v>-1.551218441743337</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.272706281709993</v>
+        <v>-1.294513851749457</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.100289409573023</v>
+        <v>-1.122309643392931</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.7998813555208457</v>
+        <v>-0.8220735079080157</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.4991768055756083</v>
+        <v>-0.5216275238496522</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.6368447920733757</v>
+        <v>-0.6591766129067693</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.3358571151232681</v>
+        <v>-0.3583616863713743</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.5376322887877762</v>
+        <v>-0.5270135718469575</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.3684723466757731</v>
+        <v>-0.3579715082294683</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.5158374012109306</v>
+        <v>-0.5379970311441653</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.4864546139483039</v>
+        <v>-0.4756005478395267</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.3324970053674434</v>
+        <v>-0.3216796644272719</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.3790369382551404</v>
+        <v>-0.368276421299214</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.08323645250987255</v>
+        <v>-0.05305230892162882</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.4331454567328663</v>
+        <v>-0.4026696865286752</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.3297473032312865</v>
+        <v>-0.2994417364496016</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.4872144985104256</v>
+        <v>-0.4568919497389032</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.3155514023754336</v>
+        <v>-0.3047639529679103</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.4711345968035374</v>
+        <v>-0.4601785775687333</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.4748474949775172</v>
+        <v>-0.4639349371914889</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.4980064236383726</v>
+        <v>-0.487056693693134</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.01783</t>
+          <t>X &gt; -0.0178</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2892</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-3.742802724432117</v>
+        <v>-3.812550410135266</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.514965075668229</v>
+        <v>-2.515644523255503</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.184392573484693</v>
+        <v>-2.183402410984591</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.74546515625125</v>
+        <v>-1.743647513084667</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.404264059039591</v>
+        <v>-1.426292574837852</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.301336186169145</v>
+        <v>-1.323564320350528</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.9885039150285735</v>
+        <v>-1.010218247809377</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.8197082508430711</v>
+        <v>-0.8217961234974993</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.8964115977321683</v>
+        <v>-0.898552044759434</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.6177489406694647</v>
+        <v>-0.6189933605450051</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.8402870600328214</v>
+        <v>-0.8418548287761496</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.7206869629336836</v>
+        <v>-0.7416858719072295</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.9291462325527036</v>
+        <v>-0.949162200038721</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.8200462450990287</v>
+        <v>-0.8399288739628759</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.8723354791643345</v>
+        <v>-0.8916700985365082</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.8434376743949983</v>
+        <v>-0.8632809641778252</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.5289461373499975</v>
+        <v>-0.5283898140588406</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.9241800755698506</v>
+        <v>-0.923504862273326</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.7222647900955721</v>
+        <v>-0.7218451975271023</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.825777202072544</v>
+        <v>-0.7910371360108783</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.6781313243692892</v>
+        <v>-0.6427370172756852</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.8718334190289525</v>
+        <v>-0.8363419535395664</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.025982441262478</v>
+        <v>-0.9908033738623985</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.081628691368806</v>
+        <v>-1.046352490272874</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.01247</t>
+          <t>X &gt; -0.01245</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2658</v>
+        <v>2661</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-5.074943221215868</v>
+        <v>-5.096070994028985</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.261912764939225</v>
+        <v>-3.247740373147963</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.850866543359764</v>
+        <v>-2.837093296884468</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.423074916073823</v>
+        <v>-2.409749763221519</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.870372491677145</v>
+        <v>-1.886369522283552</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.924728205021026</v>
+        <v>-1.940593165061159</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.516607378009269</v>
+        <v>-1.53335125900697</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.383331248537189</v>
+        <v>-1.379433302603886</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.433197585986953</v>
+        <v>-1.429249469700494</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.174467390538219</v>
+        <v>-1.170782344560436</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.366018854831253</v>
+        <v>-1.362134073590987</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.382743942713951</v>
+        <v>-1.378809347499491</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.736051574141982</v>
+        <v>-1.731678197013565</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.748286925958894</v>
+        <v>-1.743894884055649</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.635087984233365</v>
+        <v>-1.630800533319118</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.543594352812548</v>
+        <v>-1.561151242560541</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.302312671586094</v>
+        <v>-1.298402258155505</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.573135039663775</v>
+        <v>-1.56891992677469</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.372712465793235</v>
+        <v>-1.368736037451221</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.314120631341595</v>
+        <v>-1.310222124107774</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.218463467998326</v>
+        <v>-1.214630153935673</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.309944938324769</v>
+        <v>-1.306009861633306</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.539613468523228</v>
+        <v>-1.535435186759315</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.518421712671447</v>
+        <v>-1.51426849227505</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.007121</t>
+          <t>X &gt; -0.007097</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-7.620915997988043</v>
+        <v>-7.651309188410174</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.40196707746319</v>
+        <v>-4.389928316491769</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.637561330356419</v>
+        <v>-3.581182227828478</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.669340916015031</v>
+        <v>-2.612847525868787</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.224871317123984</v>
+        <v>-2.206603952148058</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.494742023537832</v>
+        <v>-2.476294629150821</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.888576168776744</v>
+        <v>-1.870436792011219</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.817327578615384</v>
+        <v>-1.774882094649534</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.707755962819057</v>
+        <v>-1.665379740325257</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.494439056468394</v>
+        <v>-1.451585567510868</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.676896690869462</v>
+        <v>-1.634153748402788</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.955990594344364</v>
+        <v>-1.912903151850784</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.136034427796453</v>
+        <v>-2.092042102901779</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.113255468708076</v>
+        <v>-2.069103099534651</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.808120099506986</v>
+        <v>-1.738054093217521</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-2.020457669439125</v>
+        <v>-1.976270151116772</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.759987575775682</v>
+        <v>-1.690418139993156</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-2.278166958552255</v>
+        <v>-2.208454810495631</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.729661171662556</v>
+        <v>-1.685545885711647</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.780618964003509</v>
+        <v>-1.736608361156591</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.489754403730181</v>
+        <v>-1.445455538337185</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.496131749225547</v>
+        <v>-1.451765587433179</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.898642161075827</v>
+        <v>-1.854290284629855</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.509607351712617</v>
+        <v>-1.46536184156497</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001769</t>
+          <t>X &gt; -0.001747</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1736</v>
+        <v>1733</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-11.4214055681293</v>
+        <v>-11.5778098641483</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-6.183209963873381</v>
+        <v>-6.181927636710149</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-5.992786737658136</v>
+        <v>-6.044376905766896</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-4.645904607233653</v>
+        <v>-4.663602143766695</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.667728484988103</v>
+        <v>-4.655158537140139</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-4.04994512513268</v>
+        <v>-4.094020577842031</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.360180339854594</v>
+        <v>-3.342602575523962</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.294895443825865</v>
+        <v>-3.276184497014548</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.024153017771724</v>
+        <v>-3.004944299591514</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.734727736130324</v>
+        <v>-2.712182303263717</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.747065716721409</v>
+        <v>-2.693818562432327</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.02615962019631</v>
+        <v>-2.972567965880323</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.627355823761377</v>
+        <v>-2.600617899326437</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.217616822977043</v>
+        <v>-2.156228281055945</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.532313982840499</v>
+        <v>-2.469147182779203</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.70786137528853</v>
+        <v>-2.680283851169925</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.210496975292791</v>
+        <v>-2.148231262690558</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.971733874118009</v>
+        <v>-2.943918253212949</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.745951841597446</v>
+        <v>-1.749327966128575</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.928191489361694</v>
+        <v>-1.932445730202346</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-1.723835831654647</v>
+        <v>-1.726143971901095</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.766307363374743</v>
+        <v>-1.76849015243662</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.26399745417455</v>
+        <v>-2.267858796588627</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.730805508394639</v>
+        <v>-1.733545766349742</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.003584</t>
+          <t>X &gt; 0.003604</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-15.7208579085711</v>
+        <v>-15.79865709732891</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-9.493167888137059</v>
+        <v>-9.531179467337338</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-8.233501016442517</v>
+        <v>-8.274239254124616</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-6.525986823582407</v>
+        <v>-6.529822786707129</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-5.51918235517627</v>
+        <v>-5.494645517318922</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-5.21003964998247</v>
+        <v>-5.266543139183213</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-4.609723229532456</v>
+        <v>-4.62410662264746</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.242074320931472</v>
+        <v>-4.17533906901604</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.231252924729517</v>
+        <v>-3.164546555922016</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.233770997053092</v>
+        <v>-3.166144893512651</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.444456192346813</v>
+        <v>-3.377129713759786</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.319346377147504</v>
+        <v>-3.332516142268418</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.180296771059069</v>
+        <v>-2.19213738454895</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.674086888479842</v>
+        <v>-1.638950302797269</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-2.333018127517143</v>
+        <v>-2.297093600377828</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-2.546365515244183</v>
+        <v>-2.511768167107974</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.11457400324921</v>
+        <v>-2.079342262014251</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.785442625488386</v>
+        <v>-2.750526007906629</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.9859920156851558</v>
+        <v>-0.9974177985033421</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.589574898785429</v>
+        <v>-0.6487596908006807</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.3230587085930878</v>
+        <v>-0.3822443700935807</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.02657037549955987</v>
+        <v>-0.1344657360334125</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.453578029114666</v>
+        <v>-1.511983214634</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.5901310453749957</v>
+        <v>-0.6492922492009825</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.008936</t>
+          <t>X &gt; 0.008955</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-19.72705581311558</v>
+        <v>-19.8477436651561</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-12.07381304942738</v>
+        <v>-12.13654345201167</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-11.50436070628056</v>
+        <v>-11.57014468693475</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-8.642606153268417</v>
+        <v>-8.661159192237079</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-7.047091624566981</v>
+        <v>-7.038424319162232</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-6.687316193017317</v>
+        <v>-6.736250759792966</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-5.959027590660263</v>
+        <v>-5.951637539984453</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.198321266201916</v>
+        <v>-5.19178670100051</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.925858318962185</v>
+        <v>-4.919619011588694</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.598624432317422</v>
+        <v>-4.592806656214272</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.94276227502867</v>
+        <v>-5.935375189571978</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.528214560006461</v>
+        <v>-5.521283946368705</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.415711558840428</v>
+        <v>-3.411189662185564</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.29024756062622</v>
+        <v>-3.220969495793497</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-3.833571863247343</v>
+        <v>-3.763505856957877</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-5.203829732701116</v>
+        <v>-5.13443685409004</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-4.181854062688188</v>
+        <v>-4.112284626905662</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-5.327299906529127</v>
+        <v>-5.257587758472503</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-3.543525277101907</v>
+        <v>-3.538806204137764</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.480446118192347</v>
+        <v>-2.542711839256448</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.67602196172102</v>
+        <v>-2.738437197973923</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.172602741581464</v>
+        <v>-2.236248477302105</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-3.404200692132946</v>
+        <v>-3.399635036496349</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.602746231394413</v>
+        <v>-2.599163697599117</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.01429</t>
+          <t>X &gt; 0.01431</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>648</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-21.61305270346072</v>
+        <v>-21.83656576786622</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-14.10104003966118</v>
+        <v>-14.22027222982459</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-12.56997747636488</v>
+        <v>-12.68776240951109</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-8.995868798746393</v>
+        <v>-8.959675081327489</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-7.52346630199402</v>
+        <v>-7.610932628913048</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.187521636562842</v>
+        <v>-6.35199094511276</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.659774271684356</v>
+        <v>-4.746756453663245</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.478206217816407</v>
+        <v>-4.564845199029818</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.743438619051453</v>
+        <v>-4.830106483372781</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.822024625883564</v>
+        <v>-4.908008353372317</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-5.776544007001718</v>
+        <v>-5.86282735944387</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.209247741505799</v>
+        <v>-6.295186593921052</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.107932508380038</v>
+        <v>-4.192542209164273</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.561240164268476</v>
+        <v>-3.559786747905555</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-3.452122248159839</v>
+        <v>-3.448699276255347</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-5.161209663976251</v>
+        <v>-5.162004662004655</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-4.220034540920871</v>
+        <v>-4.218998722059055</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-5.70750643627882</v>
+        <v>-5.708454810495624</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-3.715889949466586</v>
+        <v>-3.800255737263605</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-2.518297380585523</v>
+        <v>-2.690333004218658</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.753331379722141</v>
+        <v>-2.925186864492382</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-2.2129536156421</v>
+        <v>-2.385648210516862</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.862677678743957</v>
+        <v>-2.947015622012529</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.461988304093566</v>
+        <v>-1.546454944040612</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.01964</t>
+          <t>X &gt; 0.01966</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-22.8440818800591</v>
+        <v>-23.00843604623829</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-16.7815741481179</v>
+        <v>-16.82147371415332</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-15.36963230511618</v>
+        <v>-15.41364296081277</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-10.92469545957918</v>
+        <v>-10.97808212877036</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-8.909012863650851</v>
+        <v>-8.937634977555263</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-6.936133964929773</v>
+        <v>-6.968490573636103</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.72487311285682</v>
+        <v>-5.658481061706873</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.217713472661089</v>
+        <v>-4.150978220745657</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.176197407638455</v>
+        <v>-4.109491038830953</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.844317901559769</v>
+        <v>-4.882406714867443</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.558030205020977</v>
+        <v>-6.592474056832508</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.439509794380562</v>
+        <v>-6.474398063455098</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.383086499945243</v>
+        <v>-4.422956955708045</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.610407525691329</v>
+        <v>-3.541129460858606</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-3.076495822382711</v>
+        <v>-3.006429816093245</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-4.668314500395518</v>
+        <v>-4.598921621784442</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-4.007179566313823</v>
+        <v>-3.937610130531297</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-5.901427395927996</v>
+        <v>-5.831715247871372</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-4.382760927094544</v>
+        <v>-4.422980924601113</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-3.48677644710579</v>
+        <v>-3.639713643460126</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.832372065684581</v>
+        <v>-2.98941686908023</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-3.307528718133575</v>
+        <v>-3.462877144604647</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-2.83315275324825</v>
+        <v>-2.87672666996248</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.395321637426903</v>
+        <v>-1.442034155987095</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.02499</t>
+          <t>X &gt; 0.02501</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-21.66419584743814</v>
+        <v>-21.71015404412504</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-16.54031429012217</v>
+        <v>-16.5993862880194</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-15.39924614070016</v>
+        <v>-15.46327075237605</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-10.14289020016198</v>
+        <v>-10.22088978422573</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-7.523085358320358</v>
+        <v>-7.579012762976483</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-6.340895869691678</v>
+        <v>-6.399490745613598</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-6.367493345029288</v>
+        <v>-6.301101293879341</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.163460925871235</v>
+        <v>-3.096725673955802</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.116969736470487</v>
+        <v>-4.050263367662986</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.508675893260438</v>
+        <v>-4.574422824794006</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.226835329386994</v>
+        <v>-7.285437809497758</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-6.508422998447926</v>
+        <v>-6.569162337323853</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-5.139148630900159</v>
+        <v>-5.204762215125243</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.864246090313571</v>
+        <v>-3.794968025480848</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-3.525671094936904</v>
+        <v>-3.455605088647438</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-4.676246955539959</v>
+        <v>-4.606854076928883</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-4.560964091085395</v>
+        <v>-4.491394655302869</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-6.162206858801625</v>
+        <v>-6.092494710745001</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-5.062043795620426</v>
+        <v>-5.1284736540102</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-3.986528822055135</v>
+        <v>-4.193498168231699</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-3.777849531804975</v>
+        <v>-3.987914660387261</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-3.853804587447584</v>
+        <v>-4.063760621796362</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-3.579029420965455</v>
+        <v>-3.649635036496342</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.006376913808815</v>
+        <v>-2.081357014030402</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.03035</t>
+          <t>X &gt; 0.03036</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>322</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-19.93179011740724</v>
+        <v>-19.89851582508841</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-14.13199630689819</v>
+        <v>-14.09832329828485</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-15.14130507678895</v>
+        <v>-15.22959388105817</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-9.393559928443651</v>
+        <v>-9.500830109089875</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-7.604983559621537</v>
+        <v>-7.689381317833458</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.571665100460912</v>
+        <v>-5.661924334190076</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-7.267608155591859</v>
+        <v>-7.201216104441912</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.392316647264259</v>
+        <v>-1.325581395348827</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.196954428395479</v>
+        <v>-3.130248059587977</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.260438462146858</v>
+        <v>-2.364702197162927</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-5.689782898735231</v>
+        <v>-5.782950247308698</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.425666925666917</v>
+        <v>-4.523238112295161</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-4.315590242919498</v>
+        <v>-4.415630948382038</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.685095202102005</v>
+        <v>-2.615817137269282</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-2.418100515213375</v>
+        <v>-2.348034508923909</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-3.057608366826571</v>
+        <v>-2.988215488215495</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-2.574418110358202</v>
+        <v>-2.504848674575676</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-5.457179304231261</v>
+        <v>-5.387467156174637</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-4.144087139273687</v>
+        <v>-4.245649849324387</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-2.542701863354033</v>
+        <v>-2.824236138121798</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-2.154225253718451</v>
+        <v>-2.440856380161897</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-2.540739315572239</v>
+        <v>-2.825344316879637</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.955405142878931</v>
+        <v>-2.064495717610903</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.1425665613308595</v>
+        <v>0.212420909038137</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.0357</t>
+          <t>X &gt; 0.03571</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>260</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-19.58321231484171</v>
+        <v>-19.54993802252288</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-13.47899389009209</v>
+        <v>-13.44532088147875</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-14.00413046432917</v>
+        <v>-14.12576417293398</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-8.634273587408259</v>
+        <v>-8.778112131770662</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-8.619315235550175</v>
+        <v>-8.73511472553006</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.770553664368485</v>
+        <v>-5.896633387917532</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-7.303876070186774</v>
+        <v>-7.237484019036827</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.498780525591265</v>
+        <v>-1.432045273675833</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.978177008097148</v>
+        <v>-2.911470639289647</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.3994451533164</v>
+        <v>-2.54370190467975</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-6.323559168643811</v>
+        <v>-6.452151768221249</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.694256125553835</v>
+        <v>-4.829760487258596</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.528671008163109</v>
+        <v>-3.671553732821941</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.078272094006628</v>
+        <v>-1.008994029173905</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.9738445544179726</v>
+        <v>-0.903778548128507</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-2.287181451361484</v>
+        <v>-2.217788572750408</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.276236977571472</v>
+        <v>-1.206667541788946</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-4.816334897483543</v>
+        <v>-4.746622749426919</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-4.006488240064876</v>
+        <v>-4.149051979189622</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.067307692307693</v>
+        <v>-2.435488611969681</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.456661947459487</v>
+        <v>-1.832996611996784</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.917232387717483</v>
+        <v>-2.290521962718856</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-2.027072605850748</v>
+        <v>-2.178370668680259</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.1799370220422887</v>
+        <v>-0.1100826743350112</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.04105</t>
+          <t>X &gt; 0.04106</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>209</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-20.81027164049258</v>
+        <v>-20.77699734817375</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-12.22525936170968</v>
+        <v>-12.19158635309634</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-12.05277096938692</v>
+        <v>-12.22115469790197</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-8.049583150504603</v>
+        <v>-8.239273036593545</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-7.943154822321105</v>
+        <v>-8.105579941065699</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-6.340895869691678</v>
+        <v>-6.510163050742968</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-7.58546011495325</v>
+        <v>-7.519068063803303</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.731939288773702</v>
+        <v>-1.66520403685827</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-4.992310016203888</v>
+        <v>-4.925603647396386</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-4.096199974053711</v>
+        <v>-4.283424983810242</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-9.509044498407576</v>
+        <v>-9.669742700138883</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-7.418470155436978</v>
+        <v>-7.590001537549142</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-5.22542582890042</v>
+        <v>-5.411276811952433</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.077114393489275</v>
+        <v>-3.007836328656552</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-3.262111983237482</v>
+        <v>-3.192045976948016</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-5.984587478639803</v>
+        <v>-5.915194600028727</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-2.801145627765024</v>
+        <v>-2.731576191982498</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-6.223664588884006</v>
+        <v>-6.153952440827382</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-5.752519986096623</v>
+        <v>-5.938061059903056</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-2.915669856459338</v>
+        <v>-3.38154700348953</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-2.501932466414225</v>
+        <v>-2.976225872877357</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-2.577887522056834</v>
+        <v>-3.052071834286458</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-3.738519054139289</v>
+        <v>-3.935349322210634</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-2.857522594364703</v>
+        <v>-2.787668246657425</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.0464</t>
+          <t>X &gt; 0.04641</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>174</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-21.65164949563844</v>
+        <v>-21.61837520331961</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-14.12165647095692</v>
+        <v>-14.08798346234358</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-11.9461725257242</v>
+        <v>-12.15521599452064</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-7.010248324793061</v>
+        <v>-7.250192485873491</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-6.810546358404679</v>
+        <v>-7.024185205611779</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.928466491160599</v>
+        <v>-5.15182576108743</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-6.831276126039491</v>
+        <v>-6.764884074889544</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.895141506021325</v>
+        <v>-0.828406254105893</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5.938371203710552</v>
+        <v>-5.871664834903051</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.851908720283788</v>
+        <v>-6.079608759527119</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-9.554822180441178</v>
+        <v>-9.760351377252199</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-7.561188811188806</v>
+        <v>-7.779213775050479</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-5.276589120585044</v>
+        <v>-5.512545333432016</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.520673204346664</v>
+        <v>-1.451395139513942</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-2.747786261565793</v>
+        <v>-2.677720255276327</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-4.993635302853505</v>
+        <v>-4.924242424242429</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-1.718638087911508</v>
+        <v>-1.649068652128982</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-5.232712413097708</v>
+        <v>-5.163000265041084</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-4.704900938477572</v>
+        <v>-4.947108884116759</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-1.329022988505749</v>
+        <v>-1.919353983239638</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.7227981101473802</v>
+        <v>-1.325536514842028</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-1.373465809468158</v>
+        <v>-1.969564294432942</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-2.822828574020498</v>
+        <v>-3.07820646506778</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.74934462593265</v>
+        <v>-1.679490278225373</v>
       </c>
     </row>
     <row r="29">
@@ -5073,76 +5073,76 @@
         <v>149</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-20.9943828436593</v>
+        <v>-20.96110855134047</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-16.10080018836898</v>
+        <v>-16.06712717975564</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-14.65952370027073</v>
+        <v>-14.89076714381931</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-8.794369645042842</v>
+        <v>-9.067773450843752</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-7.185955219540574</v>
+        <v>-7.442779609665536</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-6.998790606533788</v>
+        <v>-7.255813423568156</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-9.74534094911413</v>
+        <v>-9.678948897964183</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.787053489369534</v>
+        <v>-2.720318237454102</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-7.350800582241632</v>
+        <v>-7.28409421343413</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-6.469006853938218</v>
+        <v>-6.741220415786408</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-10.16815752059771</v>
+        <v>-10.41452919467712</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-7.798244801556052</v>
+        <v>-8.061699650756694</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-6.273729397526644</v>
+        <v>-6.553282770244394</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.197072963527887</v>
+        <v>-1.127794898695164</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-2.51825585819433</v>
+        <v>-2.448189851904864</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-3.909950775460366</v>
+        <v>-3.84055789684929</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.7327861914635889</v>
+        <v>-0.6632167556810629</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-5.473531196962846</v>
+        <v>-5.403819048906222</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-4.895377128953768</v>
+        <v>-5.187927667981896</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-1.656879194630868</v>
+        <v>-2.35207523549731</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-1.528938664031507</v>
+        <v>-2.232369747834205</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-2.276034659271431</v>
+        <v>-2.970467364872441</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-4.014682311581254</v>
+        <v>-4.316301703163013</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-2.748341771655092</v>
+        <v>-2.678487423947814</v>
       </c>
     </row>
     <row r="30">
@@ -5155,76 +5155,76 @@
         <v>135</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-21.06542575357688</v>
+        <v>-21.03215146125805</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-18.50205054358353</v>
+        <v>-18.46837753497019</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-13.84315796842287</v>
+        <v>-14.10929513472582</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-7.987608215922592</v>
+        <v>-8.300510023733771</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-6.893023986348098</v>
+        <v>-7.187025133962202</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-6.705859373341312</v>
+        <v>-7.000058947864822</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-7.478725505395339</v>
+        <v>-7.412333454245392</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.64779109981901</v>
+        <v>-2.581055847903578</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-5.525983063993451</v>
+        <v>-5.459276695185949</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.448165404775771</v>
+        <v>-4.772338356623905</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-7.850276725895725</v>
+        <v>-8.147913750958331</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-5.188194158782387</v>
+        <v>-5.506955125209245</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-4.842097141975422</v>
+        <v>-5.170263177466829</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.289487223460817</v>
+        <v>2.35876528829354</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.630555984423516</v>
+        <v>1.700621990712982</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.7155604365433348</v>
+        <v>-0.6461675579322588</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>2.826816457543032</v>
+        <v>2.896385893325558</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-1.689931664434596</v>
+        <v>-1.620219516377972</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-1.784266017842661</v>
+        <v>-2.139622253100711</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>2.106481481481481</v>
+        <v>1.723694145102613</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.563281072483527</v>
+        <v>1.181147977136582</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>1.487326016840917</v>
+        <v>1.105302015727482</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.4601210388991817</v>
+        <v>-0.3903757772370966</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.9454191033138386</v>
+        <v>1.015273451021116</v>
       </c>
     </row>
     <row r="31">
@@ -5237,76 +5237,76 @@
         <v>123</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-19.2741214057508</v>
+        <v>-19.24084711343197</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-16.40929692039512</v>
+        <v>-16.37562391178178</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-11.09415867480384</v>
+        <v>-11.41364296081277</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-6.162790697674417</v>
+        <v>-6.526596980255512</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.72160886979524</v>
+        <v>-6.062387452802788</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-7.147347482594903</v>
+        <v>-7.475421266705411</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-7.113762001745705</v>
+        <v>-7.047369950595758</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.74715535694169</v>
+        <v>-1.680420105026258</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4.93144574353196</v>
+        <v>-4.864739374724458</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-4.466099407645203</v>
+        <v>-4.831203437857724</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-7.443772660855075</v>
+        <v>-7.782950247308698</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-4.470834044004768</v>
+        <v>-4.835893199143797</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.969309002329311</v>
+        <v>-4.346152040193459</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.939415487449338</v>
+        <v>4.008693552282061</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>3.280484248412037</v>
+        <v>3.350550254701503</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>1.436519907789517</v>
+        <v>1.505912786400593</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.367466864047088</v>
+        <v>5.437036299829614</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.3844346674640207</v>
+        <v>0.4541468155206445</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.2124502996854716</v>
+        <v>-0.142969933636337</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.226626016260155</v>
+        <v>3.295908396656884</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>5.122449997506102</v>
+        <v>5.192386618934755</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>4.233486811782207</v>
+        <v>4.303532527444368</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.882245718101721</v>
+        <v>2.951990979763806</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>4.432320638995868</v>
+        <v>4.502174986703146</v>
       </c>
     </row>
     <row r="32">
@@ -5319,322 +5319,322 @@
         <v>103</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-18.43602616765556</v>
+        <v>-18.40275187533673</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-14.96167787277607</v>
+        <v>-14.92800486416273</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-9.295151230635106</v>
+        <v>-9.699357246527057</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-5.201252236135957</v>
+        <v>-5.650406504065039</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-5.566522021160004</v>
+        <v>-5.986196976612312</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-7.302434331230145</v>
+        <v>-7.703992695276838</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-6.152223540207245</v>
+        <v>-6.085831489057298</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.623085878033493</v>
+        <v>-1.556350626118061</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6.389262120703172</v>
+        <v>-6.322555751895671</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.755703954176113</v>
+        <v>-4.210856043316774</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-6.393966046284078</v>
+        <v>-6.821411785770238</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.789564804127913</v>
+        <v>-3.25400734306438</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.97230844979952</v>
+        <v>-2.454092486843585</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>6.544198816836037</v>
+        <v>6.61347688166876</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5.885267577798736</v>
+        <v>5.955333584088201</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>3.567706268196815</v>
+        <v>3.637099146807891</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>7.317107719678958</v>
+        <v>7.386677155461484</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>2.357755371544833</v>
+        <v>2.427467519601457</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>1.603004748068884</v>
+        <v>1.672485114118018</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>4.702669902912632</v>
+        <v>4.771952283309361</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>7.072090853137972</v>
+        <v>7.142027474566625</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.025262011087598</v>
+        <v>6.095307726749759</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>4.358289604754198</v>
+        <v>4.428034866416283</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>6.22409583830126</v>
+        <v>6.293950186008537</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.07317</t>
+          <t>X &gt; 0.07316</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>92</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-19.63156821426143</v>
+        <v>-19.59829392194261</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-16.77525436720364</v>
+        <v>-16.7415813585903</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-10.28770706190062</v>
+        <v>-10.73279189698299</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-7.775693923480866</v>
+        <v>-8.254256554723597</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-8.140963708504913</v>
+        <v>-8.59004702727087</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-7.953799095498127</v>
+        <v>-8.403080841173491</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-5.500858775939257</v>
+        <v>-5.43446672478931</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.4030693354363066</v>
+        <v>-0.3363340835208746</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.587359722026584</v>
+        <v>-3.520653353219082</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.5159403408371475</v>
+        <v>-1.067762577642661</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-4.589407160678327</v>
+        <v>-5.094778204297945</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.607631498935845</v>
+        <v>-2.147721156133045</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.5582096739447238</v>
+        <v>-1.120345588580548</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.829129167194829</v>
+        <v>6.898407232027552</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>7.257154449896667</v>
+        <v>7.327220456186133</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>4.591344934300643</v>
+        <v>4.660737812911719</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>8.805077327108251</v>
+        <v>8.874646762890777</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.35226782405644</v>
+        <v>4.421979972113064</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.481434465249137</v>
+        <v>3.550914831298272</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>6.929347826086953</v>
+        <v>6.998630206483682</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>8.560060460567264</v>
+        <v>8.629997081995917</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>7.39714888318553</v>
+        <v>7.467194598847691</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>6.584967527928519</v>
+        <v>6.654712789590604</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>7.595982710399191</v>
+        <v>7.665837058106469</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.07852</t>
+          <t>X &gt; 0.07851</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>80</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-16.63708436871376</v>
+        <v>-16.60381007639493</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-14.50312408088895</v>
+        <v>-14.46945107227561</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-9.19899738448126</v>
+        <v>-9.73463061513376</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-6.162790697674417</v>
+        <v>-6.743880930872798</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.528060482698464</v>
+        <v>-7.079671403420072</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-5.090895869691686</v>
+        <v>-5.658137316088123</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-5.863762001745712</v>
+        <v>-5.797369950595765</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1076833527357266</v>
+        <v>0.1744186046511587</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-2.350800582241625</v>
+        <v>-2.284094213434123</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.6253640069889386</v>
+        <v>0.6929901105293794</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.850276725895718</v>
+        <v>-2.78295024730869</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.6293706293706336</v>
+        <v>-0.5616996507567009</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.5038618478577703</v>
+        <v>-0.4348617176128116</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>9.274781341107875</v>
+        <v>9.344059405940598</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>8.615850102070574</v>
+        <v>8.68591610836004</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>5.460910151691955</v>
+        <v>5.530303030303031</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>11.57681645754303</v>
+        <v>11.64638589332556</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>7.721833041447752</v>
+        <v>7.791545189504376</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>6.687956204379567</v>
+        <v>6.757436570428702</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>10.625</v>
+        <v>10.69428238039673</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>12.58179959100205</v>
+        <v>12.6517362124307</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>11.25584453535944</v>
+        <v>11.3258902510216</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>10.28061970184157</v>
+        <v>10.35036496350365</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>11.4546783625731</v>
+        <v>11.52453271028038</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.08387</t>
+          <t>X &gt; 0.08386</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>68</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-13.09441126082326</v>
+        <v>-13.06113696850443</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-11.98031141314875</v>
+        <v>-11.94663840453541</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-2.507820913893021</v>
+        <v>-3.239729917334515</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-3.221614227086178</v>
+        <v>-3.952683936777255</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-7.99864871799258</v>
+        <v>-8.636300496281045</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-6.340895869691678</v>
+        <v>-7.000058947864822</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.231409060569234</v>
+        <v>-1.165017009419287</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>2.901800999794553</v>
+        <v>2.968536251709985</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.472728829523078</v>
+        <v>1.53943519833058</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.110658124635997</v>
+        <v>5.178284228176437</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.9732526858689852</v>
+        <v>1.040579164456013</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3.635335252982316</v>
+        <v>3.703006231596248</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>3.981432269789288</v>
+        <v>4.050432400034246</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>14.05419310581376</v>
+        <v>14.12347117064648</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>13.39526186677646</v>
+        <v>13.46532787306592</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>9.578557210515477</v>
+        <v>9.647950089126553</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>15.32681645754303</v>
+        <v>15.39638589332556</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>12.28065657085952</v>
+        <v>12.35036871891614</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>11.02619149849722</v>
+        <v>11.09567186454635</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>14.15441176470588</v>
+        <v>14.22369414510261</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>18.02297606159028</v>
+        <v>18.09291268301893</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>16.47643277065355</v>
+        <v>16.54647848631571</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>15.28061970184157</v>
+        <v>15.35036496350365</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>16.67526659786721</v>
+        <v>16.74512094557449</v>
       </c>
     </row>
   </sheetData>
@@ -5824,1887 +5824,1887 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.07135</t>
+          <t>X &lt; -0.0713</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>68</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>17.34037134787239</v>
+        <v>17.37364564019122</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.410992934677338</v>
+        <v>5.44466594329068</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.11622000682308</v>
+        <v>14.15157443049157</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.50387596899224</v>
+        <v>10.54006968641114</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.892229372373997</v>
+        <v>2.957902402269674</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.630118623061946</v>
+        <v>1.695593226048217</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.306527853326756</v>
+        <v>2.372919904476703</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.8705775168294849</v>
+        <v>-0.8038422649140529</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.6202139105119926</v>
+        <v>0.6869202793194944</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.74492922438025</v>
+        <v>2.812555327920691</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.328537595460944</v>
+        <v>-1.261211116873916</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.607631498935845</v>
+        <v>-1.539960520321912</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.282847355104145</v>
+        <v>-1.213847224859187</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.5042041661385</v>
+        <v>-1.434926101305777</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.735415319461886</v>
+        <v>0.8054813257513516</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1.330475369083267</v>
+        <v>1.399868247694343</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.849654130692258</v>
+        <v>-1.632599613920817</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>1.986538923800694</v>
+        <v>1.161110406895688</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.202662086732509</v>
+        <v>1.377001787820014</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>3.860294117647058</v>
+        <v>3.01312296010687</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>6.258270179237336</v>
+        <v>6.328206800665988</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>6.182315123594726</v>
+        <v>6.252360839256887</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>4.98650205478274</v>
+        <v>5.056247316444825</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.381148950808388</v>
+        <v>6.451003298515666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.066</t>
+          <t>X &lt; -0.06595</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>80</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>19.16538476708871</v>
+        <v>19.19865905940754</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.953666042567839</v>
+        <v>8.987339051181181</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>14.92137298588911</v>
+        <v>14.95672740955759</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.50387596899224</v>
+        <v>10.54006968641114</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.965766677795365</v>
+        <v>4.031439707691042</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.152931290802151</v>
+        <v>4.218405893788422</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.380065158748124</v>
+        <v>3.446457209898071</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.6021931904741464</v>
+        <v>-0.5354579385587144</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5606771254515124</v>
+        <v>-0.4939707566440106</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.369191167482768</v>
+        <v>2.436817271023209</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1744146321289719</v>
+        <v>0.2417411107159992</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1046792713459297</v>
+        <v>-0.03700829273199702</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.005397411401482088</v>
+        <v>0.07439754164644086</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.018608501601705</v>
+        <v>1.087886566434427</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>4.063380966268106</v>
+        <v>4.133446972557572</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>2.189305213420347</v>
+        <v>2.258698092031423</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>1.576816457543039</v>
+        <v>0.8902130538193873</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>2.721833041447752</v>
+        <v>2.019940251232768</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>2.937956204379567</v>
+        <v>2.235831632157094</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>5.625</v>
+        <v>4.89181324459426</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>7.581799591002046</v>
+        <v>7.651736212430698</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>8.755844535359437</v>
+        <v>8.825890251021598</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>6.530619701841566</v>
+        <v>6.600364963503651</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>6.454678362573098</v>
+        <v>6.524532710280376</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.06065</t>
+          <t>X &lt; -0.0606</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>93</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>17.60247433893005</v>
+        <v>17.63574863124888</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8.756660526413384</v>
+        <v>8.790333535026726</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>14.76376857296555</v>
+        <v>14.79912299663403</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.794656110836222</v>
+        <v>9.830849828255126</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.110237389641966</v>
+        <v>4.175910419537644</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.297402002648752</v>
+        <v>4.362876605635023</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.524535870594725</v>
+        <v>3.590927921744672</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.009337923860016</v>
+        <v>-0.9426026719445844</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.9678218588373824</v>
+        <v>-0.9011154900298806</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.44983209209532</v>
+        <v>1.517458195635761</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.4034682152574192</v>
+        <v>-0.3361417366703918</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.6825621187323208</v>
+        <v>-0.6148911401183881</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3206062372486116</v>
+        <v>0.3896063674935704</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.163079213448306</v>
+        <v>1.232357278281029</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>2.631807548879081</v>
+        <v>2.701873555168547</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.099208024032386</v>
+        <v>1.168600902643462</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.5418702209838955</v>
+        <v>-0.02914602156806012</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.512155622092912</v>
+        <v>0.9298430618448066</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.728278785024727</v>
+        <v>1.145734442769132</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>4.06586021505376</v>
+        <v>3.460239827205235</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>5.673197440464413</v>
+        <v>5.743134061893066</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>4.79674873409963</v>
+        <v>4.866493995761715</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>5.796076212035466</v>
+        <v>5.865930559742743</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.05529</t>
+          <t>X &lt; -0.05525</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>110</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>19.29885156722217</v>
+        <v>19.332125859541</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.152865241767039</v>
+        <v>8.18653825038038</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>13.92037198488811</v>
+        <v>13.95572640855659</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.602975068091361</v>
+        <v>9.639168785510265</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.634101679463697</v>
+        <v>5.699774709359374</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.821266292470483</v>
+        <v>5.886740895456754</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.147499259515548</v>
+        <v>4.213891310665495</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2653410103933922</v>
+        <v>0.3320762623088243</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.207757976316927</v>
+        <v>1.274464345124429</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.235724367349306</v>
+        <v>2.303350470889747</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.7082818326628342</v>
+        <v>0.7756083112498615</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4291879291879326</v>
+        <v>0.4968589078018653</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2055976116016893</v>
+        <v>0.2745977418466481</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.786042602369129</v>
+        <v>1.855320667201852</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2.028012264232736</v>
+        <v>2.098078270522201</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.0796303888485852</v>
+        <v>-0.01023751023750918</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.5822744515478746</v>
+        <v>-1.045055548115883</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.130923950538666</v>
+        <v>0.6519055498647433</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.347047113470481</v>
+        <v>0.8677969307890692</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2.443181818181813</v>
+        <v>1.955543641657982</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2.809072318274779</v>
+        <v>2.879008939703432</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>4.551299080813983</v>
+        <v>4.621344796476144</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>2.098801520023379</v>
+        <v>2.168546781685464</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>4.750132908027645</v>
+        <v>4.819987255734922</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.04994</t>
+          <t>X &lt; -0.0499</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>128</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>19.96928944696238</v>
+        <v>20.00256373928121</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>11.10698214937232</v>
+        <v>11.14065515798566</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>15.86883207288308</v>
+        <v>15.90418649655157</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.50387596899224</v>
+        <v>10.54006968641114</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.813024788619373</v>
+        <v>7.87869781851505</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.000189401626159</v>
+        <v>8.065664004612429</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.901741874223283</v>
+        <v>4.96813392537323</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.7472182364566677</v>
+        <v>0.8139534883720998</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.114315696828129</v>
+        <v>3.181022065635631</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.565286487609086</v>
+        <v>1.632912591149527</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2892581578252091</v>
+        <v>0.3565846364122365</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.7853580527999213</v>
+        <v>0.853029031413854</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.211254431211991</v>
+        <v>1.28025456145695</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.9898976201776364</v>
+        <v>1.059175685010359</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.106160179589949</v>
+        <v>1.176226185879415</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.624361166137497</v>
+        <v>-0.554968287526421</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.2981835424569681</v>
+        <v>-0.6888854245038942</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>1.159333041447752</v>
+        <v>0.7566614685741371</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.375456204379567</v>
+        <v>0.972552849498463</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.78125</v>
+        <v>0.384204861016876</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.2380495910020457</v>
+        <v>0.3079862124306985</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>3.287094535359437</v>
+        <v>3.357140251021598</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.4368697018415659</v>
+        <v>0.506614963503651</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>3.485928362573098</v>
+        <v>3.555782710280376</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.04459</t>
+          <t>X &lt; -0.04455</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>153</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>19.70250197087258</v>
+        <v>19.7357762631914</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>13.52317061207241</v>
+        <v>13.55684362068575</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>17.92762599214211</v>
+        <v>17.9629804158106</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>11.36967683479312</v>
+        <v>11.40587055221202</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.407004452366465</v>
+        <v>8.472677482262142</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>8.594169065373251</v>
+        <v>8.659643668359521</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5.223900335916632</v>
+        <v>5.290292387066579</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.698592443644827</v>
+        <v>1.765327695560259</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.038809807368764</v>
+        <v>3.105516176176266</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.264974396599335</v>
+        <v>2.332600500139776</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.240632365013369</v>
+        <v>1.307958843600396</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.961538461538467</v>
+        <v>1.0292094401524</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.785099191103264</v>
+        <v>1.854099321348222</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.213093029419568</v>
+        <v>2.282371094252291</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2.852863089083563</v>
+        <v>2.922929095373028</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2.149221840003648</v>
+        <v>2.218614718614724</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>1.111130183033225</v>
+        <v>0.7859962829359546</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2.966931080663436</v>
+        <v>2.629207527166713</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.529459472353423</v>
+        <v>2.195748258740394</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>2.062908496732028</v>
+        <v>1.733243419357763</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.866113316492239</v>
+        <v>0.9360499379208918</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>4.71172688830061</v>
+        <v>4.781772603962771</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>2.372122969815422</v>
+        <v>2.441868231477507</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>4.256965944272444</v>
+        <v>4.326820291979722</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.03924</t>
+          <t>X &lt; -0.0392</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>190</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>20.67142833246911</v>
+        <v>20.70470262478793</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>13.52997009531168</v>
+        <v>13.56364310392502</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>15.23163088777005</v>
+        <v>15.26698531143854</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9.282235480336048</v>
+        <v>9.318429197754952</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.346285067039759</v>
+        <v>7.411958096935436</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>8.057009889470621</v>
+        <v>8.122484492456891</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.237023338568427</v>
+        <v>6.303415389718374</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.34066764592945</v>
+        <v>3.407402897844882</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.476424548648417</v>
+        <v>5.543130917455919</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4.179028928454912</v>
+        <v>4.246655031995353</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.929827986146158</v>
+        <v>3.997154464733185</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.60361366382309</v>
+        <v>2.671284642437023</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.096923492456362</v>
+        <v>4.165923622701321</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.875566681422008</v>
+        <v>3.944844746254731</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>4.263755861232873</v>
+        <v>4.333821867522339</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>3.811695492006088</v>
+        <v>3.881088370617164</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.379448036490402</v>
+        <v>1.129370186519274</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>3.90604356776354</v>
+        <v>3.642330529818508</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>3.069535151747985</v>
+        <v>2.811101491894675</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>2.73026315789474</v>
+        <v>2.474387092438612</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>1.134431169949416</v>
+        <v>1.204367791378068</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>3.690055061675224</v>
+        <v>3.760100777337385</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>2.912198649209984</v>
+        <v>2.981943910872069</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>3.888888888888886</v>
+        <v>3.958743236596163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.03388</t>
+          <t>X &lt; -0.03385</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>21.83608267588185</v>
+        <v>21.96890898412901</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>16.19478471225793</v>
+        <v>16.34957934025074</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>16.38773730939629</v>
+        <v>16.53757655138235</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11.59231134314191</v>
+        <v>11.75958188153311</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>10.00255176219949</v>
+        <v>10.20427921386387</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9.37338984459403</v>
+        <v>9.578237269879963</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7.784197181927759</v>
+        <v>7.993280455908298</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.648499679266344</v>
+        <v>4.869540555870678</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.098179009595107</v>
+        <v>5.317531802826025</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.324343598825678</v>
+        <v>4.544616126789535</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.415029396553258</v>
+        <v>5.631683899032765</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>5.952262023690594</v>
+        <v>6.165942625666077</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.460423866427938</v>
+        <v>6.668796818972559</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>7.055393586005827</v>
+        <v>7.260726072607255</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>6.396462346968526</v>
+        <v>6.602582775026697</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>6.175195865977663</v>
+        <v>6.383961566888402</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.851406621477459</v>
+        <v>3.811020039667021</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>5.385767467677255</v>
+        <v>5.332195596008432</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>4.782218499461528</v>
+        <v>4.735078846851472</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>4.969262295081961</v>
+        <v>4.921924656819499</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>3.196553689362702</v>
+        <v>3.417042334879682</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>5.169778961588939</v>
+        <v>5.382012700001191</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>5.444554128071069</v>
+        <v>5.656487412483244</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>6.188284919950142</v>
+        <v>6.396981689872213</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.02853</t>
+          <t>X &lt; -0.0285</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>20.78070725468534</v>
+        <v>20.66255845932346</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>14.52652862477621</v>
+        <v>14.44542871979716</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>14.64446055944397</v>
+        <v>14.24579976364544</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.19234948924147</v>
+        <v>9.817675465564918</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>8.580973785214297</v>
+        <v>8.444444845333848</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>7.522032479217977</v>
+        <v>7.38917500658652</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.191533948410054</v>
+        <v>5.064431291640261</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.043820424386823</v>
+        <v>2.922865809620113</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.019915928661788</v>
+        <v>3.896030010168353</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.999974598889246</v>
+        <v>1.880878309287141</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.520439785007696</v>
+        <v>3.397173976293786</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.929819401782019</v>
+        <v>2.807865566634618</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.362960582048764</v>
+        <v>3.237498530834394</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.14160377101441</v>
+        <v>3.016419654387803</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.859619572475552</v>
+        <v>1.737158344384888</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>2.143153142346158</v>
+        <v>2.0209862601167</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.2981835424569681</v>
+        <v>-0.5974029265502168</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.096833041447752</v>
+        <v>1.782228419318045</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.4379562043795673</v>
+        <v>0.1347657629752845</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.5625</v>
+        <v>1.253288591576847</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.7067995910020386</v>
+        <v>0.5878732840817875</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.880844535359437</v>
+        <v>1.7581332416758</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>1.530619701841573</v>
+        <v>1.409554994656297</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>3.017178362573105</v>
+        <v>2.89135514018691</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.02318</t>
+          <t>X &lt; -0.02315</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>21.01570489697873</v>
+        <v>21.17396770138284</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>14.72519439474136</v>
+        <v>14.66635139686019</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>14.77432767755347</v>
+        <v>14.70981382931068</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>11.57914478619654</v>
+        <v>11.52772400739882</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>9.476902296457865</v>
+        <v>9.626721458088312</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>8.175233162566386</v>
+        <v>8.328539129334203</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.913533283614093</v>
+        <v>6.071441930592364</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.649866975564514</v>
+        <v>3.813032466037306</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.683938871852661</v>
+        <v>4.844618657852998</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.421269714184973</v>
+        <v>2.586554466965019</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.936323770382188</v>
+        <v>3.850713119027937</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.664674035641774</v>
+        <v>2.581864705678946</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>3.773433437502028</v>
+        <v>3.933950163575311</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3.552076626467674</v>
+        <v>3.46534653465347</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>2.39686747179762</v>
+        <v>2.312153732122418</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>2.743788563602628</v>
+        <v>2.659015901590159</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.5258214326674135</v>
+        <v>0.2973759923354535</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.157156424532324</v>
+        <v>2.915307565741998</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.378254711842253</v>
+        <v>2.141099936765336</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>3.560323383084572</v>
+        <v>3.31804475663435</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>2.270854317370201</v>
+        <v>2.186475666524991</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>3.438680356254963</v>
+        <v>3.351324494197776</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>3.464699303831615</v>
+        <v>3.37766024886345</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>3.637514183468625</v>
+        <v>3.549966953456554</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.01783</t>
+          <t>X &lt; -0.0178</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>20.47682199047561</v>
+        <v>20.70372217495756</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>13.72655213620865</v>
+        <v>13.62737234289986</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>11.90949318155647</v>
+        <v>11.81482145866288</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>9.497586660816147</v>
+        <v>9.416474180793173</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>7.622882913527945</v>
+        <v>7.702715736690649</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.055330545402661</v>
+        <v>7.139212879636055</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.339068186933538</v>
+        <v>5.429177891805736</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.422428154248024</v>
+        <v>4.400497403900694</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4.842016052919057</v>
+        <v>4.817219107391381</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.31203697485283</v>
+        <v>3.293834388202924</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.531575826089146</v>
+        <v>4.505980334304816</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.87441008896586</v>
+        <v>3.968375537213234</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.018349872369079</v>
+        <v>5.10085256810148</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.418921227686326</v>
+        <v>4.503833842030829</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>4.705169572770011</v>
+        <v>4.785540168510416</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>4.544085955094609</v>
+        <v>4.628047391205286</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>2.826816457543032</v>
+        <v>2.802400930919546</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>4.994560314175018</v>
+        <v>4.953199324842714</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.88492590134927</v>
+        <v>3.853301232082842</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>4.450757575757578</v>
+        <v>4.228116966862892</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>3.649162019844546</v>
+        <v>3.428572370622796</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>4.71172688830061</v>
+        <v>4.482669912038538</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>5.55576201683207</v>
+        <v>5.322116375933035</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>5.859327318929836</v>
+        <v>5.622931956984708</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.01247</t>
+          <t>X &lt; -0.01245</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>17.69842761385705</v>
+        <v>17.7690745575863</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>11.35018020378788</v>
+        <v>11.29852752424955</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9.910479739701742</v>
+        <v>9.860508475218559</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>8.412372701018391</v>
+        <v>8.364264638543446</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>6.47847546501395</v>
+        <v>6.544148494909628</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>6.665640078020736</v>
+        <v>6.731114681007007</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>5.239179174724882</v>
+        <v>5.305571225874829</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.780458221845684</v>
+        <v>4.765921872625022</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.952864339224341</v>
+        <v>4.938128008788091</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.048138876098889</v>
+        <v>4.034493378503235</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>4.715168300282286</v>
+        <v>4.700709883410255</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.780196867352835</v>
+        <v>4.765525480133356</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6.014814429992818</v>
+        <v>5.998384355685623</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.055580816861486</v>
+        <v>6.039085583951064</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>5.658772775727194</v>
+        <v>5.642722391082565</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>5.33640163268803</v>
+        <v>5.405794511299106</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>4.500044803999728</v>
+        <v>4.485507780612579</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>5.444930154308651</v>
+        <v>5.42915986840346</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.742418146636787</v>
+        <v>4.727620056667241</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>4.535761154855642</v>
+        <v>4.521281069780734</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>4.207949393892982</v>
+        <v>4.193730963086871</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>4.526212472284534</v>
+        <v>4.511585789079341</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>5.326611817478884</v>
+        <v>5.310994884763488</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>5.250670478210417</v>
+        <v>5.235162631540213</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.007121</t>
+          <t>X &lt; -0.007097</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>15.16835030878359</v>
+        <v>15.19595844212359</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>8.740920660109666</v>
+        <v>8.697987199329333</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>7.214187994108819</v>
+        <v>7.086357039187227</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.281943854109748</v>
+        <v>5.158125241966708</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.394480857597443</v>
+        <v>4.354293694026055</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.929774278263061</v>
+        <v>4.888783772391037</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.7217471366355</v>
+        <v>3.682430223166193</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.583293108833296</v>
+        <v>3.491099751480007</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.363485132044076</v>
+        <v>3.27194401419402</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.938081777023783</v>
+        <v>2.846552230425118</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.299549058076394</v>
+        <v>3.207492845653945</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.858423616488139</v>
+        <v>3.764387305765048</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.216059686579896</v>
+        <v>4.119486108474149</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4.169070791848938</v>
+        <v>4.072320275505817</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>3.565675582000772</v>
+        <v>3.414176977925258</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>3.98621556181412</v>
+        <v>3.889746024210773</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.47092126103648</v>
+        <v>3.320667877659766</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>4.501309023980511</v>
+        <v>4.347245798729801</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.407388518790043</v>
+        <v>3.312314619209189</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>3.507096069869</v>
+        <v>3.412052415239927</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>2.931449940652399</v>
+        <v>2.837002123503062</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.942907472422377</v>
+        <v>2.848340120245666</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>3.742158163380026</v>
+        <v>3.645918581637908</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.966916124810858</v>
+        <v>2.872614663201034</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001769</t>
+          <t>X &lt; -0.001747</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1683</v>
+        <v>1690</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>11.77183252218778</v>
+        <v>11.85004059967797</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>6.356916901223308</v>
+        <v>6.318493735277038</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>6.157618091006043</v>
+        <v>6.174592333304872</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.771015448897685</v>
+        <v>4.755755960920951</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.79659948181957</v>
+        <v>4.750090475390266</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4.15585161700259</v>
+        <v>4.171900687385232</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.442122090507404</v>
+        <v>3.399952003494882</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.3769141219665</v>
+        <v>3.334018133508643</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.099169814442796</v>
+        <v>3.057685397644242</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.798987452814877</v>
+        <v>2.756189874819306</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.813230383109016</v>
+        <v>2.735611921224013</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.103587284085215</v>
+        <v>3.023206009620658</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.690417938745668</v>
+        <v>2.644046836959461</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.268553583100754</v>
+        <v>2.186979759922906</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2.595820428480074</v>
+        <v>2.509705954877155</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>2.775450211039136</v>
+        <v>2.727585960013606</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.262683440915957</v>
+        <v>2.180201605079844</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>3.048436366863427</v>
+        <v>2.998400981466553</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.779998959723983</v>
+        <v>1.772959929387895</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.967042755344416</v>
+        <v>1.959805739355922</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.757378913640189</v>
+        <v>1.749369348525377</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.800259270950647</v>
+        <v>1.791866582382539</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>2.312705263338898</v>
+        <v>2.30302768539714</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.76142227225818</v>
+        <v>1.753822651108784</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.003584</t>
+          <t>X &lt; 0.003604</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>8.842916304380964</v>
+        <v>8.881838911976381</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.327368231808428</v>
+        <v>5.352564921627206</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.614610066677301</v>
+        <v>4.640828214856768</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.655391120507396</v>
+        <v>3.655518317066324</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.089947702840419</v>
+        <v>3.074397288341622</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.913310587788999</v>
+        <v>2.943470649734188</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.576865841748379</v>
+        <v>2.580241311892884</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.370996962203193</v>
+        <v>2.329121012647526</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.802204882239245</v>
+        <v>1.761360332020416</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.802504261998045</v>
+        <v>1.761171928711192</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.92193284130245</v>
+        <v>1.880533154237462</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.852397830064199</v>
+        <v>1.856407719579977</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.211254431211991</v>
+        <v>1.21568448174996</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.926241195122472</v>
+        <v>0.9035723781754683</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.298985656611883</v>
+        <v>1.274713922567685</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.419814261280997</v>
+        <v>1.395906674949956</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.176519518301376</v>
+        <v>1.152994826780436</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.556385143824357</v>
+        <v>1.531855267023751</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.5385046504490347</v>
+        <v>0.5439329207936652</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.3142138939671</v>
+        <v>0.3474088066860901</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.1641041177510232</v>
+        <v>0.1973983128873158</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.003300412057114954</v>
+        <v>0.0576170669192706</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.8021201592981129</v>
+        <v>0.8346043422153997</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.314467932563943</v>
+        <v>0.3476254466896904</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.008936</t>
+          <t>X &lt; 0.008955</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2557</v>
+        <v>2560</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>6.644572725613372</v>
+        <v>6.685239843089775</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>4.055219208637141</v>
+        <v>4.082628515402682</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.859203159630674</v>
+        <v>3.887327912973632</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.896307280552641</v>
+        <v>2.902529233336715</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.359531893808729</v>
+        <v>2.356571366156032</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.235533535209143</v>
+        <v>2.25547651798172</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.991296364013053</v>
+        <v>1.988774627717497</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.735748747831096</v>
+        <v>1.733516582878224</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.64452652056211</v>
+        <v>1.642393534523862</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.53268487926308</v>
+        <v>1.530699173150929</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.986108159184141</v>
+        <v>1.983586717671848</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.847246673825005</v>
+        <v>1.84487878443209</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.136001699900511</v>
+        <v>1.134452924131736</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.094204118018951</v>
+        <v>1.069137287560544</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1.278257437224688</v>
+        <v>1.252628223669738</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.741159956531924</v>
+        <v>1.715026335057516</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.396711029975677</v>
+        <v>1.371044762721276</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.784333041447752</v>
+        <v>1.758003847850709</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.180143704379567</v>
+        <v>1.178525138512974</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.8203125</v>
+        <v>0.8426040041281908</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.8868015448902824</v>
+        <v>0.9092528075107538</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.7173378895423923</v>
+        <v>0.7399527510216046</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.133181297461434</v>
+        <v>1.131614963503651</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.8616983078214346</v>
+        <v>0.8604702102803756</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.01429</t>
+          <t>X &lt; 0.01431</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2771</v>
+        <v>2775</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>5.062871776882858</v>
+        <v>5.098407900894685</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.292461242504054</v>
+        <v>3.31566953142854</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.929187043218768</v>
+        <v>2.952534036679161</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.092772834271024</v>
+        <v>2.081288324403985</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.748420666314104</v>
+        <v>1.76636837365831</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.432892281116224</v>
+        <v>1.472067972892873</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.075893170668088</v>
+        <v>1.094667352130209</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.033842174151474</v>
+        <v>1.052603032351193</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.096359734077559</v>
+        <v>1.115044336458183</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.113322310367806</v>
+        <v>1.131791259129528</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.337065956592582</v>
+        <v>1.355290327197586</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.438974694370387</v>
+        <v>1.456978510162841</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.9476494871548198</v>
+        <v>0.9660545597856824</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.8199577269970035</v>
+        <v>0.8168405773383753</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.7949102389088907</v>
+        <v>0.7914157489064095</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.195780468694842</v>
+        <v>1.191935536595729</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.9754651061916846</v>
+        <v>0.9719254616708852</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.324933257741911</v>
+        <v>1.320692364747266</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.8561249138244094</v>
+        <v>0.874607196778598</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.5745313626532109</v>
+        <v>0.6150601981857093</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.6299423966277189</v>
+        <v>0.6704682009033149</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.5036800331949323</v>
+        <v>0.5443587194900701</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.6559354723215449</v>
+        <v>0.6746892878279667</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.3273777490761631</v>
+        <v>0.3466047823524434</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.01964</t>
+          <t>X &lt; 0.01966</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2919</v>
+        <v>2922</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.921246441660657</v>
+        <v>3.94418690017347</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.870812071430493</v>
+        <v>2.880449582604072</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.623209699987406</v>
+        <v>2.633311785699654</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.861059387504454</v>
+        <v>1.872041549356467</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.515565965835961</v>
+        <v>1.521950306815867</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.17700389164483</v>
+        <v>1.183706798689684</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.9694576435476137</v>
+        <v>0.9567172428647268</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.7107198590475647</v>
+        <v>0.6982686898300372</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.7038069262907882</v>
+        <v>0.691365909265258</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.817343529173236</v>
+        <v>0.8246812117908817</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.111826380966683</v>
+        <v>1.118823286115585</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.091940846039208</v>
+        <v>1.098996357431638</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.7393052173967547</v>
+        <v>0.7468788967216611</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.6068045810258553</v>
+        <v>0.5940594059405981</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.5154227516432215</v>
+        <v>0.5026624381654372</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.7892275251529739</v>
+        <v>0.7762046696472851</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.6757730090312322</v>
+        <v>0.6628703483990108</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.002120515780405</v>
+        <v>0.9887427288071819</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.7391197909640965</v>
+        <v>0.7467528097449474</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.5839322381930216</v>
+        <v>0.6122030370314775</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.4720768932957853</v>
+        <v>0.5006927639188987</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.5537897408388872</v>
+        <v>0.5823926466410398</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.4724662246233464</v>
+        <v>0.4804128758924264</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.2252333471568591</v>
+        <v>0.2334649484733973</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.02499</t>
+          <t>X &lt; 0.02501</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3021</v>
+        <v>3024</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.857632460652624</v>
+        <v>2.868028626213004</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.178984843923502</v>
+        <v>2.190111043824928</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.02302368200985</v>
+        <v>2.034564865560128</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.328154313850114</v>
+        <v>1.340508282902377</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.9818209402264415</v>
+        <v>0.9907221227154679</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.8254962225653202</v>
+        <v>0.8345194837883412</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.8295471610756522</v>
+        <v>0.8196478242561227</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4052435241831489</v>
+        <v>0.3958542319149174</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.5317851697372546</v>
+        <v>0.522229897237807</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.582488017543028</v>
+        <v>0.5920840149774804</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.942201004226348</v>
+        <v>0.9513938528890549</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.847527060398356</v>
+        <v>0.8568628286366504</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.6669040814918503</v>
+        <v>0.6766158549465544</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4983612618476343</v>
+        <v>0.4885185088429722</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.4538910667220435</v>
+        <v>0.4439992492376419</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.6063166288895729</v>
+        <v>0.5963096309631055</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.5912792674603864</v>
+        <v>0.5812653915097741</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.8038436234583344</v>
+        <v>0.7935266954488895</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.6562101726335356</v>
+        <v>0.666009414829098</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.5125661375661394</v>
+        <v>0.5422665178719441</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.4853722009921242</v>
+        <v>0.5153725760670653</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.4955864281456641</v>
+        <v>0.5256257007570539</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.4593684605307402</v>
+        <v>0.4694125825512643</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.2510206333443676</v>
+        <v>0.261305197052863</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.03035</t>
+          <t>X &lt; 0.03036</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3097</v>
+        <v>3101</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.070422881797342</v>
+        <v>2.064281091696238</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.464218328401024</v>
+        <v>1.45881020171614</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.56544884344811</v>
+        <v>1.57801836054707</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.9663037146569877</v>
+        <v>0.9795948708834104</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.7800024790747457</v>
+        <v>0.7905008655540797</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.5678444902054878</v>
+        <v>0.5785113175642564</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.7454472557277683</v>
+        <v>0.7375417669002289</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.131799108362749</v>
+        <v>0.1246433959164222</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.3204763556805332</v>
+        <v>0.3130789314421918</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.2220992916463871</v>
+        <v>0.2334785424059902</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5795817039627025</v>
+        <v>0.5905630924534435</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.4480352283699602</v>
+        <v>0.4592006707867213</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.4370589505968354</v>
+        <v>0.4484608941594672</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.2671323878067469</v>
+        <v>0.2595467008907448</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.2395614422767594</v>
+        <v>0.2319264043703342</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.3062211410570868</v>
+        <v>0.2985682378987775</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.2558944717274301</v>
+        <v>0.2482854425850576</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.5572087267105701</v>
+        <v>0.5491941428054972</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.4186076071528646</v>
+        <v>0.4301169827998308</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.2509271202837837</v>
+        <v>0.2817783520370796</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.2108318490665653</v>
+        <v>0.2420005580141975</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.2510849354885138</v>
+        <v>0.2822752881064048</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.1902388109442157</v>
+        <v>0.2020257180989447</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.02780468553797988</v>
+        <v>-0.03504484534684593</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.0357</t>
+          <t>X &lt; 0.03571</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3159</v>
+        <v>3163</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.612222206584001</v>
+        <v>1.607424413909328</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.105591338969056</v>
+        <v>1.101395893310958</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.145273940668254</v>
+        <v>1.158684083212385</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.7011891511920822</v>
+        <v>0.7151771625566923</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.7002859739944469</v>
+        <v>0.7119360210801631</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.4643971359793966</v>
+        <v>0.4762312356553053</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5918793471354817</v>
+        <v>0.5856171441477116</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.1108359378555335</v>
+        <v>0.1051490832405833</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.23355766436827</v>
+        <v>0.2277168101879212</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1850454954783771</v>
+        <v>0.197558478519305</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.5093447252083791</v>
+        <v>0.5214934967820639</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.3748893895627887</v>
+        <v>0.3872284703025812</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.2789664349705205</v>
+        <v>0.2916441165089196</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.07640748572423206</v>
+        <v>0.07056524006232934</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.06799792266438232</v>
+        <v>0.06209907365971645</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.1765499621184929</v>
+        <v>0.1705680981477755</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.0929352944583286</v>
+        <v>0.08704245898211838</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.386233926683289</v>
+        <v>0.3799569356363648</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.3178170959382101</v>
+        <v>0.3305572274091233</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.1570897881757816</v>
+        <v>0.1887531544883529</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.1071000337597923</v>
+        <v>0.1390939873990931</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.1450409921769023</v>
+        <v>0.1770600265511604</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>0.154037423360549</v>
+        <v>0.1669947453563196</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>0.002082604421779877</v>
+        <v>-0.003684172425920451</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.04105</t>
+          <t>X &lt; 0.04106</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3210</v>
+        <v>3214</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.358396401619913</v>
+        <v>1.354513232995501</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.7924378999270587</v>
+        <v>0.7892275733667304</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.7777684147752453</v>
+        <v>0.7918661694874416</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.5152384315477647</v>
+        <v>0.5297497689704898</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.5085173226332174</v>
+        <v>0.5211987968100971</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.4032901768199437</v>
+        <v>0.4160285474209857</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.4854935813808439</v>
+        <v>0.4805110902964316</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.1007022792017551</v>
+        <v>0.09617255568927874</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.3152453519607263</v>
+        <v>0.3104501139062279</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.2552522751453594</v>
+        <v>0.2685715058782137</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.6098288313846254</v>
+        <v>0.6227569487210829</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.4731138426790622</v>
+        <v>0.4862370541765983</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.3298598048294039</v>
+        <v>0.3433816095131945</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1891691596286975</v>
+        <v>0.1843759794973963</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.2015666081321186</v>
+        <v>0.1967046833367618</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.3800643805476724</v>
+        <v>0.3750235271974418</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.1712954622086613</v>
+        <v>0.1665008358543005</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.3960707514664179</v>
+        <v>0.3909858358685767</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.3632829000858493</v>
+        <v>0.3768801514047695</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.1769601742377063</v>
+        <v>0.2092077535310608</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.1502714241797634</v>
+        <v>0.1828404114975726</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.1552841368538296</v>
+        <v>0.187900207462171</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.2307909880452428</v>
+        <v>0.2445777824208903</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.1735257145980214</v>
+        <v>0.168745529197615</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.0464</t>
+          <t>X &lt; 0.04641</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3245</v>
+        <v>3249</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.166564868759011</v>
+        <v>1.163314453275497</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.7562562515325482</v>
+        <v>0.7534853627820439</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.6343614877222308</v>
+        <v>0.6488187660702636</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3669456603881258</v>
+        <v>0.3818256843693035</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3563308083165566</v>
+        <v>0.3697203903344715</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.254196154848195</v>
+        <v>0.2676372683850019</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.3578550587022846</v>
+        <v>0.3537946218835515</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.03555321154482272</v>
+        <v>0.03186802218642271</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.3096231205523523</v>
+        <v>0.30560219870938</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3033652351129774</v>
+        <v>0.3172232393637344</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.5035316279126292</v>
+        <v>0.5171418054682348</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3959749927491885</v>
+        <v>0.4097552295379643</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.2728744766658977</v>
+        <v>0.2870449449601011</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.06981669309066518</v>
+        <v>0.06596606851351083</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.136452808097637</v>
+        <v>0.1324763049202389</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.257895694601828</v>
+        <v>0.2538053344504974</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.08066261138918662</v>
+        <v>0.07677925534154184</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.2710789632698578</v>
+        <v>0.2669525058277671</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.2409725170911656</v>
+        <v>0.2552840489034836</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.05867189904586212</v>
+        <v>0.09139096237150568</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.02638087179022364</v>
+        <v>0.05942852012300648</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.06128032223963231</v>
+        <v>0.09435747170488895</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.1389068244540042</v>
+        <v>0.1533812762152493</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.08141179862857228</v>
+        <v>0.07754902299197397</v>
       </c>
     </row>
     <row r="29">
@@ -7714,79 +7714,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3270</v>
+        <v>3274</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.9625462743951516</v>
+        <v>0.9598209703821823</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.7352286270501338</v>
+        <v>0.7327600493360791</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.6641413016501332</v>
+        <v>0.6787301780507988</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3933395122434362</v>
+        <v>0.40835742703932</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.3191701928949655</v>
+        <v>0.332991081706183</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.3105500968227801</v>
+        <v>0.3243354242921654</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.4380041371093455</v>
+        <v>0.4343818742217564</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.1160598376580637</v>
+        <v>0.1128122766925443</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.327444390336062</v>
+        <v>0.3239398705585685</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.2848704055264193</v>
+        <v>0.2991544940910273</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.4551179708430766</v>
+        <v>0.4691812995853368</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.3462391267269282</v>
+        <v>0.3604751893285894</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.2764827694035858</v>
+        <v>0.2910675937826781</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.0427801208516172</v>
+        <v>0.03951949125442411</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.1038726837001107</v>
+        <v>0.1005000766623851</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.1678698586516632</v>
+        <v>0.1644493717664446</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.0214729460926435</v>
+        <v>0.01822181891263597</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.2401592479230104</v>
+        <v>0.2366336580827735</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.2119329911846961</v>
+        <v>0.2266919869682198</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.06299633475870081</v>
+        <v>0.09599178210613246</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.05735718342490514</v>
+        <v>0.09066751014061936</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.09141910748657978</v>
+        <v>0.1247601349556291</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.1705616156294028</v>
+        <v>0.1854291052263122</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.1129352433070423</v>
+        <v>0.1095968520030368</v>
       </c>
     </row>
     <row r="30">
@@ -7796,79 +7796,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3284</v>
+        <v>3288</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.8658301680990803</v>
+        <v>0.8633850510178505</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.7590954501770852</v>
+        <v>0.7567619364190037</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.5606907777954575</v>
+        <v>0.5754677469912153</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3181299564745856</v>
+        <v>0.3333122481862389</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.2729089205126769</v>
+        <v>0.287007220320703</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2651647363689236</v>
+        <v>0.2792260236367028</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2975747669720832</v>
+        <v>0.2944405247297013</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.09707086031608014</v>
+        <v>0.09416421337314773</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.2166850107216618</v>
+        <v>0.2136337477897428</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1707840858485099</v>
+        <v>0.1854143529536216</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.3111310410945691</v>
+        <v>0.3255674853375581</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2014336194912829</v>
+        <v>0.2160444365689642</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1875467738787222</v>
+        <v>0.2024600900911651</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1068615377260116</v>
+        <v>-0.1096105970924697</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.07947189063902727</v>
+        <v>-0.08228777513510011</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.01727599793929357</v>
+        <v>0.0143697981330746</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.1291105941287043</v>
+        <v>-0.1318472578584107</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.05764939900323185</v>
+        <v>0.05467910994167369</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.06094191432180196</v>
+        <v>0.07608784624887477</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.09884428223843855</v>
+        <v>-0.08359668371752349</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.07639937462010238</v>
+        <v>-0.06102974501610703</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.07327901911408929</v>
+        <v>-0.05788901319244388</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.006647099101840581</v>
+        <v>0.003755051676350263</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.05110726471070137</v>
+        <v>-0.05393444300430161</v>
       </c>
     </row>
     <row r="31">
@@ -7878,79 +7878,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3296</v>
+        <v>3300</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.7123724139658094</v>
+        <v>0.7102519531142519</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.6046958419691677</v>
+        <v>0.602689341230267</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.4014248109348983</v>
+        <v>0.4164263371685522</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.2172998000631381</v>
+        <v>0.2326555815286966</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.2009678818157141</v>
+        <v>0.2153333792743979</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.254335038850428</v>
+        <v>0.2686076838374163</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.2533877567083991</v>
+        <v>0.2505793859543033</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.0525640534303875</v>
+        <v>0.04998421551088938</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1718580280302717</v>
+        <v>0.1691345131802251</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1533096263242868</v>
+        <v>0.1681636692375008</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.263957181629209</v>
+        <v>0.2786439555898497</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1535797938458145</v>
+        <v>0.1684423003154834</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.135312630521419</v>
+        <v>0.1504857144113529</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1588242245303633</v>
+        <v>-0.1612276031228461</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.136613356735154</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.06572423087462909</v>
+        <v>-0.06824594188559985</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.2120875690994097</v>
+        <v>-0.2144396282952528</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.02650130137477902</v>
+        <v>-0.02908396960028625</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.004334010706770641</v>
+        <v>-0.006935592960097381</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.1325757575757578</v>
+        <v>-0.135015440426514</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.2031352377339388</v>
+        <v>-0.2055147715232835</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.1700196247375914</v>
+        <v>-0.1724440918009336</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.1197442654013798</v>
+        <v>-0.1222191019310657</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.1776031908249607</v>
+        <v>-0.1800127442650776</v>
       </c>
     </row>
     <row r="32">
@@ -7960,325 +7960,325 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3316</v>
+        <v>3320</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.5662142250553188</v>
+        <v>0.5644806327518097</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.4571299381180722</v>
+        <v>0.4555138127691123</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2764222797873259</v>
+        <v>0.2916580275070899</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1490533802865954</v>
+        <v>0.1645953504814557</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1606017848480192</v>
+        <v>0.1753110788124346</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2147596958648705</v>
+        <v>0.229374896364142</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1791551651210384</v>
+        <v>0.176850672905438</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.03788449353428547</v>
+        <v>0.03573794498099403</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.1867369552959133</v>
+        <v>0.1844120853061213</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.103592235217171</v>
+        <v>0.1188076922875538</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.1851693540081527</v>
+        <v>0.200243030002234</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.07375437062937351</v>
+        <v>0.08900584308899795</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.04881323479928312</v>
+        <v>0.0643875316364344</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2148458386876726</v>
+        <v>-0.2167514048702159</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1943002738692741</v>
+        <v>-0.1962557150103379</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.1227240239999858</v>
+        <v>-0.1247450466200419</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.2389373793513343</v>
+        <v>-0.2408248070050689</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.08521090798030428</v>
+        <v>-0.08728824404943936</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.06189323855930695</v>
+        <v>-0.06399200099986757</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.1581325301204828</v>
+        <v>-0.1601099180388843</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.2315478027912619</v>
+        <v>-0.2334578892846153</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.1990982012288782</v>
+        <v>-0.2010513504233202</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.1474779767836978</v>
+        <v>-0.1494844794352232</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.2054543274148344</v>
+        <v>-0.2073950005629897</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.07317</t>
+          <t>X &lt; 0.07316</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3327</v>
+        <v>3331</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.5373481282993851</v>
+        <v>0.5357638650883203</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.4573896646063673</v>
+        <v>0.4558890694178572</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.2725442946343648</v>
+        <v>0.2878495765006619</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.2030192246208529</v>
+        <v>0.2185806847191074</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.2133445995137961</v>
+        <v>0.2281740764684201</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.2081471925092728</v>
+        <v>0.2229354706713451</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1402015040873792</v>
+        <v>0.1381693383196847</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.001532685564690439</v>
+        <v>-0.003405663131260894</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.08709226421152039</v>
+        <v>0.08511355936108345</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.001673495166137684</v>
+        <v>0.01715278995521174</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1137951303917006</v>
+        <v>0.1291047930741982</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.03175545628376142</v>
+        <v>0.04721716552098343</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.003178295940905684</v>
+        <v>0.0189694706541772</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2004209363868767</v>
+        <v>-0.2021094057924131</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.2120875478095172</v>
+        <v>-0.2137844904423574</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1387899982330794</v>
+        <v>-0.1405565084810334</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.2550671657323207</v>
+        <v>-0.2566997867223719</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1322023620926061</v>
+        <v>-0.1339867253892422</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.1082622830153923</v>
+        <v>-0.1100694247751406</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.2035800060042021</v>
+        <v>-0.2052678444908338</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.2485307393282881</v>
+        <v>-0.2501834036460906</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.2164444403089405</v>
+        <v>-0.2181391519186917</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.1941399135430473</v>
+        <v>-0.1958535238913086</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2221325782143992</v>
+        <v>-0.2238161339105602</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.07852</t>
+          <t>X &lt; 0.07851</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3339</v>
+        <v>3343</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.3871698766056397</v>
+        <v>0.3858988003867552</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.335941174842965</v>
+        <v>0.3347209158044251</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.2057645202806455</v>
+        <v>0.2212068756427712</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1337261228078717</v>
+        <v>0.1494291946403834</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1425768013992155</v>
+        <v>0.1576661026866475</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1083147350149005</v>
+        <v>0.1233882571041178</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1270008111267629</v>
+        <v>0.1252490970232856</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.01526746693640035</v>
+        <v>-0.01685856117199336</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.04335564912390311</v>
+        <v>0.04169494678028229</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.02740962856130835</v>
+        <v>-0.02900869793054994</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.05545119773195495</v>
+        <v>0.05376012217878667</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.002530295726366205</v>
+        <v>0.0008934938036659901</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.00013050457419439</v>
+        <v>-0.001796720594327894</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2336540127290903</v>
+        <v>-0.2350488553179773</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2177819170453148</v>
+        <v>-0.2192151565564231</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.1426153935724628</v>
+        <v>-0.1441225143105171</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.2888440325944401</v>
+        <v>-0.2901812708535445</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.196702085607555</v>
+        <v>-0.1981532279336591</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.172091642510388</v>
+        <v>-0.1735670138006924</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.266414896799283</v>
+        <v>-0.2677731917574349</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.3131734790159157</v>
+        <v>-0.3144921199064186</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.2814945846645074</v>
+        <v>-0.2828541435972411</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.2583024538470653</v>
+        <v>-0.2596828833863043</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.2864866568938069</v>
+        <v>-0.2878364192440017</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.08387</t>
+          <t>X &lt; 0.08386</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.2541323742669945</v>
+        <v>0.2531416339769734</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.2315097225467539</v>
+        <v>0.2305372256589777</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.03736085988410309</v>
+        <v>0.05302370585388871</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.05198236669817646</v>
+        <v>0.06783099840482976</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1484973808030219</v>
+        <v>0.1637613761328751</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1150257687767109</v>
+        <v>0.1302726834725263</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.01212873459633812</v>
+        <v>0.01075579080401212</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.07125932620694186</v>
+        <v>-0.07254075458941145</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.04242268562843776</v>
+        <v>-0.04373813034807483</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1157206884048136</v>
+        <v>-0.1169683341129542</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.03220300413591559</v>
+        <v>-0.03354407153673122</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.08595701057787863</v>
+        <v>-0.08724167629872426</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.09264828450262996</v>
+        <v>-0.09395262670371807</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.2964028302696917</v>
+        <v>-0.29747105468347</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.2829594217389513</v>
+        <v>-0.2840601104271201</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.2059549867421069</v>
+        <v>-0.2071337820668759</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3223794924271886</v>
+        <v>-0.3234237437952032</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2607406850938077</v>
+        <v>-0.2618615346848543</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2354645345954083</v>
+        <v>-0.2366110486189186</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.298994038748134</v>
+        <v>-0.3000611742326242</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.3773536588488753</v>
+        <v>-0.3783412146092004</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.3460791151028388</v>
+        <v>-0.3471064722432189</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.3220055964877844</v>
+        <v>-0.3230557754713246</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.3503798290115085</v>
+        <v>-0.3513987353232082</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/vix/vix_ret_1.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/vix/vix_ret_1.xlsx
@@ -618,2379 +618,2379 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.06862</t>
+          <t>X ≈ -0.06892</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>29.49594941078978</v>
+        <v>28.08112471375525</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>29.17366213525682</v>
+        <v>27.84696379078922</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>19.46807640351108</v>
+        <v>26.60718482800187</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.47921191328977</v>
+        <v>16.98941479806048</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.14923651298965</v>
+        <v>16.72150869447049</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>18.62960012797622</v>
+        <v>25.92510898009768</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.573184853649799</v>
+        <v>16.09639043426067</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.003267320005008</v>
+        <v>6.750081679395869</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.253828246942582</v>
+        <v>-2.171295370000259</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.274981618154392</v>
+        <v>6.088403918222646</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.851989174516198</v>
+        <v>6.361730282234589</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.576808266820123</v>
+        <v>6.088028231961012</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.459529243473902</v>
+        <v>4.978541494996982</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.55223653908128</v>
+        <v>13.79651564024913</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>23.21362986328342</v>
+        <v>22.18681391540076</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>7.181846029168469</v>
+        <v>4.614619012040841</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>15.36884055723847</v>
+        <v>13.58450683469803</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>6.947766743236457</v>
+        <v>4.381039977031058</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>7.165481248754425</v>
+        <v>4.596484942138495</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>15.68014462086121</v>
+        <v>13.89227127916162</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>15.13802565619903</v>
+        <v>13.3294318322034</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>23.395144175955</v>
+        <v>22.34383487474391</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>15.34574031066471</v>
+        <v>13.50585299119013</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>4.256833337726349</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.06327</t>
+          <t>X ≈ -0.06356</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>13</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.84265689971312</v>
+        <v>7.938143325776316</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.51400106122437</v>
+        <v>7.698099381639167</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>13.73240611174408</v>
+        <v>6.45245644815914</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.379646514288474</v>
+        <v>-1.780509979898262</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.048191368292954</v>
+        <v>-2.053926393570954</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.235725750303565</v>
+        <v>-1.898590148232692</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.469157395944372</v>
+        <v>-2.690091270997556</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.463823803392998</v>
+        <v>-10.64966082471241</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.423550448839784</v>
+        <v>-10.52547307043866</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-4.194758506862868</v>
+        <v>-11.3216250494276</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.92272682591242</v>
+        <v>-3.390854027437761</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.201704651779451</v>
+        <v>-3.667432924593648</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.346511288516567</v>
+        <v>2.887381755375799</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.126669408627102</v>
+        <v>2.64067306118821</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-6.203295895188006</v>
+        <v>-5.710779448051994</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-5.61188660013827</v>
+        <v>-5.152373444003587</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-5.747165535599251</v>
+        <v>-5.257489329744367</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-5.853603217814396</v>
+        <v>-5.391743411555346</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-5.639714684665094</v>
+        <v>-5.179200857188825</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-5.454767211220336</v>
+        <v>-4.96647521030696</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-5.996882971524556</v>
+        <v>-5.534899472633107</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-6.074441561592991</v>
+        <v>-5.611618500067593</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-5.80178995310699</v>
+        <v>-5.369666952068776</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>1.812994248741916</v>
+        <v>2.158931239824255</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.05793</t>
+          <t>X ≈ -0.0582</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>28.51933525501926</v>
+        <v>27.51429397485951</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.815730145599801</v>
+        <v>14.86197210646262</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.233908712703446</v>
+        <v>13.61854005617024</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.528715727090756</v>
+        <v>13.03464739849989</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>14.04881099332073</v>
+        <v>12.76566269988662</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>14.23905338299249</v>
+        <v>12.92540099099748</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.621157135387044</v>
+        <v>12.13834929801948</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.34709826853171</v>
+        <v>11.83913860428588</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>13.24821015670676</v>
+        <v>11.97000106954231</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.622668874099503</v>
+        <v>4.956663100131934</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>6.897935619274257</v>
+        <v>5.229533743835844</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.622211045448026</v>
+        <v>4.95552812322866</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.3603147095944905</v>
+        <v>-2.383791428463987</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>5.285456167298634</v>
+        <v>3.599270804013209</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-1.237778197691846</v>
+        <v>-3.313266571656492</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-6.51485056084357</v>
+        <v>-8.989225938071655</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-6.650413864466231</v>
+        <v>-9.095499576054543</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.8836495766925339</v>
+        <v>-2.992127383814534</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.6682808300278893</v>
+        <v>-2.778883679123609</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-6.358882454995907</v>
+        <v>-8.807975400874355</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-12.77802547160675</v>
+        <v>-15.62194588087874</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-6.978841143798306</v>
+        <v>-9.455441011625787</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-12.5870568819721</v>
+        <v>-15.46278345215024</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.9019378779535856</v>
+        <v>-3.129530298635864</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.05257</t>
+          <t>X ≈ -0.05285</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>23.97248269036424</v>
+        <v>26.27081871155483</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>29.16997555698391</v>
+        <v>21.06973204781761</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>27.74836102238806</v>
+        <v>24.79683404777878</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>16.00142844033402</v>
+        <v>14.27629808198265</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>21.19847781915207</v>
+        <v>23.95081901554575</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>21.3909135463679</v>
+        <v>24.11394043764839</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9.572071324270233</v>
+        <v>8.406792082280958</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.768266444982729</v>
+        <v>3.13051899915876</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>14.87469227993513</v>
+        <v>18.19129355214283</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.491975600815351</v>
+        <v>2.466940870669291</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.219452247192656</v>
+        <v>2.739070944105123</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.039168017674776</v>
+        <v>7.446327271007036</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>7.459102195325421</v>
+        <v>11.32085914962985</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.84009885482682</v>
+        <v>1.106665167309593</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-4.497807469971114</v>
+        <v>0.426683729897924</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-3.905868873142602</v>
+        <v>0.9869536083524224</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.504798335635513</v>
+        <v>5.873128097711437</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.400479621222274</v>
+        <v>5.742136226889329</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.616535193288271</v>
+        <v>5.957995157818132</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-9.297323454480157</v>
+        <v>-3.813882697336702</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-15.38990526767721</v>
+        <v>-9.377440904689649</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-4.366004531825105</v>
+        <v>0.538595449821635</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-9.646732888504559</v>
+        <v>-4.216123047609074</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-4.169911734166597</v>
+        <v>0.6204697013604346</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.04723</t>
+          <t>X ≈ -0.04749</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>18.23116902201024</v>
+        <v>17.16523885003716</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>25.85545943538875</v>
+        <v>25.20687429357213</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>28.40873574517233</v>
+        <v>28.10692838123258</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>15.77925844059585</v>
+        <v>15.10343291289652</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>11.47269905665654</v>
+        <v>10.69211944080548</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11.66224747371471</v>
+        <v>10.85131983764843</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6.917771052861809</v>
+        <v>5.919045073432393</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.643738087607218</v>
+        <v>5.618232031651836</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.703743923357521</v>
+        <v>1.599083019007054</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.91915474303444</v>
+        <v>4.956218408054518</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.194220774882517</v>
+        <v>5.229099815056479</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.931647810003867</v>
+        <v>0.8035003988429494</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.800267982399475</v>
+        <v>3.845321786985437</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>8.570323724994878</v>
+        <v>7.753107897315296</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>11.90664473581885</v>
+        <v>11.23048100192057</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>16.49501274193611</v>
+        <v>15.95058076986524</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>8.381034789819594</v>
+        <v>7.536096683887202</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>12.2727156729654</v>
+        <v>11.56472488182021</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>8.496981170587908</v>
+        <v>7.622015775047899</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>8.686288201218488</v>
+        <v>7.838694497033529</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>4.14790865591317</v>
+        <v>3.111297519325241</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>12.06842180337852</v>
+        <v>11.3653501022902</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>12.34657949069658</v>
+        <v>11.61242196097859</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>8.274532710281285</v>
+        <v>7.287136368030339</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.04187</t>
+          <t>X ≈ -0.04213</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>24.5639992209957</v>
+        <v>20.591170271809</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>13.50004244505911</v>
+        <v>9.003630659012018</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.015689299490582</v>
+        <v>2.080840160298727</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.6232798522465828</v>
+        <v>1.49476445679273</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.978207452847911</v>
+        <v>4.062953833510264</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.853756929766973</v>
+        <v>9.903070226049657</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10.46710459800222</v>
+        <v>14.80071442425201</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>10.1942441694689</v>
+        <v>11.65950304189647</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>15.6205494626553</v>
+        <v>14.63418183775156</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>12.16385775936182</v>
+        <v>13.8462127736925</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>15.13357554375644</v>
+        <v>14.12182282724838</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>9.473427553688026</v>
+        <v>11.00398009747299</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>13.74528792165774</v>
+        <v>12.74362263177735</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>10.83383765823615</v>
+        <v>9.651615202662562</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>10.1806246675339</v>
+        <v>11.8235229463254</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>10.77698674992835</v>
+        <v>15.23734495564443</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>2.553717254114119</v>
+        <v>9.436487325436978</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>7.846767098512018</v>
+        <v>12.15848709701525</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>5.365519901917303</v>
+        <v>9.523649338921487</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>5.553906393120201</v>
+        <v>9.740948679327758</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>2.31170128934027</v>
+        <v>6.322575762515868</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.4645088338169217</v>
+        <v>6.249316161929734</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>5.213578071028735</v>
+        <v>6.494880895183648</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2.436694872442537</v>
+        <v>6.334755415648424</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.03653</t>
+          <t>X ≈ -0.03677</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>55</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>26.16948314770446</v>
+        <v>27.12896804351251</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>25.84821854974366</v>
+        <v>28.69024714103156</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>20.81328232611629</v>
+        <v>21.17593646568164</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>20.1134363857557</v>
+        <v>20.5959601669167</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>19.78663632097246</v>
+        <v>16.71447557834701</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>14.5531951247284</v>
+        <v>9.643189937325538</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>13.79035964547038</v>
+        <v>8.856024553345691</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>9.899413376717888</v>
+        <v>8.55649568560392</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.512713439710197</v>
+        <v>5.066672095641714</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.555553051204548</v>
+        <v>4.275955955468348</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>11.26448709299289</v>
+        <v>11.79202347825205</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>18.23821968930945</v>
+        <v>16.9545753189572</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>15.31160118723295</v>
+        <v>15.84862847299804</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>18.72216335551873</v>
+        <v>19.23126418796702</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>14.4443358882225</v>
+        <v>14.93074976479092</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>15.04209370876059</v>
+        <v>13.68172953534388</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>13.09877910781995</v>
+        <v>9.954264769307748</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>11.18268459105775</v>
+        <v>9.824560103169432</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>11.40195185272754</v>
+        <v>10.04190609258696</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>13.40874764691995</v>
+        <v>12.07535785281499</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>11.05031726730139</v>
+        <v>9.695876385258259</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>10.97792568217623</v>
+        <v>7.806674806534026</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>14.89107478170423</v>
+        <v>15.32323774970418</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>14.81998725573492</v>
+        <v>13.34774242863504</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.03118</t>
+          <t>X ≈ -0.03141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>16.60445566982289</v>
+        <v>17.17508698192324</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>8.426270620547847</v>
+        <v>8.773289198531621</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.981407852841734</v>
+        <v>8.768655352742861</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.646806001284389</v>
+        <v>4.398928322740645</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.727674264019043</v>
+        <v>5.380327690465563</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2977775469878523</v>
+        <v>4.281218114260433</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.396359545443502</v>
+        <v>-1.556659279938614</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.363825672200363</v>
+        <v>-1.8659150235138</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.7038800387158375</v>
+        <v>0.7832643503874692</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-6.714603913086265</v>
+        <v>-3.801393823466114</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.822525738486007</v>
+        <v>-1.005179057878848</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-8.034940262532565</v>
+        <v>-5.068236489276309</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-7.845480740002728</v>
+        <v>-6.194733800889964</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-10.69237072091583</v>
+        <v>-8.97115434788693</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-13.97675362830385</v>
+        <v>-12.18825697003696</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-12.07516838879936</v>
+        <v>-10.36204714500094</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-14.83866458769219</v>
+        <v>-12.99906714334822</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-9.693514844889684</v>
+        <v>-8.081002538988692</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-14.73720629169748</v>
+        <v>-12.92388707394935</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-10.61162488922358</v>
+        <v>-8.916781990929707</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-8.524496852999697</v>
+        <v>-6.215593917636284</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-9.917990641153047</v>
+        <v>-7.557700632589025</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-12.27740071104735</v>
+        <v>-9.847280539373656</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-8.409677816035412</v>
+        <v>-6.214973336611976</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.02583</t>
+          <t>X ≈ -0.02605</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>23.0134305108464</v>
+        <v>20.38354179950176</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>15.42442760879482</v>
+        <v>16.46391824292998</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>16.42487575699395</v>
+        <v>13.99080918689425</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>18.14933039123797</v>
+        <v>15.86370248923286</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>14.17952851590879</v>
+        <v>11.91445901412187</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>11.94564488803029</v>
+        <v>12.07495886689382</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>9.970134973342546</v>
+        <v>10.06156349405653</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>7.270883557904426</v>
+        <v>7.305669228424762</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>8.52810014692966</v>
+        <v>8.663925168404212</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.333769419868197</v>
+        <v>5.416356028373151</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.607950960802263</v>
+        <v>5.688766627187491</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.687145721461</v>
+        <v>1.725027263241913</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.64563874104838</v>
+        <v>4.306002452096585</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>5.211704861303915</v>
+        <v>4.060105386984482</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>4.557479190365235</v>
+        <v>4.612780984637105</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>5.151992285709071</v>
+        <v>3.942590452462667</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3.803560440538654</v>
+        <v>2.608677493836453</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>7.352216105299476</v>
+        <v>6.174099162127874</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>10.00634247997952</v>
+        <v>8.856501391774955</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>11.41450865240002</v>
+        <v>10.30704163958927</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>8.435965822262482</v>
+        <v>7.273521908753224</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>9.581610976097487</v>
+        <v>8.434533689807573</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>11.07835136300771</v>
+        <v>11.14926239365348</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>6.128191246865747</v>
+        <v>6.052568466795087</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.02048</t>
+          <t>X ≈ -0.02069</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>19.24702130334729</v>
+        <v>20.33491286969117</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>10.38068881817597</v>
+        <v>11.59378891171377</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.733312808345964</v>
+        <v>4.921585992907289</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.796475888875008</v>
+        <v>4.313901566214362</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.682861673029024</v>
+        <v>2.487557592352665</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.424788214117811</v>
+        <v>4.190801768743</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.428821709238619</v>
+        <v>3.804852065533765</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.260306774443947</v>
+        <v>6.581852661245208</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.749212050514565</v>
+        <v>5.17130823140829</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.530285201989152</v>
+        <v>5.137087768978681</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>6.586431076897064</v>
+        <v>6.189049154027778</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>8.311574896115047</v>
+        <v>6.68209122525414</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>8.751766003567191</v>
+        <v>9.095046828464625</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>7.75594257050993</v>
+        <v>7.302543388233552</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>12.55654170622817</v>
+        <v>11.25893968851199</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>10.81573246936456</v>
+        <v>11.05386354703533</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>10.68660444777224</v>
+        <v>10.95140997837913</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>11.36495006545223</v>
+        <v>11.59777085946841</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>9.244236462270173</v>
+        <v>9.493908884380659</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>7.09270085259358</v>
+        <v>8.614096891473594</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>7.331314968735761</v>
+        <v>8.821791522191646</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>8.038762698272215</v>
+        <v>9.52439058619624</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>11.43999880384182</v>
+        <v>12.09612890167504</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>12.14953271028038</v>
+        <v>12.71349295717666</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.01512</t>
+          <t>X ≈ -0.01533</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>10.97293995238073</v>
+        <v>10.5264262760141</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.917719357973269</v>
+        <v>3.694047468923721</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.346777014901093</v>
+        <v>4.208216285949639</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.929504381348877</v>
+        <v>4.504069795197658</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.873554858725001</v>
+        <v>3.354482085268856</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.784287436251098</v>
+        <v>4.832758000021585</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.016002283778391</v>
+        <v>4.043688300145774</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>5.601894498156682</v>
+        <v>4.623737337671763</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.214806603587569</v>
+        <v>4.312200810555169</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.737329091684657</v>
+        <v>4.4038372819535</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>5.151491796558282</v>
+        <v>4.235279403581828</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6.597645593681534</v>
+        <v>6.167033807265568</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>8.065015583294844</v>
+        <v>7.701233085890657</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>9.573289969573437</v>
+        <v>9.221927709158486</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>7.622728546297004</v>
+        <v>6.779736405706124</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>7.175822112776288</v>
+        <v>7.342631397582892</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>8.341753535470232</v>
+        <v>8.567572781425532</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>6.511341400229384</v>
+        <v>7.112236195312732</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>6.730001231209222</v>
+        <v>7.329673608214719</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>5.189704220378005</v>
+        <v>4.449984732550732</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>5.945174829703653</v>
+        <v>5.651281333852111</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>4.57398836437148</v>
+        <v>4.694125255771404</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>5.28307218509299</v>
+        <v>4.939683953015724</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>4.343796779544441</v>
+        <v>3.452328108442359</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.009773</t>
+          <t>X ≈ -0.009971</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>10.00970077327381</v>
+        <v>11.3192523669667</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.504518741268924</v>
+        <v>5.719431137193773</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.561728539033865</v>
+        <v>3.930825072510792</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.209099093649563</v>
+        <v>0.9306562336896533</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.006756613746581763</v>
+        <v>1.728806116823613</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.226306918752073</v>
+        <v>2.691768355685596</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4593933464935134</v>
+        <v>1.896418598764527</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.9583366992035423</v>
+        <v>2.665716838427031</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.0333209088123354</v>
+        <v>0.9168788847366685</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.4892387864401044</v>
+        <v>0.6571670715769145</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2459614585432419</v>
+        <v>0.9311102453946702</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.778586753029167</v>
+        <v>2.26720862200721</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.3986808933800674</v>
+        <v>1.150476589775572</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.1786347222565468</v>
+        <v>0.9027607953184358</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.9967509168807709</v>
+        <v>0.7570426994430264</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.8929023571121633</v>
+        <v>2.128790237298979</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.019073448500365</v>
+        <v>2.563436599420974</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>2.211810970235319</v>
+        <v>2.971587881713482</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.504145039537633</v>
+        <v>1.456118445723831</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.210440409718494</v>
+        <v>1.940218357997104</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.149937573071746</v>
+        <v>0.2943799013571535</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.4443474410605646</v>
+        <v>-0.8577833547061005</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.3495367684441533</v>
+        <v>0.4653710479803124</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.803389367641707</v>
+        <v>-1.158506039877174</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.004422</t>
+          <t>X ≈ -0.004612</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.880229800639881</v>
+        <v>4.485917040388891</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.329288666820311</v>
+        <v>1.33834844212732</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.280173898998925</v>
+        <v>3.302529631897677</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.93219437618842</v>
+        <v>3.059847309742025</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5.608027900137891</v>
+        <v>4.759511628332838</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.686723914277998</v>
+        <v>1.865342170027702</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.828022329218172</v>
+        <v>2.315965393485975</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.016567377355216</v>
+        <v>2.009690579838164</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.60987878860373</v>
+        <v>1.875759486276444</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.571644898529073</v>
+        <v>2.692756415284428</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.747796753831445</v>
+        <v>1.628836225983562</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.469047350383448</v>
+        <v>1.353589731111406</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.4689079312554654</v>
+        <v>-0.8502280596259979</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.791040595710726</v>
+        <v>-1.899707937543631</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.5952503712583166</v>
+        <v>-0.2421387230132837</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.2706096687581763</v>
+        <v>-0.8355397194020213</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.22929449057402</v>
+        <v>-1.198663452918964</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.1387977608287017</v>
+        <v>-0.686852214255218</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.481983555393874</v>
+        <v>-2.27674147772062</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.111587807645932</v>
+        <v>-1.520732240207401</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.5496303903330357</v>
+        <v>-0.8264748348994715</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.4409300972840597</v>
+        <v>-0.5405244531544682</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.5343745733507319</v>
+        <v>-0.5531313765499846</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.6094451902721048</v>
+        <v>-0.7152703708394696</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.0009285</t>
+          <t>X ≈ 0.0007475</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.139883039008282</v>
+        <v>-1.346033918321751</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.10059091838793</v>
+        <v>1.135699673325497</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.5300479721528291</v>
+        <v>-0.6938644136609327</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.04853947164546923</v>
+        <v>-0.1145632752486705</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.579152658301211</v>
+        <v>-2.323531113875397</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.194435726749802</v>
+        <v>-1.388700292055766</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.1735124068858767</v>
+        <v>-0.4364862019388269</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.052623892105053</v>
+        <v>-0.9329449997322143</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.610256555479637</v>
+        <v>-2.163546205302502</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.589557380684212</v>
+        <v>-1.405453303269127</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.004027057947177</v>
+        <v>-1.133101150011242</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.082435601826383</v>
+        <v>-2.186123283215721</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.610768110219048</v>
+        <v>-3.691559393197181</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.435428732300814</v>
+        <v>-3.940506405119862</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.89462638254529</v>
+        <v>-3.345573442326156</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-3.09701401977199</v>
+        <v>-3.368049222343529</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.318590033902126</v>
+        <v>-2.888330993421128</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.42216681174601</v>
+        <v>-3.799256040351196</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-3.608761126147662</v>
+        <v>-4.167260215167921</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-5.106931847680599</v>
+        <v>-5.50816688952964</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-5.049534971160561</v>
+        <v>-5.491786302525995</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-5.809344120054959</v>
+        <v>-5.959080264334368</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-4.137098211682833</v>
+        <v>-4.353578074775832</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-4.414846047234654</v>
+        <v>-4.710269598248161</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.006279</t>
+          <t>X ≈ 0.006107</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.379892385644624</v>
+        <v>-5.135265496043083</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-3.470723621585464</v>
+        <v>-4.040618352624108</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6074834899328536</v>
+        <v>-1.213003653306451</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.572024085973034</v>
+        <v>-1.262662315340471</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.903591323273702</v>
+        <v>-2.225965916291614</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.847789293937353</v>
+        <v>-1.792402202556012</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.536076483397252</v>
+        <v>-1.225320921454269</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.810933930464564</v>
+        <v>-1.529783356506933</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.9180074312487179</v>
+        <v>1.331311981147323</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.152478020804061</v>
+        <v>0.9541215495770388</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.573721622159148</v>
+        <v>3.416434183396412</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.7588763508274</v>
+        <v>2.324351662017165</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.6435556494143739</v>
+        <v>1.203108461049652</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.041056607056447</v>
+        <v>2.870273587115847</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.113994748486249</v>
+        <v>1.914146602491066</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>3.588940934955424</v>
+        <v>4.121476266547973</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>2.649577578690042</v>
+        <v>3.194364029324518</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>3.081264533167072</v>
+        <v>3.884711749661363</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>4.914221538592336</v>
+        <v>5.738848538527648</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>3.756848676092382</v>
+        <v>4.035407761528631</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>5.098603097455559</v>
+        <v>5.65733505038699</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>4.754586840017488</v>
+        <v>5.19650845694914</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>2.878969675574119</v>
+        <v>3.248362120309714</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>3.886392548555307</v>
+        <v>4.182113536979159</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.01163</t>
+          <t>X ≈ 0.01147</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-13.85352635094142</v>
+        <v>-14.52927841491123</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.856281833301047</v>
+        <v>-4.909745676726942</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-8.201696853309308</v>
+        <v>-7.509669725678606</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-7.76144618697856</v>
+        <v>-8.550241539794527</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-5.312910901866744</v>
+        <v>-5.685303717562903</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-7.894391968689568</v>
+        <v>-8.67524317715511</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-9.58309309317584</v>
+        <v>-9.924481924191412</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-7.081359227870301</v>
+        <v>-7.751251274497761</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-5.189405608258056</v>
+        <v>-6.274006181160154</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.642803401523949</v>
+        <v>-4.819667548973371</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-6.154030975260433</v>
+        <v>-7.248444623724552</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.188777362117911</v>
+        <v>-3.92312277605545</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.056229427570663</v>
+        <v>-1.434411289902613</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.199790056869709</v>
+        <v>-2.133095801786176</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-4.712318249028762</v>
+        <v>-4.166601535022586</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-5.051348763259007</v>
+        <v>-4.055747966653342</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-3.790653307559609</v>
+        <v>-3.258727477477485</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-3.898695434235378</v>
+        <v>-3.842062033089512</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-2.750809471739863</v>
+        <v>-2.726698905042852</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.09778851416106</v>
+        <v>-1.611211559082967</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.175582389118269</v>
+        <v>-1.728205610013255</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.785964630217642</v>
+        <v>-1.80336813196854</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-4.763808899684804</v>
+        <v>-4.262436349392864</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-5.771978917626598</v>
+        <v>-5.325476244583207</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.01699</t>
+          <t>X ≈ 0.01683</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-17.84264053341447</v>
+        <v>-17.38206646479588</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-5.354952885275694</v>
+        <v>-4.501304751959417</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.397516448952302</v>
+        <v>-3.778059671580458</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.08061432779769</v>
+        <v>-2.370998989080064</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.089314420275315</v>
+        <v>-2.639521997490554</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.250859558104636</v>
+        <v>-3.128109399209997</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.639450136453313</v>
+        <v>-1.949244018251541</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.975371431141184</v>
+        <v>-5.536036811255954</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-7.286081569872479</v>
+        <v>-7.378819696118413</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.995262917256305</v>
+        <v>-5.547255465275576</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.376072288751978</v>
+        <v>-3.964154040953453</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-5.684404646733576</v>
+        <v>-5.553042169132702</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.407251134208977</v>
+        <v>-3.378460602373025</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.623373828249257</v>
+        <v>-3.626694663806084</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-4.956025803746584</v>
+        <v>-5.62463851937536</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-7.081083595000102</v>
+        <v>-7.694913447924158</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-5.178016982980175</v>
+        <v>-5.825109649122801</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-5.288363115766025</v>
+        <v>-5.957993754284452</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.677906629399075</v>
+        <v>-2.454057842928115</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.5453112152369428</v>
+        <v>-0.2657871873428093</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.706280522325642</v>
+        <v>-3.464810636091961</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.285723870965988</v>
+        <v>0.4073952630053412</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-3.186571846346361</v>
+        <v>-3.954233409611021</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.902338038018904</v>
+        <v>-2.800582930216315</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.02234</t>
+          <t>X ≈ 0.02218</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-28.08700976038719</v>
+        <v>-26.94818222876045</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-17.69022746932425</v>
+        <v>-16.64595866129855</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-15.21951071734468</v>
+        <v>-13.1075447635607</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-13.94004041772435</v>
+        <v>-13.34764159401448</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-14.25224540517224</v>
+        <v>-13.64013543550241</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-9.194284018547663</v>
+        <v>-9.628268354926199</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-3.144701918208703</v>
+        <v>-2.67721869240161</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-8.274966124364809</v>
+        <v>-7.853574208625794</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.341175752517422</v>
+        <v>-3.842150153310619</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-6.087167226037067</v>
+        <v>-5.609075434937722</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.881762906700772</v>
+        <v>-3.376130468877072</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.103702521556762</v>
+        <v>-5.099541913639605</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.364718735046644</v>
+        <v>-0.389191312643753</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.548172722777451</v>
+        <v>-1.608299160484684</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.249361838160716</v>
+        <v>-0.3487059695542101</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-4.567891723719391</v>
+        <v>-2.700023309957793</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.771335371866016</v>
+        <v>-0.8621561488672853</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-4.811607348983358</v>
+        <v>-3.907661613252166</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.663259365442016</v>
+        <v>0.1902957595246164</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.473438884794845</v>
+        <v>0.404882204583636</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.9164715498560909</v>
+        <v>2.750059062426146</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.112362366178239</v>
+        <v>0.7331489676554028</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.1467089991258703</v>
+        <v>1.947657239341531</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.058846435770512</v>
+        <v>2.756392031459889</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.02769</t>
+          <t>X ≈ 0.02754</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-29.28609568736912</v>
+        <v>-28.94299347627686</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-27.05837697236386</v>
+        <v>-26.75308124107607</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-16.4404649415235</v>
+        <v>-16.78833769015596</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-13.23204842570296</v>
+        <v>-12.45714575693481</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-7.117471533574623</v>
+        <v>-6.519378713660068</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-9.483859375202847</v>
+        <v>-8.254254398615522</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.536984813344944</v>
+        <v>-1.549336410848284</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-10.50332902085771</v>
+        <v>-9.35425685425686</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-7.897600110522085</v>
+        <v>-6.726327944572752</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-13.81507272216032</v>
+        <v>-12.52237943979209</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-13.56856761501565</v>
+        <v>-12.25014442518776</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-15.12484546017112</v>
+        <v>-13.77672637965909</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-8.504765694233193</v>
+        <v>-7.391618497109832</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-8.725962648911022</v>
+        <v>-7.639852558542941</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-8.087263876582156</v>
+        <v>-7.07200694042799</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-11.37570635700303</v>
+        <v>-11.51070292160833</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-12.79876875652575</v>
+        <v>-11.61458333333337</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-9.040791757130179</v>
+        <v>-7.997467438494944</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-8.820282291787208</v>
+        <v>-9.033005211349163</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-9.919503021418556</v>
+        <v>-10.06841876629021</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-10.45743110496605</v>
+        <v>-10.63586326767088</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-9.242592442357243</v>
+        <v>-9.461025789626198</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-10.27839946092637</v>
+        <v>-10.46739130434779</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-11.67351923777157</v>
+        <v>-11.87953029863732</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.03304</t>
+          <t>X ≈ 0.0329</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>62</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-21.36029370681483</v>
+        <v>-21.28456221198157</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-16.83672053005238</v>
+        <v>-16.69175937026608</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-19.85855717319188</v>
+        <v>-19.55935669796411</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-12.53158291720273</v>
+        <v>-12.08724276774008</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.304047672654121</v>
+        <v>-2.685381553000681</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.677660560494289</v>
+        <v>-4.141351172809074</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-7.049124849689022</v>
+        <v>-6.549336410848241</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.8791199701065366</v>
+        <v>-0.4026439510311022</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.047701757613261</v>
+        <v>-5.113424718766304</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.614058262414986</v>
+        <v>-1.070766536566275</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.97662128864318</v>
+        <v>-2.411434747768453</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.237821701158197</v>
+        <v>-2.6880167022397</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-7.535954755569563</v>
+        <v>-7.028715271303376</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-9.354107590572511</v>
+        <v>-8.889852558542891</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-8.404591763872403</v>
+        <v>-7.959103714621584</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-6.219038036940105</v>
+        <v>-5.784896469995431</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-7.948834070132904</v>
+        <v>-7.501680107526845</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-8.074879184471513</v>
+        <v>-7.634564212688488</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-4.650737691825064</v>
+        <v>-4.194295533929811</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-4.454467699404908</v>
+        <v>-3.979709088870827</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-4.989945730531723</v>
+        <v>-4.547153590251504</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-5.068147737553829</v>
+        <v>-3.009412886400341</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.586955600223256</v>
+        <v>-1.152875175315557</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.564855290925536</v>
+        <v>3.523695507814331</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.03839</t>
+          <t>X ≈ 0.03826</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-14.52140078603204</v>
+        <v>-13.54262672811063</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-18.58317414484982</v>
+        <v>-17.78853356381447</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-21.93092849218282</v>
+        <v>-21.04322766570605</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-10.98629587475139</v>
+        <v>-9.635629864514272</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-11.31497295990363</v>
+        <v>-9.911188004613635</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-3.382364769672108</v>
+        <v>-3.754254398615522</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-6.083541561072259</v>
+        <v>-6.549336410848241</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4765515186732614</v>
+        <v>-2.854256854256803</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.342525413539946</v>
+        <v>5.273672055427248</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.585751498031513</v>
+        <v>2.477620560207889</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.733662050813756</v>
+        <v>4.749855574812301</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.48181558157917</v>
+        <v>4.473273620340947</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.457899669889322</v>
+        <v>1.358381502890154</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.18234010007852</v>
+        <v>5.110147441456981</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>8.473631111151455</v>
+        <v>6.427993059572096</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>12.93432632335094</v>
+        <v>10.98929707839164</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>5.042467907043473</v>
+        <v>2.885416666666629</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>1.020669515331861</v>
+        <v>-1.247467438494965</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.182377390792901</v>
+        <v>0.9669947886508155</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.441495776807741</v>
+        <v>-0.8184187662902076</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.852001731611843</v>
+        <v>0.6141367323290297</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.8303392756660131</v>
+        <v>-1.461025789626255</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.021796754610904</v>
+        <v>2.782608695652179</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>10.86276800439803</v>
+        <v>8.620469701362744</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.04373</t>
+          <t>X ≈ 0.04362</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-16.59414743973435</v>
+        <v>-17.43151561699945</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.763783581410031</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-12.54896425185486</v>
+        <v>-13.37656099903938</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-13.15641634588754</v>
+        <v>-13.9689631978476</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-13.48165662589373</v>
+        <v>-14.24452133794694</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-13.26303986217335</v>
+        <v>-11.30980995417108</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-11.26843989440314</v>
+        <v>-9.32711418862602</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-5.82528444254153</v>
+        <v>-1.298701298701303</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.222328029506123</v>
+        <v>4.384783166538362</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.646174358325112</v>
+        <v>9.144287226874624</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-9.219288133918376</v>
+        <v>-4.472366647409977</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-6.649346413971081</v>
+        <v>-1.971170824103496</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-4.907827590882519</v>
+        <v>-0.3082851637764534</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-10.74557252610836</v>
+        <v>-6.11207478076512</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-5.748979564687261</v>
+        <v>-1.238673607094697</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-10.84164255965204</v>
+        <v>-6.232925143830514</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-8.11318510439709</v>
+        <v>-3.559027777777821</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-11.0804004004507</v>
+        <v>-6.469689660717123</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-10.86450901952637</v>
+        <v>-6.255227433571349</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-10.65073516130326</v>
+        <v>-6.040640988512365</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-11.18251010996727</v>
+        <v>-6.608085489893099</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-8.43368074670105</v>
+        <v>-3.905470234070641</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-8.196573812006555</v>
+        <v>-3.661835748792264</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-8.296895861148201</v>
+        <v>-3.82397474308177</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.04909</t>
+          <t>X ≈ 0.04898</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-25.53568444911532</v>
+        <v>-26.61954980503367</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.292286906567732</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.148668855299441</v>
+        <v>2.649080026601638</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.582590065349322</v>
+        <v>2.056677827793472</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.529362557451421</v>
+        <v>-5.911188004613606</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.387940707297659</v>
+        <v>5.784207139846018</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10.60294227063529</v>
+        <v>8.835278973767203</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>10.44738916664947</v>
+        <v>8.530358530358527</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.54641426114221</v>
+        <v>0.9659797477349343</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.136403288221786</v>
+        <v>-3.676225593638193</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-5.861451585399671</v>
+        <v>-7.250144425187699</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.095597955841427</v>
+        <v>-7.526726379659053</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.6902497899697693</v>
+        <v>-0.9493108048020815</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.380052574793858</v>
+        <v>-5.043698712389087</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-4.045721459370228</v>
+        <v>-5.725853094274143</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-11.38300220750548</v>
+        <v>-12.85685676776217</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-7.524745954958611</v>
+        <v>-9.114583333333336</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-3.727720313204848</v>
+        <v>-5.40131359234109</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-3.511828932280523</v>
+        <v>-5.186851365195317</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.6596646802160677</v>
+        <v>-1.126111073982493</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>4.079189553791359</v>
+        <v>2.15259827079057</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>3.995818005386433</v>
+        <v>2.077435748835342</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>4.300841153979789</v>
+        <v>2.321070234113719</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>4.274532710280376</v>
+        <v>2.158931239824255</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.05443</t>
+          <t>X ≈ 0.05434</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-20.27605191999228</v>
+        <v>-16.0426267281106</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>7.087786959813243</v>
+        <v>2.461466436185532</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-22.42639008864942</v>
+        <v>-23.79322766570605</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-16.46638506940425</v>
+        <v>-18.13562986451436</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-9.908983482519169</v>
+        <v>-12.16118800461369</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-9.722017296421789</v>
+        <v>-12.00425439861561</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-31.53559781953826</v>
+        <v>-31.54933641084842</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.063205565262649</v>
+        <v>-6.854256854256775</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-24.88054885368445</v>
+        <v>-25.47632794457266</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-25.7268688434248</v>
+        <v>-26.27237943979218</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-32.2711781162512</v>
+        <v>-32.25014442518793</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-32.69673614710713</v>
+        <v>-32.52672637965905</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-19.88954312917083</v>
+        <v>-21.14161849711</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-34.74819670180053</v>
+        <v>-33.88985255854303</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-42.45458976286264</v>
+        <v>-40.82200694042808</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-34.64360759354931</v>
+        <v>-34.01070292160833</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-34.98795658538775</v>
+        <v>-34.11458333333334</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-41.88852882685714</v>
+        <v>-34.24746743849494</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-34.58230131147899</v>
+        <v>-27.78300521134916</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-41.65413711985368</v>
+        <v>-33.81841876629018</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-35.14843352433826</v>
+        <v>-28.13586326767091</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-42.27252924922881</v>
+        <v>-34.4610257896262</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-42.17344456030573</v>
+        <v>-34.21739130434782</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-38.2968958611482</v>
+        <v>-34.37953029863728</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.05979</t>
+          <t>X ≈ 0.0597</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-39.39302102647544</v>
+        <v>-38.15801134349521</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-39.91910217265141</v>
+        <v>-38.40391817919908</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-41.73972991733449</v>
+        <v>-39.65861228109066</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-26.483118719386</v>
+        <v>-24.8663990952835</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-18.71456136584613</v>
+        <v>-17.44964954307504</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.127595179748724</v>
+        <v>-1.908100552461569</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-11.15320936665405</v>
+        <v>-10.39549025700198</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-11.81257221239619</v>
+        <v>-10.70041070041081</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-11.55328422991624</v>
+        <v>-10.57248179072671</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.168971273977228</v>
+        <v>-3.676225593638357</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-11.88878966336699</v>
+        <v>-11.0962982713415</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-12.38533986738</v>
+        <v>-11.37288022581301</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-13.61740233451898</v>
+        <v>-12.48777234326367</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-14.55299941758886</v>
+        <v>-12.73600640469667</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-15.21114271516942</v>
+        <v>-13.41816078658173</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-22.70499108734396</v>
+        <v>-20.54916446006986</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-23.14528077334099</v>
+        <v>-20.65304487179487</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-22.88247441833886</v>
+        <v>-20.78592897695637</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-22.60530852761055</v>
+        <v>-20.5714667498107</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-14.39150193332864</v>
+        <v>-12.66457261244403</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-39.93404810129466</v>
+        <v>-36.30894019074783</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-31.67656072937067</v>
+        <v>-28.69179502039543</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-34.64963503649635</v>
+        <v>-36.14046822742475</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-34.72546728971975</v>
+        <v>-36.30260722171421</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.06513</t>
+          <t>X ≈ 0.06506</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>20</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-23.55703758962246</v>
+        <v>-23.54262672811063</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-23.83086200701987</v>
+        <v>-23.78853356381447</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-20.24221438938419</v>
+        <v>-20.04322766570605</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-11.03897793263647</v>
+        <v>-10.63562986451427</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-6.454768405183778</v>
+        <v>-5.911188004613606</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-6.298278409562563</v>
+        <v>-5.754254398615522</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-11.99929302751882</v>
+        <v>-11.54933641084824</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.319377921403451</v>
+        <v>-1.854256854256853</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.643014967707281</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-8.025992519743674</v>
+        <v>-7.522379439792026</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-12.73487332423176</v>
+        <v>-12.25014442518776</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-12.98260535795284</v>
+        <v>-12.52672637965898</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-14.09025873994531</v>
+        <v>-13.64161849710975</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-9.405940594059473</v>
+        <v>-8.889852558542934</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-10.06408389164003</v>
+        <v>-9.57200694042799</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-9.46969696969704</v>
+        <v>-9.010702921608328</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-4.603614106674513</v>
+        <v>-4.114583333333265</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-9.70845481049551</v>
+        <v>-9.247467438495008</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-9.492563429571298</v>
+        <v>-9.033005211349163</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-4.305717619603413</v>
+        <v>-3.818418766290172</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-4.848263787569373</v>
+        <v>-4.385863267670842</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-4.924109748978395</v>
+        <v>-4.461025789626191</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-4.649635036496491</v>
+        <v>-4.217391304347814</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-4.725467289719617</v>
+        <v>-4.379530298637277</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.07048</t>
+          <t>X ≈ 0.07042</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>11</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-8.403672940087546</v>
+        <v>-8.088081273565081</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.2400894528678137</v>
+        <v>0.7569209816401425</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.056085624532059</v>
+        <v>-0.4977731202515088</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>16.12724846507933</v>
+        <v>17.09164286275846</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>15.79145799253206</v>
+        <v>16.81608472265913</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.857073656868458</v>
+        <v>-1.208799853160983</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-11.53360951748044</v>
+        <v>-11.09479095630279</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-11.7601253460218</v>
+        <v>-11.39971139971134</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-29.75664854082718</v>
+        <v>-29.45360067184548</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-30.49854684713656</v>
+        <v>-30.24965216706475</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-21.26234719444756</v>
+        <v>-20.88650806155146</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-12.50658272467184</v>
+        <v>-12.0721809251136</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-13.60906654504348</v>
+        <v>-13.18707304256444</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.230423042304366</v>
+        <v>4.746511077820699</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-5.51862934618535</v>
+        <v>-5.02655239497345</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-4.92424242424223</v>
+        <v>-4.465248376153788</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-5.058159561219902</v>
+        <v>-4.569128787878917</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-14.25390935595017</v>
+        <v>-13.79292198394948</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-14.03801797502584</v>
+        <v>-13.57845975680371</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-13.85117216505768</v>
+        <v>-13.36387331174473</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-5.302809242114762</v>
+        <v>-4.840408722216495</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-5.378655203523792</v>
+        <v>-4.915571244171659</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-14.19508958195076</v>
+        <v>-13.76284584980237</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-5.180012744265014</v>
+        <v>-4.834075753182745</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.07583</t>
+          <t>X ≈ 0.07578</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-39.56151955892712</v>
+        <v>-38.15801134349521</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-31.8891166006882</v>
+        <v>-30.71161048689144</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-17.38720044264448</v>
+        <v>-16.58168920416758</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-18.32342738039559</v>
+        <v>-17.1740914029758</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-18.65921785294287</v>
+        <v>-17.44964954307514</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-26.70270434174264</v>
+        <v>-24.98502362938475</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-3.015111886079623</v>
+        <v>-2.703182564694394</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-3.741352004667775</v>
+        <v>-3.00810300810307</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-11.76438095178545</v>
+        <v>-10.5724817907266</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-12.80611383212295</v>
+        <v>-11.36853328594599</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-20.50696458422635</v>
+        <v>-18.78860596364924</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-12.72119785864203</v>
+        <v>-11.3728802258129</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-5.690238061698814</v>
+        <v>-4.795464650955928</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-9.405940594059402</v>
+        <v>-12.73600640469683</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-1.730750558306568</v>
+        <v>-5.7258530942742</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-1.136363636363697</v>
+        <v>-5.164549075454481</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-9.603614106674442</v>
+        <v>-12.96073717948718</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-18.04178814382902</v>
+        <v>-20.78592897695642</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-17.82589676290463</v>
+        <v>-20.5714667498107</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-17.6390509529366</v>
+        <v>-20.35688030475171</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-18.18159712090263</v>
+        <v>-20.92432480613245</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-18.25744308231168</v>
+        <v>-20.99948732808773</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-17.98296836982968</v>
+        <v>-20.75585284280935</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-18.0588006230529</v>
+        <v>-20.91799183709882</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.08119</t>
+          <t>X ≈ 0.08114</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-36.67895768777444</v>
+        <v>-44.4517176372015</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-28.76538952280344</v>
+        <v>-35.60671538199628</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-46.53906790266285</v>
+        <v>-45.95231857479689</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-22.56066389741425</v>
+        <v>-19.27199350087785</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.741226789458793</v>
+        <v>-1.365733459159067</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.946085263979832</v>
+        <v>-1.208799853160983</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-32.04736995059582</v>
+        <v>-29.27660913812097</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-15.65891472868223</v>
+        <v>-11.39971139971141</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-23.9507608801008</v>
+        <v>-20.36269158093633</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-24.72367655613729</v>
+        <v>-21.15874307615572</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-24.44961691397537</v>
+        <v>-20.88650806155133</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-24.72836631742341</v>
+        <v>-21.16309001602269</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-25.85152838427948</v>
+        <v>-22.27798213347346</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-17.73927392739273</v>
+        <v>-22.52621619490644</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-18.39741722497329</v>
+        <v>-23.20837057679149</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-17.80303030303025</v>
+        <v>-22.64706655797196</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-9.603614106674442</v>
+        <v>-13.66003787878788</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-18.04178814382895</v>
+        <v>-13.79292198394955</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-17.82589676290463</v>
+        <v>-13.57845975680371</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-9.305717619603271</v>
+        <v>-13.36387331174466</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-18.18159712090263</v>
+        <v>-23.02222690403462</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-18.25744308231173</v>
+        <v>-23.09738942598983</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-17.98296836982968</v>
+        <v>-22.85375494071145</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-18.05880062305295</v>
+        <v>-23.01589393500092</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2461 +3180,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.0713</t>
+          <t>X &gt; -0.0716</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3355</v>
+        <v>3378</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.368712082339286</v>
+        <v>-0.3817916795954588</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1249130113078536</v>
+        <v>-0.1120629755791782</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3025318497016585</v>
+        <v>-0.2918301958619693</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2285531154066689</v>
+        <v>-0.2206798939433483</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.07341621058517234</v>
+        <v>-0.03835903787825146</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.04766325958797069</v>
+        <v>-0.04165133618914041</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.06131240090724077</v>
+        <v>-0.05449105002350052</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.003795459250575561</v>
+        <v>0.0107991268863401</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.0267478198455251</v>
+        <v>-0.02134710166087217</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.07007402248725469</v>
+        <v>-0.06365302469775003</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.01330754894910058</v>
+        <v>0.01909768628378572</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.01910843005138219</v>
+        <v>0.02489603922000327</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.0127608678255271</v>
+        <v>0.01875329397898895</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.01736499452561446</v>
+        <v>0.02396090072507207</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.02840146523497111</v>
+        <v>-0.0207816673249539</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.04078560741261583</v>
+        <v>-0.0325576174145894</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.02149746726188795</v>
+        <v>0.02869583948793775</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.03583576287658019</v>
+        <v>-0.02760928246656391</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.04034550757070576</v>
+        <v>-0.0321184244736159</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.07403209250380627</v>
+        <v>-0.06620114358172202</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1401041687485787</v>
+        <v>-0.1134586536513922</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1385869607746528</v>
+        <v>-0.08232756477413261</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.1144741306560562</v>
+        <v>-0.05787665504329453</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1427549201220089</v>
+        <v>-0.1136925248066163</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.06595</t>
+          <t>X &gt; -0.06624</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3343</v>
+        <v>3367</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.4759139782165107</v>
+        <v>-0.4747801204409754</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2300828891896316</v>
+        <v>-0.2034052073671404</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3735002311071511</v>
+        <v>-0.3797093658241053</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2669896036939434</v>
+        <v>-0.2769053295275583</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1101113445016821</v>
+        <v>-0.09311358051437679</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.114706980991123</v>
+        <v>-0.1264848269759398</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.09589629772288077</v>
+        <v>-0.1072560325976468</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.0002077648655784969</v>
+        <v>-0.01121813122996684</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.0008055628532517289</v>
+        <v>-0.01432321364431033</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.07131263082937522</v>
+        <v>-0.08375181482906413</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.01841969589290215</v>
+        <v>-0.001623715128587833</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.01161020531841217</v>
+        <v>0.005087766538046878</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.01396997887138696</v>
+        <v>0.002549649722617175</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.03839882794961369</v>
+        <v>-0.02103408060393264</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1118308328515454</v>
+        <v>-0.09333395464599903</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.06671189507009956</v>
+        <v>-0.04773995864536573</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.03359320491271944</v>
+        <v>-0.0155910393202916</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.06090403391258548</v>
+        <v>-0.0420123540004198</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.06621147259490101</v>
+        <v>-0.04724008679400526</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1305831306612575</v>
+        <v>-0.1118035185891983</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1949463936661289</v>
+        <v>-0.1573766207866427</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.2230634111607586</v>
+        <v>-0.1555939107303814</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.1699699647260076</v>
+        <v>-0.102189404110284</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1681834129622217</v>
+        <v>-0.1279710470780344</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.0606</t>
+          <t>X &gt; -0.06088</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3330</v>
+        <v>3354</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.508388879541755</v>
+        <v>-0.5073883508526791</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2603150487558139</v>
+        <v>-0.2340311941462261</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.4285683339471049</v>
+        <v>-0.4061906286690089</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2890335284788605</v>
+        <v>-0.2710774045261246</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1302488625996787</v>
+        <v>-0.08551353085137237</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1355945562184004</v>
+        <v>-0.1196162016997491</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1137178286591194</v>
+        <v>-0.09724504330151973</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.01373101122814546</v>
+        <v>0.03001614277577858</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.01255650426921306</v>
+        <v>0.02641767727349276</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.05521509437639338</v>
+        <v>-0.04019416663294351</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.003177656045984634</v>
+        <v>0.01151283646950674</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.00474752074885032</v>
+        <v>0.01932234286026357</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.02318507090623001</v>
+        <v>-0.008631870066729164</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.04685104629060532</v>
+        <v>-0.03135077495196725</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.08805033861419531</v>
+        <v>-0.0715609100979222</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.04506406589115386</v>
+        <v>-0.0279545575393243</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.01128796758571582</v>
+        <v>0.004726395913912995</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.03828989295440266</v>
+        <v>-0.02127696230446219</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.04445305164688307</v>
+        <v>-0.0273487659785161</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.109798027644068</v>
+        <v>-0.09298696164455578</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1722961908096323</v>
+        <v>-0.1365335089577826</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.2002201931560705</v>
+        <v>-0.134446528601174</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1479838806872849</v>
+        <v>-0.08177282446703771</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1759177401700711</v>
+        <v>-0.1368350094303707</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.05525</t>
+          <t>X &gt; -0.05552</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3313</v>
+        <v>3338</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6573388675549054</v>
+        <v>-0.6417043835702856</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2863617642112999</v>
+        <v>-0.3063907066716141</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.4781494114578422</v>
+        <v>-0.4734152215262384</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3342800534848038</v>
+        <v>-0.3348555941152256</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2030058857058208</v>
+        <v>-0.1471129375894762</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2093552006393438</v>
+        <v>-0.1821447442651021</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1534077997997159</v>
+        <v>-0.1558937878974263</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.02389870304114794</v>
+        <v>-0.02658839868142593</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.05535961770224418</v>
+        <v>-0.03083137433714001</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.08948132663237374</v>
+        <v>-0.06414554957729734</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.03858934505305456</v>
+        <v>-0.01349864780786447</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.02920867602745147</v>
+        <v>-0.004338319957561509</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.02145515727577418</v>
+        <v>0.002752957055598415</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.07421271928517115</v>
+        <v>-0.04875339486311958</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.08215073897510194</v>
+        <v>-0.05602247672915439</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.01186564439576898</v>
+        <v>0.01499940953333123</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.02277938534123081</v>
+        <v>0.04834641255605732</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.03395209801822574</v>
+        <v>-0.007036816485367581</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.04125200358395631</v>
+        <v>-0.01415986285978477</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.07773209487468336</v>
+        <v>-0.0512134999825804</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1076124003557979</v>
+        <v>-0.06230744606061478</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.1654370491292312</v>
+        <v>-0.08976830459626228</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.08415525375645672</v>
+        <v>-0.008047189343329819</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.1721923123577227</v>
+        <v>-0.1224901548386086</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.0499</t>
+          <t>X &gt; -0.05017</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3295</v>
+        <v>3318</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.7918872099046865</v>
+        <v>-0.8039257403823683</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.447276505267908</v>
+        <v>-0.4352401506408157</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6323458265744577</v>
+        <v>-0.6257373991591706</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4235191287165847</v>
+        <v>-0.4229276476179251</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3199183915290149</v>
+        <v>-0.2923687058422573</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3273536338551679</v>
+        <v>-0.3285949261934604</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2065363655761203</v>
+        <v>-0.2075073253909707</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.04461462797723215</v>
+        <v>-0.04561858191132728</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.1369198405117942</v>
+        <v>-0.1406693787161615</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.07635692695551199</v>
+        <v>-0.07940224891573422</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.02667567821283967</v>
+        <v>-0.03009038736128389</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.04597067314023917</v>
+        <v>-0.04924890218157429</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.06232011398194715</v>
+        <v>-0.06546950341802216</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.05364035192864947</v>
+        <v>-0.05571794315832079</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.05802879021700846</v>
+        <v>-0.05893209822781387</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.009406603894795751</v>
+        <v>0.00914073443496477</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.01468337893597749</v>
+        <v>0.01323621553884635</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.04178814382895268</v>
+        <v>-0.04169126520974231</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.05030820071406339</v>
+        <v>-0.05015838619117829</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.02736710413935128</v>
+        <v>-0.02853315521251432</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.02412794766632942</v>
+        <v>-0.006158359510720857</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1424900947472807</v>
+        <v>-0.09355591010812248</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.03191658989440782</v>
+        <v>0.0173179454262069</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.1503534809184046</v>
+        <v>-0.126968514429926</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.04455</t>
+          <t>X &gt; -0.04481</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3270</v>
+        <v>3294</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.9373234196288109</v>
+        <v>-0.9348486153581064</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6483677586368373</v>
+        <v>-0.6220679425840743</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.8543724440954463</v>
+        <v>-0.8350828693259587</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5473935749651488</v>
+        <v>-0.5360523147255023</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4100760172796711</v>
+        <v>-0.3724014063642826</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.419017250885517</v>
+        <v>-0.4100515000648031</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2610035476742709</v>
+        <v>-0.2521452299361329</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.09574882305051347</v>
+        <v>-0.08688525304840056</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1586374533854098</v>
+        <v>-0.1533451703207049</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1221941721389115</v>
+        <v>-0.116091652609505</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.07423604864934674</v>
+        <v>-0.06840871306196306</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.06109008050372466</v>
+        <v>-0.05546201184296251</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.09949586395428156</v>
+        <v>-0.09396342903116306</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1195727989999327</v>
+        <v>-0.1126128490998397</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1495018294068942</v>
+        <v>-0.1411864741851829</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.116630140279824</v>
+        <v>-0.1070081911419436</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.04927955233988968</v>
+        <v>-0.04157515399374034</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1359357265261565</v>
+        <v>-0.1262553172828191</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.1156544497301297</v>
+        <v>-0.1060576514825371</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.09398526396624618</v>
+        <v>-0.08585357526531112</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.05602425197503891</v>
+        <v>-0.02887206354594696</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.2358456902986958</v>
+        <v>-0.1770452071019193</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.1265534100824084</v>
+        <v>-0.06716368674539552</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.2147639258052507</v>
+        <v>-0.1809874935371028</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.0392</t>
+          <t>X &gt; -0.03945</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3233</v>
+        <v>3259</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.229172766273749</v>
+        <v>-1.166027093741306</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.8102889394400421</v>
+        <v>-0.7254430426319018</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.9101077625342668</v>
+        <v>-0.86639839741337</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5607913221989378</v>
+        <v>-0.5578622524374168</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4488531556634427</v>
+        <v>-0.420034862453754</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4908058820900223</v>
+        <v>-0.5208091743250094</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3837811540429712</v>
+        <v>-0.4138052753171024</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2135124298315958</v>
+        <v>-0.2130354802110546</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.3392220237205521</v>
+        <v>-0.312155678231882</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2628016331551635</v>
+        <v>-0.2660396903267639</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2482815261992997</v>
+        <v>-0.2208045718870224</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1702076655532494</v>
+        <v>-0.1742347868739671</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2579421986488839</v>
+        <v>-0.2318325643881138</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2449288728996279</v>
+        <v>-0.2174756848812649</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.2677247432289747</v>
+        <v>-0.2696813590326386</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.2413019079685697</v>
+        <v>-0.2717987281586787</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.07906949413970921</v>
+        <v>-0.143364717289252</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.2272935998717784</v>
+        <v>-0.2581871934719686</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1783836334637954</v>
+        <v>-0.2094757995844532</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.1586224403696477</v>
+        <v>-0.1913884261124252</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.0831216367658385</v>
+        <v>-0.09708337803265721</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.2332287597975622</v>
+        <v>-0.2460610548822544</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.1876684316726056</v>
+        <v>-0.1376367031208261</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.2451084898433464</v>
+        <v>-0.2509632535314239</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.03385</t>
+          <t>X &gt; -0.03409</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3178</v>
+        <v>3204</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.703347113431967</v>
+        <v>-1.65174018130341</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.271653921159711</v>
+        <v>-1.230394028930746</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.28606322347693</v>
+        <v>-1.244778053302952</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.9185894732176649</v>
+        <v>-0.9209896660031021</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.7990582913509741</v>
+        <v>-0.7141665959881038</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.7511646156881966</v>
+        <v>-0.6952848145062731</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.6290856675650716</v>
+        <v>-0.5729315676318549</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.3885315989191369</v>
+        <v>-0.3635736244431982</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.4231919577950265</v>
+        <v>-0.4044888641129845</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.3634968841431387</v>
+        <v>-0.3440077803763089</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.4475270498165358</v>
+        <v>-0.4270172881035137</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.4887927834001502</v>
+        <v>-0.4682686682162611</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.5273962220042847</v>
+        <v>-0.5078704411222716</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.5731825143606244</v>
+        <v>-0.5513335790780971</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.5223387566744861</v>
+        <v>-0.5306126049160014</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.5058037200894319</v>
+        <v>-0.5113255866145536</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.3071316946141422</v>
+        <v>-0.316701053669675</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.4247601827859171</v>
+        <v>-0.4312680615478968</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.3787985018528843</v>
+        <v>-0.3854514562852742</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.393425887443577</v>
+        <v>-0.4019599134223526</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2758022974718486</v>
+        <v>-0.265189741010488</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.4272544030664562</v>
+        <v>-0.3842946604933246</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.4486284306454564</v>
+        <v>-0.4030387302448517</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.5058322991595219</v>
+        <v>-0.4843992124949565</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.0285</t>
+          <t>X &gt; -0.02873</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3102</v>
+        <v>3125</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.151894183556848</v>
+        <v>-2.127682371989771</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.509256198777301</v>
+        <v>-1.483287140920986</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.488618930053399</v>
+        <v>-1.497917649807796</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.03044313410166</v>
+        <v>-1.055477192758552</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.8854643758797067</v>
+        <v>-0.8682354115496551</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.7768640368240369</v>
+        <v>-0.8210908085454989</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.536786243090944</v>
+        <v>-0.5480629310647345</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.315635934970274</v>
+        <v>-0.3255944338746914</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.4163150093263042</v>
+        <v>-0.4345152653755591</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2078927145107485</v>
+        <v>-0.2566050612070043</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.3648384939368299</v>
+        <v>-0.4124013585635993</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.3039097374897466</v>
+        <v>-0.3519814816998661</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.3481007921629384</v>
+        <v>-0.3641065353873429</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3252591411503687</v>
+        <v>-0.3384805100426149</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.1927012549840157</v>
+        <v>-0.2359073553657467</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.2223505560591406</v>
+        <v>-0.2622993456185441</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.04889554583521516</v>
+        <v>0.003909161077402246</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.1976727055712573</v>
+        <v>-0.2378827739581979</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.0270128822435467</v>
+        <v>-0.06847980387072994</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.1430767178319385</v>
+        <v>-0.1867052113029715</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.07370662170779241</v>
+        <v>-0.1147635234253883</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.1947283056794333</v>
+        <v>-0.2029509575187447</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.1588196965027961</v>
+        <v>-0.1642882973100797</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.3121855360123433</v>
+        <v>-0.3395302986372783</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.02315</t>
+          <t>X &gt; -0.02337</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3020</v>
+        <v>3044</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.835191079232693</v>
+        <v>-2.726699835160204</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.969044964413364</v>
+        <v>-1.960857323605595</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.975011832152035</v>
+        <v>-1.910068396776538</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.551218441743337</v>
+        <v>-1.505691895203135</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.294513851749457</v>
+        <v>-1.208379382797801</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.122309643392931</v>
+        <v>-1.164251131709285</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.8220735079080157</v>
+        <v>-0.8303821624822234</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5216275238496522</v>
+        <v>-0.5286602540607248</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.6591766129067693</v>
+        <v>-0.6766222545792928</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.3583616863713743</v>
+        <v>-0.4075609903318309</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.5270135718469575</v>
+        <v>-0.5747517550306895</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.3579715082294683</v>
+        <v>-0.4072501112466114</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.5379970311441653</v>
+        <v>-0.4883768468151288</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.4756005478395267</v>
+        <v>-0.4555256669608809</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.3216796644272719</v>
+        <v>-0.364929614084609</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.368276421299214</v>
+        <v>-0.3741903027948226</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.05305230892162882</v>
+        <v>-0.06540300546448208</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.4026696865286752</v>
+        <v>-0.4085038438737527</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.2994417364496016</v>
+        <v>-0.3059710906142499</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.4568919497389032</v>
+        <v>-0.4659409192274921</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.3047639529679103</v>
+        <v>-0.3113637599584038</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.4601785775687333</v>
+        <v>-0.4327920404469481</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.4639349371914889</v>
+        <v>-0.4653387591918232</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.487056693693134</v>
+        <v>-0.5096222828685626</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.0178</t>
+          <t>X &gt; -0.01801</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2892</v>
+        <v>2915</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-3.812550410135266</v>
+        <v>-3.747265200143339</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.515644523255503</v>
+        <v>-2.560702731618015</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.183402410984591</v>
+        <v>-2.21239546925311</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.743647513084667</v>
+        <v>-1.7632313657084</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.426292574837852</v>
+        <v>-1.371938857855923</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.323564320350528</v>
+        <v>-1.401232889568064</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.010218247809377</v>
+        <v>-1.035509166054794</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.8217961234974993</v>
+        <v>-0.8433278925082277</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.898552044759434</v>
+        <v>-0.9354157477842264</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.6189933605450051</v>
+        <v>-0.6529330966615277</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.8418548287761496</v>
+        <v>-0.8740760491193811</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.7416858719072295</v>
+        <v>-0.7209808256234851</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.949162200038721</v>
+        <v>-0.9124803302151605</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.8399288739628759</v>
+        <v>-0.7988501637430687</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.8916700985365082</v>
+        <v>-0.8793306912835632</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.8632809641778252</v>
+        <v>-0.8799257904888478</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.5283898140588406</v>
+        <v>-0.5529394977168991</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.923504862273326</v>
+        <v>-0.9398278358913004</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.7218451975271023</v>
+        <v>-0.7396536006569079</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.7910371360108783</v>
+        <v>-0.8677676353785984</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.6427370172756852</v>
+        <v>-0.7155411292199219</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.8363419535395664</v>
+        <v>-0.8734357999107374</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.9908033738623985</v>
+        <v>-1.021232182262779</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.046352490272874</v>
+        <v>-1.094796164846549</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.01245</t>
+          <t>X &gt; -0.01265</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2661</v>
+        <v>2689</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-5.096070994028985</v>
+        <v>-4.946913498251028</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.247740373147963</v>
+        <v>-3.086390178744246</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.837093296884468</v>
+        <v>-2.752022935476923</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.409749763221519</v>
+        <v>-2.289973672277668</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.886369522283552</v>
+        <v>-1.769176170294081</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.940593165061159</v>
+        <v>-1.925175597283669</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.53335125900697</v>
+        <v>-1.462395974296264</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.379433302603886</v>
+        <v>-1.302813478979282</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.429249469700494</v>
+        <v>-1.376457526209187</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.170782344560436</v>
+        <v>-1.077934995347647</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.362134073590987</v>
+        <v>-1.303497518926179</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.378809347499491</v>
+        <v>-1.299891687294341</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.731678197013565</v>
+        <v>-1.636429468199516</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.743894884055649</v>
+        <v>-1.641057601182908</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.630800533319118</v>
+        <v>-1.523045516095642</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.561151242560541</v>
+        <v>-1.570999767619462</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.298402258155505</v>
+        <v>-1.31948311061619</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.56891992677469</v>
+        <v>-1.616572525758208</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-1.368736037451221</v>
+        <v>-1.417849193518556</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.310222124107774</v>
+        <v>-1.314704056037584</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.214630153935673</v>
+        <v>-1.25064781447626</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.306009861633306</v>
+        <v>-1.341367669968072</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.535435186759315</v>
+        <v>-1.52222401810247</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.51426849227505</v>
+        <v>-1.476964288968261</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.007097</t>
+          <t>X &gt; -0.007291</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2276</v>
+        <v>2318</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-7.651309188410174</v>
+        <v>-7.550342116023153</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.389928316491769</v>
+        <v>-4.495777455799036</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.581182227828478</v>
+        <v>-3.821624579550885</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.612847525868787</v>
+        <v>-2.80544118526899</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.206603952148058</v>
+        <v>-2.329034422460026</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.476294629150821</v>
+        <v>-2.664125643250713</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.870436792011219</v>
+        <v>-1.999980187672271</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.774882094649534</v>
+        <v>-1.937983775682362</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.665379740325257</v>
+        <v>-1.743510075156941</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.451585567510868</v>
+        <v>-1.355641150148777</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.634153748402788</v>
+        <v>-1.661150444104358</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.912903151850784</v>
+        <v>-1.870812401164436</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.092042102901779</v>
+        <v>-2.082478712163592</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.069103099534651</v>
+        <v>-2.048200234962898</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.738054093217521</v>
+        <v>-1.887977667935523</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.976270151116772</v>
+        <v>-2.163157701970086</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.690418139993156</v>
+        <v>-1.940951278184698</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-2.208454810495631</v>
+        <v>-2.350915714357001</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.685545885711647</v>
+        <v>-1.877832797556067</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.736608361156591</v>
+        <v>-1.835660145600521</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.445455538337185</v>
+        <v>-1.497932233188159</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.451765587433179</v>
+        <v>-1.41876619497333</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.854290284629855</v>
+        <v>-1.840342124019955</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.46536184156497</v>
+        <v>-1.527934095013471</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001747</t>
+          <t>X &gt; -0.001932</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1733</v>
+        <v>1764</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-11.5778098641483</v>
+        <v>-11.33043711185778</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-6.181927636710149</v>
+        <v>-6.328036949818987</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.044376905766896</v>
+        <v>-6.059029020107857</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-4.663602143766695</v>
+        <v>-4.647487572024147</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.655158537140139</v>
+        <v>-4.555255801223772</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-4.094020577842031</v>
+        <v>-4.086645580073977</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.342602575523962</v>
+        <v>-3.355441554997476</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.276184497014548</v>
+        <v>-3.17778626602157</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.004944299591514</v>
+        <v>-2.880174098418905</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.712182303263717</v>
+        <v>-2.62707666673041</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.693818562432327</v>
+        <v>-2.694400225980054</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.972567965880323</v>
+        <v>-2.883464771505025</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.600617899326437</v>
+        <v>-2.469478066758747</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.156228281055945</v>
+        <v>-2.094835571000466</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.469147182779203</v>
+        <v>-2.404868130229687</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.680283851169925</v>
+        <v>-2.580108020758466</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.148231262690558</v>
+        <v>-2.174073418319175</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.943918253212949</v>
+        <v>-2.873529761441119</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.749327966128575</v>
+        <v>-1.7525519535588</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.932445730202346</v>
+        <v>-1.934566075072048</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-1.726143971901095</v>
+        <v>-1.708809443308311</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.76849015243662</v>
+        <v>-1.69458588032915</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.267858796588627</v>
+        <v>-2.244602188701563</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.733545766349742</v>
+        <v>-1.78315841655111</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.003604</t>
+          <t>X &gt; 0.003427</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1234</v>
+        <v>1250</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-15.79865709732891</v>
+        <v>-15.43602370503979</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-9.531179467337338</v>
+        <v>-9.397125449255995</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-8.274239254124616</v>
+        <v>-8.265184706278838</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-6.529822786707129</v>
+        <v>-6.511426042858226</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-5.494645517318922</v>
+        <v>-5.472940992661421</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-5.266543139183213</v>
+        <v>-5.196040682507068</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-4.62410662264746</v>
+        <v>-4.555715996175195</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.17533906901604</v>
+        <v>-4.10086499471975</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.164546555922016</v>
+        <v>-3.174851488068363</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.166144893512651</v>
+        <v>-3.129408193785693</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.377129713759786</v>
+        <v>-3.336406406018426</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.332516142268418</v>
+        <v>-3.17021159148959</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.19213738454895</v>
+        <v>-1.966958225327254</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.638950302797269</v>
+        <v>-1.335895724010562</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-2.297093600377828</v>
+        <v>-2.018050105895618</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-2.511768167107974</v>
+        <v>-2.256106598666683</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.079342262014251</v>
+        <v>-1.880370703437251</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.750526007906629</v>
+        <v>-2.492871115553292</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.9974177985033421</v>
+        <v>-0.7596239163851308</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.6487596908006807</v>
+        <v>-0.4651014201670804</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.3822443700935807</v>
+        <v>-0.1532493587980142</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.1344657360334125</v>
+        <v>0.05897421037379758</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.511983214634</v>
+        <v>-1.377391304347817</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.6492922492009825</v>
+        <v>-0.5795302986372874</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.008955</t>
+          <t>X &gt; 0.008787</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>863</v>
+        <v>885</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-19.8477436651561</v>
+        <v>-19.68435901157516</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-12.13654345201167</v>
+        <v>-11.60630634221717</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-11.57014468693475</v>
+        <v>-11.17371135524485</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-8.661159192237079</v>
+        <v>-8.676170405054812</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-7.038424319162232</v>
+        <v>-6.812088905514507</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-6.736250759792966</v>
+        <v>-6.599801185537729</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-5.951637539984453</v>
+        <v>-5.929268767105292</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.19178670100051</v>
+        <v>-5.161254596920521</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.919619011588694</v>
+        <v>-5.033325687236413</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.592806656214272</v>
+        <v>-4.813575828053935</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.935375189571978</v>
+        <v>-6.121476253630192</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.521283946368705</v>
+        <v>-5.436330899433059</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.411189662185564</v>
+        <v>-3.274386858691749</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.220969495793497</v>
+        <v>-3.070643518994913</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-3.763505856957877</v>
+        <v>-3.639803550597485</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-5.13443685409004</v>
+        <v>-4.886409136297587</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-4.112284626905662</v>
+        <v>-3.973340395480228</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-5.257587758472503</v>
+        <v>-5.123173653184196</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-3.538806204137764</v>
+        <v>-3.439784872366111</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.542711839256448</v>
+        <v>-2.321243625047238</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.738437197973923</v>
+        <v>-2.549705075580519</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.236248477302105</v>
+        <v>-2.059895846123375</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-3.399635036496349</v>
+        <v>-3.285187914517316</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.599163697599117</v>
+        <v>-2.54337210654689</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.01431</t>
+          <t>X &gt; 0.01415</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-21.83656576786622</v>
+        <v>-21.41049459597847</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-14.22027222982459</v>
+        <v>-13.84859362387453</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-12.68776240951109</v>
+        <v>-12.40058502306341</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-8.959675081327489</v>
+        <v>-8.718336631431562</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-7.610932628913048</v>
+        <v>-7.189383493335413</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.35199094511276</v>
+        <v>-5.904856808254081</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.746756453663245</v>
+        <v>-4.591505085547034</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.564845199029818</v>
+        <v>-4.29401589040144</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.830106483372781</v>
+        <v>-4.617894209632986</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.908008353372317</v>
+        <v>-4.81153606629811</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-5.86282735944387</v>
+        <v>-5.744120328802218</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.295186593921052</v>
+        <v>-5.943015972419225</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.192542209164273</v>
+        <v>-3.890487275390363</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.559786747905555</v>
+        <v>-3.384573523852133</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-3.448699276255347</v>
+        <v>-3.463409655360117</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-5.162004662004655</v>
+        <v>-5.164549075454481</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-4.218998722059055</v>
+        <v>-4.212622549019606</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-5.708454810495624</v>
+        <v>-5.552143154935358</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-3.800255737263605</v>
+        <v>-3.67855573925263</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-2.690333004218658</v>
+        <v>-2.558991918628038</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.925186864492382</v>
+        <v>-2.824777294820237</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-2.385648210516862</v>
+        <v>-2.145792003804182</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.947015622012529</v>
+        <v>-2.95796445668568</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.546454944040612</v>
+        <v>-1.611807825032464</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.01966</t>
+          <t>X &gt; 0.01951</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-23.00843604623829</v>
+        <v>-22.60877458803278</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-16.82147371415332</v>
+        <v>-16.6290004898845</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-15.41364296081277</v>
+        <v>-14.9654066540329</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-10.97808212877036</v>
+        <v>-10.6063900984324</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-8.937634977555263</v>
+        <v>-8.542766951982031</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-6.968490573636103</v>
+        <v>-6.730816898615522</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.658481061706873</v>
+        <v>-5.377461410848241</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.150978220745657</v>
+        <v>-3.92456935425686</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.109491038830953</v>
+        <v>-3.796640444572752</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.882406714867443</v>
+        <v>-4.59269193979209</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.592474056832508</v>
+        <v>-6.273581925187756</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.474398063455098</v>
+        <v>-6.059016007839091</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.422956955708045</v>
+        <v>-4.042792665407276</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.541129460858606</v>
+        <v>-3.312553145627085</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-3.006429816093245</v>
+        <v>-2.82053923005617</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-4.598921621784442</v>
+        <v>-4.411877089905779</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-3.937610130531297</v>
+        <v>-3.732978636660143</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-5.831715247871372</v>
+        <v>-5.431420471763033</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-4.422980924601113</v>
+        <v>-4.042789947161296</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-3.639713643460126</v>
+        <v>-3.24111935337433</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.98941686908023</v>
+        <v>-2.634395557299094</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-3.462877144604647</v>
+        <v>-2.905252795497034</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-2.87672666996248</v>
+        <v>-2.661618310218657</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.442034155987095</v>
+        <v>-1.258199574566831</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.02501</t>
+          <t>X &gt; 0.02486</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-21.71015404412504</v>
+        <v>-21.51328687480986</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-16.5993862880194</v>
+        <v>-16.62471938288537</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-15.46327075237605</v>
+        <v>-15.43442570971583</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-10.22088978422573</v>
+        <v>-9.914358470871242</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-7.579012762976483</v>
+        <v>-7.255931280897222</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-6.399490745613598</v>
+        <v>-5.999352437831206</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-6.301101293879341</v>
+        <v>-6.059140332416874</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.096725673955802</v>
+        <v>-2.93268822680588</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.050263367662986</v>
+        <v>-3.785151473984513</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.574422824794006</v>
+        <v>-4.336104929988167</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.285437809497758</v>
+        <v>-7.005046385972072</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-6.569162337323853</v>
+        <v>-6.301236183580627</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-5.204762215125243</v>
+        <v>-4.965147908874535</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.794968025480848</v>
+        <v>-3.742793735013521</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-3.455605088647438</v>
+        <v>-3.444555960035835</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-4.606854076928883</v>
+        <v>-4.844036254941663</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-4.491394655302869</v>
+        <v>-4.457720588235304</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-6.092494710745001</v>
+        <v>-5.81609488947533</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-5.1284736540102</v>
+        <v>-5.111436583898183</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-4.193498168231699</v>
+        <v>-4.161556021192148</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-3.987914660387261</v>
+        <v>-3.99370640492581</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-4.063760621796362</v>
+        <v>-3.823770887665411</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-3.649635036496342</v>
+        <v>-3.825234441602717</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.081357014030402</v>
+        <v>-2.271687161382388</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.03036</t>
+          <t>X &gt; 0.03022</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-19.89851582508841</v>
+        <v>-19.70116331347645</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-14.09832329828485</v>
+        <v>-14.15438722235105</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-15.22959388105817</v>
+        <v>-15.10420327546215</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-9.500830109089875</v>
+        <v>-9.294166449880123</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-7.689381317833458</v>
+        <v>-7.435578248516045</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.661924334190076</v>
+        <v>-5.449376349835035</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-7.201216104441912</v>
+        <v>-7.159092508409216</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.325581395348827</v>
+        <v>-1.366451976208076</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.130248059587977</v>
+        <v>-3.067791359206893</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.364702197162927</v>
+        <v>-2.339452610523793</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-5.782950247308698</v>
+        <v>-5.725754181285318</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.523238112295161</v>
+        <v>-4.477945891854169</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-4.415630948382038</v>
+        <v>-4.373325814182991</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.615817137269282</v>
+        <v>-2.792291582933174</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-2.348034508923909</v>
+        <v>-2.559811818476774</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-2.988215488215495</v>
+        <v>-3.218019994779056</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-2.504848674575676</v>
+        <v>-2.712144308943095</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-5.387467156174637</v>
+        <v>-5.28405280434859</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-4.245649849324387</v>
+        <v>-4.154956430861354</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-2.824236138121798</v>
+        <v>-2.720857790680419</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-2.440856380161897</v>
+        <v>-2.373668145719698</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-2.825344316879637</v>
+        <v>-2.448830667674983</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-2.064495717610903</v>
+        <v>-2.205196182396605</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.212420909038137</v>
+        <v>0.07168921355783198</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.03571</t>
+          <t>X &gt; 0.03558</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-19.54993802252288</v>
+        <v>-19.33210041232113</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-13.44532088147875</v>
+        <v>-13.56296965404003</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-14.12576417293398</v>
+        <v>-14.06578405668349</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-8.778112131770662</v>
+        <v>-8.64314866150675</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-8.73511472553006</v>
+        <v>-8.542766951982031</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.896633387917532</v>
+        <v>-5.754254398615522</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-7.237484019036827</v>
+        <v>-7.301216110096362</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.432045273675833</v>
+        <v>-1.591098959520011</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.911470639289647</v>
+        <v>-2.590989598708092</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.54370190467975</v>
+        <v>-2.635161394679308</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-6.452151768221249</v>
+        <v>-6.498264725939627</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.829760487258596</v>
+        <v>-4.895147432290635</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.671553732821941</v>
+        <v>-3.754400451997043</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.008994029173905</v>
+        <v>-1.371055566061735</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.903778548128507</v>
+        <v>-1.301330248698662</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-2.217788572750408</v>
+        <v>-2.619725477999303</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.206667541788946</v>
+        <v>-1.595786340852136</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-4.746622749426919</v>
+        <v>-4.736189243006216</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-4.149051979189622</v>
+        <v>-4.145787166236381</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.435488611969681</v>
+        <v>-2.427441322681155</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.832996611996784</v>
+        <v>-1.867066275189714</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-2.290521962718856</v>
+        <v>-2.31816864676906</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-2.178370668680259</v>
+        <v>-2.450474011114736</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.1100826743350112</v>
+        <v>-0.7329137572839031</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.04106</t>
+          <t>X &gt; 0.04094</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-20.77699734817375</v>
+        <v>-20.67225635774022</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-12.19158635309634</v>
+        <v>-12.58482986011077</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-12.22115469790197</v>
+        <v>-12.45063507311345</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-8.239273036593545</v>
+        <v>-8.41340764229205</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-8.105579941065699</v>
+        <v>-8.226002819428423</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-6.510163050742968</v>
+        <v>-6.217217361578484</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-7.519068063803303</v>
+        <v>-7.475262336774165</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.66520403685827</v>
+        <v>-1.298701298701303</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-4.925603647396386</v>
+        <v>-4.411513129757935</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-4.283424983810242</v>
+        <v>-3.81867573608838</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-9.669742700138883</v>
+        <v>-9.101996277039611</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-7.590001537549142</v>
+        <v>-7.063763416696091</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-5.411276811952433</v>
+        <v>-4.937914793406115</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.007836328656552</v>
+        <v>-2.871334040024408</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-3.192045976948016</v>
+        <v>-3.090525458946516</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-5.915194600028727</v>
+        <v>-5.76996218086758</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-2.731576191982498</v>
+        <v>-2.633101851851862</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-6.153952440827382</v>
+        <v>-5.543763734791227</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-5.938061059903056</v>
+        <v>-5.329301507645454</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-3.38154700348953</v>
+        <v>-2.799900247771653</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-2.976225872877357</v>
+        <v>-2.441418823226471</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-3.052071834286458</v>
+        <v>-2.516581345181756</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-3.935349322210634</v>
+        <v>-3.661835748792264</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-2.787668246657425</v>
+        <v>-2.898048817155811</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.04641</t>
+          <t>X &gt; 0.0463</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-21.61837520331961</v>
+        <v>-21.32040450588838</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-14.08798346234358</v>
+        <v>-14.34408911937003</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-12.15521599452064</v>
+        <v>-12.26544988792827</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-7.250192485873491</v>
+        <v>-7.302296531180936</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-7.024185205611779</v>
+        <v>-7.022299115724721</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-5.15182576108743</v>
+        <v>-5.198698843059965</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-6.764884074889544</v>
+        <v>-7.104891966403798</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.828406254105893</v>
+        <v>-1.298701298701303</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5.871664834903051</v>
+        <v>-6.170772389017195</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-6.079608759527119</v>
+        <v>-6.411268328680983</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-9.760351377252199</v>
+        <v>-10.02792220296553</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-7.779213775050479</v>
+        <v>-8.08228193521461</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-5.512545333432016</v>
+        <v>-5.863840719332046</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.451395139513942</v>
+        <v>-2.22318589187627</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-2.677720255276327</v>
+        <v>-3.460895829316875</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-4.924242424242429</v>
+        <v>-5.677369588274992</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-1.649068652128982</v>
+        <v>-2.447916666666671</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-5.163000265041084</v>
+        <v>-5.358578549606051</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-4.947108884116759</v>
+        <v>-5.144116322460278</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-1.919353983239638</v>
+        <v>-2.151752099623515</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-1.325536514842028</v>
+        <v>-1.608085489893142</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-1.969564294432942</v>
+        <v>-2.238803567403977</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-3.07820646506778</v>
+        <v>-3.661835748792264</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.679490278225373</v>
+        <v>-2.71286363197062</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.05176</t>
+          <t>X &gt; 0.05166</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-20.96110855134047</v>
+        <v>-20.42574361122748</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-16.06712717975564</v>
+        <v>-16.12619590147681</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-14.89076714381931</v>
+        <v>-14.78348740596579</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-9.067773450843752</v>
+        <v>-8.882383111267522</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-7.442779609665536</v>
+        <v>-7.209889303314903</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-7.255813423568156</v>
+        <v>-7.052955697316818</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-9.678948897964183</v>
+        <v>-9.796089657601492</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.720318237454102</v>
+        <v>-2.958152958152965</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-7.28409421343413</v>
+        <v>-7.375678593923404</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-6.741220415786408</v>
+        <v>-6.873028790441445</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-10.41452919467712</v>
+        <v>-10.49689767194101</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-8.061699650756694</v>
+        <v>-8.176077029009704</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-6.553282770244394</v>
+        <v>-6.693566549057884</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.127794898695164</v>
+        <v>-1.746995415685795</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-2.448189851904864</v>
+        <v>-3.078500446921495</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-3.84055789684929</v>
+        <v>-4.465248376153788</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.6632167556810629</v>
+        <v>-1.322375541125538</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-5.403819048906222</v>
+        <v>-5.351363542391042</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-5.187927667981896</v>
+        <v>-5.136901315245268</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-2.35207523549731</v>
+        <v>-2.324912272783685</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-2.232369747834205</v>
+        <v>-2.243006124813775</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-2.970467364872441</v>
+        <v>-2.967519296119704</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-4.316301703163013</v>
+        <v>-4.671936758893281</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-2.678487423947814</v>
+        <v>-3.535374454481442</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.05711</t>
+          <t>X &gt; 0.05702</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-21.03215146125805</v>
+        <v>-20.93393107593668</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-18.46837753497019</v>
+        <v>-18.28128718700287</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-14.10929513472582</v>
+        <v>-13.73887983961909</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-8.300510023733771</v>
+        <v>-7.80954290799253</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-7.187025133962202</v>
+        <v>-6.635825685773021</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-7.000058947864822</v>
+        <v>-6.478892079774937</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-7.412333454245392</v>
+        <v>-7.273974092007656</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.581055847903578</v>
+        <v>-2.506430767300344</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-5.459276695185949</v>
+        <v>-5.277052582253916</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.772338356623905</v>
+        <v>-4.62382871515441</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-8.147913750958331</v>
+        <v>-7.97478210634717</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-5.506955125209245</v>
+        <v>-5.352813336180795</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-5.170263177466829</v>
+        <v>-5.018430091312716</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.35876528829354</v>
+        <v>1.979712658848378</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.700621990712982</v>
+        <v>1.297558276963322</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.6461675579322588</v>
+        <v>-1.039688428854703</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>2.896385893325558</v>
+        <v>2.479619565217384</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-1.620219516377972</v>
+        <v>-2.001090626900734</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-2.139622253100711</v>
+        <v>-2.511266080914382</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>1.723694145102613</v>
+        <v>1.326508769941704</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.181147977136582</v>
+        <v>0.7590642685609694</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>1.105302015727482</v>
+        <v>0.6839017466056845</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.3903757772370966</v>
+        <v>-1.246376811594196</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>1.015273451021116</v>
+        <v>0.04075955643517659</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.06246</t>
+          <t>X &gt; 0.06238</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-19.24084711343197</v>
+        <v>-19.1426267281106</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-16.37562391178178</v>
+        <v>-16.18853356381447</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-11.41364296081277</v>
+        <v>-11.04322766570605</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-6.526596980255512</v>
+        <v>-6.03562986451427</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-6.062387452802788</v>
+        <v>-5.511188004613608</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-7.475421266705411</v>
+        <v>-6.954254398615525</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-7.047369950595758</v>
+        <v>-6.94933641084824</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.680420105026258</v>
+        <v>-1.654256854256857</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4.864739374724458</v>
+        <v>-4.726327944572752</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-4.831203437857724</v>
+        <v>-4.722379439792086</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-7.782950247308698</v>
+        <v>-7.650144425187754</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-4.835893199143797</v>
+        <v>-4.726726379659048</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-4.346152040193459</v>
+        <v>-4.241618497109819</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.008693552282061</v>
+        <v>3.510147441457065</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>3.350550254701503</v>
+        <v>2.827993059572009</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>1.505912786400593</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.437036299829614</v>
+        <v>4.885416666666664</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.4541468155206445</v>
+        <v>-0.04746743849494095</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.142969933636337</v>
+        <v>-0.6330052113491647</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.295908396656884</v>
+        <v>2.781581233709822</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>5.192386618934755</v>
+        <v>4.614136732329086</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>4.303532527444368</v>
+        <v>3.738974210373804</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.951990979763806</v>
+        <v>2.382608695652181</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>4.502174986703146</v>
+        <v>3.820469701362718</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.06781</t>
+          <t>X &gt; 0.06774</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-18.40275187533673</v>
+        <v>-18.30453149001536</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-14.92800486416273</v>
+        <v>-14.74091451619542</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-9.699357246527057</v>
+        <v>-9.328941951420333</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-5.650406504065039</v>
+        <v>-5.159439388323797</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-5.986196976612312</v>
+        <v>-5.434997528423132</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-7.703992695276838</v>
+        <v>-7.182825827186953</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-6.085831489057298</v>
+        <v>-6.073145934657767</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.556350626118061</v>
+        <v>-1.616161616161619</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6.322555751895671</v>
+        <v>-6.250137468382277</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-4.210856043316774</v>
+        <v>-4.189046106458754</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-6.821411785770238</v>
+        <v>-6.773953948997281</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-3.25400734306438</v>
+        <v>-3.241012093944768</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.454092486843585</v>
+        <v>-2.451142306633635</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>6.61347688166876</v>
+        <v>5.872052203361825</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5.955333584088201</v>
+        <v>5.189897821476769</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>3.637099146807891</v>
+        <v>2.894058983153577</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>7.386677155461484</v>
+        <v>6.599702380952372</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>2.427467519601457</v>
+        <v>1.704913513886019</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>1.672485114118018</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>4.771952283309361</v>
+        <v>4.038724090852675</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>7.142027474566625</v>
+        <v>6.328422446614795</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.095307726749759</v>
+        <v>5.300878972278561</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>4.428034866416283</v>
+        <v>3.639751552795033</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>6.293950186008537</v>
+        <v>5.382374463267475</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.07316</t>
+          <t>X &gt; 0.0731</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-19.59829392194261</v>
+        <v>-19.50007353662124</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-16.7415813585903</v>
+        <v>-16.55449101062298</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-10.73279189698299</v>
+        <v>-10.36237660187626</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-8.254256554723597</v>
+        <v>-7.763289438982355</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-8.59004702727087</v>
+        <v>-8.03884757908169</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-8.403080841173491</v>
+        <v>-7.881913973083606</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-5.43446672478931</v>
+        <v>-5.485506623614199</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3363340835208746</v>
+        <v>-0.4712781308526104</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.520653353219082</v>
+        <v>-3.534838582870627</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.067762577642661</v>
+        <v>-1.13940071638784</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-5.094778204297945</v>
+        <v>-5.122484850719665</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-2.147721156133045</v>
+        <v>-2.207577443488837</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.120345588580548</v>
+        <v>-1.194809986471519</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.898407232027552</v>
+        <v>6.003764462733663</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>7.327220456186133</v>
+        <v>6.385439868082649</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>4.660737812911719</v>
+        <v>3.755254525200179</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>8.874646762890777</v>
+        <v>7.906693262411345</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.421979972113064</v>
+        <v>3.51849000831357</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.550914831298272</v>
+        <v>2.669122448225302</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>6.998630206483682</v>
+        <v>6.075198254986418</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>8.629997081995917</v>
+        <v>7.635413328073767</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>7.467194598847691</v>
+        <v>6.49642101888444</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>6.654712789590604</v>
+        <v>5.676225716928776</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>7.665837058106469</v>
+        <v>6.577916509873354</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.07851</t>
+          <t>X &gt; 0.07846</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-16.60381007639493</v>
+        <v>-16.50558969107356</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-14.46945107227561</v>
+        <v>-14.2823607243083</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-9.73463061513376</v>
+        <v>-9.364215320027036</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-6.743880930872798</v>
+        <v>-6.252913815131556</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-7.079671403420072</v>
+        <v>-6.528471955230891</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-5.658137316088123</v>
+        <v>-5.136970447998237</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-5.797369950595765</v>
+        <v>-5.932052460230956</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1744186046511587</v>
+        <v>-0.0641333974667404</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-2.284094213434123</v>
+        <v>-2.405340290251765</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.6929901105293794</v>
+        <v>0.502311918232607</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.78295024730869</v>
+        <v>-2.929156770866769</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.5616996507567009</v>
+        <v>-0.7366029228689328</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.4348617176128116</v>
+        <v>-0.6169271390851279</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>9.344059405940598</v>
+        <v>9.011382009358307</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>8.68591610836004</v>
+        <v>8.329227627473252</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>5.530303030303031</v>
+        <v>5.186827942589204</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>11.64638589332556</v>
+        <v>11.25578703703703</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>7.791545189504376</v>
+        <v>7.419199228171721</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>6.757436570428702</v>
+        <v>6.399093554082938</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>10.69428238039673</v>
+        <v>10.31738370284562</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>12.6517362124307</v>
+        <v>12.21907500393402</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>11.3258902510216</v>
+        <v>10.90934458074417</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>10.35036496350365</v>
+        <v>9.918411164787976</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>11.52453271028038</v>
+        <v>10.99084007173308</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.08386</t>
+          <t>X &gt; 0.08382</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-13.06113696850443</v>
+        <v>-12.11405529953917</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-11.94663840453541</v>
+        <v>-10.93139070667161</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-3.239729917334515</v>
+        <v>-3.614656237134625</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-3.952683936777255</v>
+        <v>-4.207058435942848</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-8.636300496281045</v>
+        <v>-7.339759433185037</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-7.000058947864822</v>
+        <v>-5.754254398615522</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.165017009419287</v>
+        <v>-2.263622125133956</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>2.968536251709985</v>
+        <v>1.717171717171716</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.53943519833058</v>
+        <v>0.4165291982843868</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.178284228176437</v>
+        <v>3.906191988779341</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>1.040579164456013</v>
+        <v>-0.107287282330617</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3.703006231596248</v>
+        <v>2.473273620340947</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>4.050432400034246</v>
+        <v>2.786952931461606</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>14.12347117064648</v>
+        <v>13.96729029859991</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>13.46532787306592</v>
+        <v>13.28513591671486</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>9.647950089126553</v>
+        <v>9.560725649820242</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>15.39638589332556</v>
+        <v>15.17113095238096</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>12.35036871891614</v>
+        <v>10.75253256150506</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>11.09567186454635</v>
+        <v>9.538423360079406</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>14.22369414510261</v>
+        <v>14.03872409085267</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>18.09291268301893</v>
+        <v>17.75699387518624</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>16.54647848631571</v>
+        <v>16.25325992465951</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>15.35036496350365</v>
+        <v>15.06832298136647</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>16.74512094557449</v>
+        <v>16.33475541564842</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2461 +5824,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.0713</t>
+          <t>X &lt; -0.0716</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>17.37364564019122</v>
+        <v>17.88594470046083</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.44466594329068</v>
+        <v>6.211466436185532</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.15157443049157</v>
+        <v>13.52820090572252</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.54006968641114</v>
+        <v>10.07865584977144</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.957902402269674</v>
+        <v>2.66024056681497</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.695593226048217</v>
+        <v>1.388602744241616</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.372919904476703</v>
+        <v>2.022092160580335</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.8038422649140529</v>
+        <v>-1.139971139971145</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.6869202793194944</v>
+        <v>0.4165291982843868</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.812555327920691</v>
+        <v>2.47762056020791</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.261211116873916</v>
+        <v>-1.535858710902041</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.539960520321912</v>
+        <v>-1.812440665373337</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-1.213847224859187</v>
+        <v>-1.498761354252686</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.434926101305777</v>
+        <v>-1.746995415685795</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.8054813257513516</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1.399868247694343</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-1.632599613920817</v>
+        <v>-1.971726190476197</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>1.161110406895688</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>1.377001787820014</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>3.01312296010687</v>
+        <v>2.610152662281251</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>6.328206800665988</v>
+        <v>4.899851018043378</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>6.252360839256887</v>
+        <v>4.824688496088093</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>5.056247316444825</v>
+        <v>3.639751552795033</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.451003298515666</v>
+        <v>6.334755415648424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.06595</t>
+          <t>X &lt; -0.06624</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>19.19865905940754</v>
+        <v>19.29687944472891</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.987339051181181</v>
+        <v>9.174429399148494</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>14.95672740955759</v>
+        <v>15.32714270466432</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.54006968641114</v>
+        <v>11.03103680215239</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.031439707691042</v>
+        <v>4.582639155880223</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.218405893788422</v>
+        <v>4.739572761878307</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.446457209898071</v>
+        <v>3.944490749645588</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.5354579385587144</v>
+        <v>-0.0641333974667404</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.4939707566440106</v>
+        <v>0.0637955122173679</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.436817271023209</v>
+        <v>2.97144772070174</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2417411107159992</v>
+        <v>-0.460020968397636</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.03700829273199702</v>
+        <v>-0.7366029228689328</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.07439754164644086</v>
+        <v>-0.6169271390851279</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.087886566434427</v>
+        <v>0.3694067007163184</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>4.133446972557572</v>
+        <v>3.390956022534972</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>2.258698092031423</v>
+        <v>1.483124238885502</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.8902130538193873</v>
+        <v>0.1446759259259167</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>2.019940251232768</v>
+        <v>1.246359721998893</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>2.235831632157094</v>
+        <v>1.460821949144666</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>4.89181324459426</v>
+        <v>4.144544196672783</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>7.651736212430698</v>
+        <v>6.046235497761188</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>8.825890251021598</v>
+        <v>7.205640877040459</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>6.600364963503651</v>
+        <v>4.980139559849711</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>6.524532710280376</v>
+        <v>6.052568466794817</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.0606</t>
+          <t>X &lt; -0.06088</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>17.63574863124888</v>
+        <v>17.73396901657025</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8.790333535026726</v>
+        <v>8.977423882994039</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>14.79912299663403</v>
+        <v>14.10570850450673</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.830849828255126</v>
+        <v>9.257987156762326</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.175910419537644</v>
+        <v>3.663280080492775</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.362876605635023</v>
+        <v>3.82021368649086</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.590927921744672</v>
+        <v>3.025131674258141</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.9426026719445844</v>
+        <v>-1.535107918086645</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.9011154900298806</v>
+        <v>-1.407179008402537</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.517458195635761</v>
+        <v>0.9882588580802505</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.3361417366703918</v>
+        <v>-0.8671657017835059</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.6148911401183881</v>
+        <v>-1.143747656254803</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3896063674935704</v>
+        <v>-0.1309801992374844</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.232357278281029</v>
+        <v>0.6846155265634479</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>2.701873555168547</v>
+        <v>2.130120719146475</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.168600902643462</v>
+        <v>0.5637651634980543</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.02914602156806012</v>
+        <v>-0.6039450354609954</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.9298430618448066</v>
+        <v>0.3270006466114452</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.145734442769132</v>
+        <v>0.5414628737572187</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>3.460239827205235</v>
+        <v>2.883708893284286</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>5.743134061893066</v>
+        <v>4.443923966371642</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>5.432591231650399</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>4.866493995761715</v>
+        <v>3.548566142460686</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>5.865930559742743</v>
+        <v>5.514086722639313</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.05525</t>
+          <t>X &lt; -0.05552</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>110</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>19.332125859541</v>
+        <v>19.18464599916214</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.18653825038038</v>
+        <v>9.847830072549165</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>13.95572640855659</v>
+        <v>14.04768142520305</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.639168785510265</v>
+        <v>9.818915590031182</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.699774709359374</v>
+        <v>4.997902904477307</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.886740895456754</v>
+        <v>5.154836510475391</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.213891310665495</v>
+        <v>4.359754498242673</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3320762623088243</v>
+        <v>0.4184704184704131</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.274464345124429</v>
+        <v>0.5463993281545214</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.303350470889747</v>
+        <v>1.568529651117004</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.7756083112498615</v>
+        <v>0.02258284753951756</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4968589078018653</v>
+        <v>-0.2539991069317793</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2745977418466481</v>
+        <v>-0.4598003152916448</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.855320667201852</v>
+        <v>1.110147441457066</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2.098078270522201</v>
+        <v>1.337083968662924</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.01023751023750918</v>
+        <v>-0.8288847397901478</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-1.045055548115883</v>
+        <v>-1.841856060606062</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.6519055498647433</v>
+        <v>-0.1565583475858432</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.8677969307890692</v>
+        <v>0.05790387955993026</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.955543641657982</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>2.879008939703432</v>
+        <v>1.52322764142</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>4.621344796476144</v>
+        <v>3.266246937646535</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>2.168546781685464</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>4.819987255734922</v>
+        <v>4.256833337726349</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.0499</t>
+          <t>X &lt; -0.05017</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>20.00256373928121</v>
+        <v>20.30352711804326</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>11.14065515798566</v>
+        <v>11.59608182080092</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>15.90418649655157</v>
+        <v>15.72600310352473</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.54006968641114</v>
+        <v>10.51821628933187</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.87869781851505</v>
+        <v>7.934965841540233</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.065664004612429</v>
+        <v>8.091899447538317</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.96813392537323</v>
+        <v>4.989125127613299</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.8139534883720998</v>
+        <v>0.838050838050826</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.181022065635631</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.632912591149527</v>
+        <v>1.708389790977144</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3565846364122365</v>
+        <v>0.4421632671199305</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.853029031413854</v>
+        <v>0.9348120818794143</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.28025456145695</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.059175685010359</v>
+        <v>1.110147441457066</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.176226185879415</v>
+        <v>1.197223828802777</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.554968287526421</v>
+        <v>-0.5491644600698606</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.6888854245038942</v>
+        <v>-0.6530448717948687</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.7566614685741371</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.972552849498463</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.384204861016876</v>
+        <v>0.4123504644790543</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.3079862124306985</v>
+        <v>-0.15509403690168</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>3.357140251021598</v>
+        <v>2.846666518066108</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.506614963503651</v>
+        <v>0.01337792642141267</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>3.555782710280376</v>
+        <v>3.697392778285788</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.04455</t>
+          <t>X &lt; -0.04481</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>19.7357762631914</v>
+        <v>19.83399664851277</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>13.55684362068575</v>
+        <v>13.74393396865307</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>17.9629804158106</v>
+        <v>17.68404506156669</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>11.40587055221202</v>
+        <v>11.24748701860261</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.472677482262142</v>
+        <v>8.374526281100685</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>8.659643668359521</v>
+        <v>8.531459887098769</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5.290292387066579</v>
+        <v>5.138975277463452</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.765327695560259</v>
+        <v>1.587301587301582</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.105516176176266</v>
+        <v>3.013931795686986</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.332600500139776</v>
+        <v>2.217880300467648</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.307958843600396</v>
+        <v>1.191414016370686</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.0292094401524</v>
+        <v>0.9148320618993893</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.854099321348222</v>
+        <v>1.747991892500572</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.282371094252291</v>
+        <v>2.1491084804181</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2.922929095373028</v>
+        <v>2.765655397234347</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2.218614718614724</v>
+        <v>2.028258117352706</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.7859962829359546</v>
+        <v>0.6256764069264023</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2.629207527166713</v>
+        <v>2.440844249816756</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.195748258740394</v>
+        <v>2.005955827611871</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.733243419357763</v>
+        <v>1.571191623320217</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.9360499379208918</v>
+        <v>0.3543964725888245</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>4.781772603962771</v>
+        <v>4.175337846737435</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>2.441868231477507</v>
+        <v>1.821569734613213</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>4.326820291979722</v>
+        <v>4.256833337726349</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.0392</t>
+          <t>X &lt; -0.03945</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>20.70470262478793</v>
+        <v>20.00234681686295</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>13.56364310392502</v>
+        <v>12.87813310285219</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>15.26698531143854</v>
+        <v>14.79804217556379</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9.318429197754952</v>
+        <v>9.443735214850804</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.411958096935436</v>
+        <v>7.58087548744988</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>8.122484492456891</v>
+        <v>8.796010151649021</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.303415389718374</v>
+        <v>6.942727081215246</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.407402897844882</v>
+        <v>3.463203463203456</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.543130917455919</v>
+        <v>5.178433960189153</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4.246655031995353</v>
+        <v>4.382382464969815</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.997154464733185</v>
+        <v>3.596416421373092</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.671284642437023</v>
+        <v>2.790733937801264</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.165923622701321</v>
+        <v>3.792243936752605</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.944844746254731</v>
+        <v>3.544009875319496</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>4.333821867522339</v>
+        <v>4.449157080736036</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>3.881088370617164</v>
+        <v>4.481360570455159</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.129370186519274</v>
+        <v>2.261078042328037</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>3.642330529818508</v>
+        <v>4.24459605356855</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.811101491894675</v>
+        <v>3.400857222513267</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>2.474387092438612</v>
+        <v>3.086343138471726</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>1.204367791378068</v>
+        <v>1.460697578889935</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>3.760100777337385</v>
+        <v>4.560138231537827</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>2.981943910872069</v>
+        <v>2.687370600414084</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>3.958743236596163</v>
+        <v>4.641633722526741</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.03385</t>
+          <t>X &lt; -0.03409</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>21.96890898412901</v>
+        <v>21.55941408821594</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>16.34957934025074</v>
+        <v>16.41554806883859</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>16.53757655138235</v>
+        <v>16.26824774413002</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11.75958188153311</v>
+        <v>11.98732095515786</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>10.20427921386387</v>
+        <v>9.662582487189667</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>9.578237269879963</v>
+        <v>8.999843962040224</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7.993280455908298</v>
+        <v>7.385089818659964</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.869540555870678</v>
+        <v>4.621152981808713</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.317531802826025</v>
+        <v>5.158917957066592</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.544616126789535</v>
+        <v>4.362866461847254</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.631683899032765</v>
+        <v>5.45477360759913</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.165942625666077</v>
+        <v>5.997863784275374</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.668796818972559</v>
+        <v>6.522315929119678</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>7.260726072607255</v>
+        <v>7.09375399883411</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>6.602582775026697</v>
+        <v>6.821435682522825</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>6.383961566888402</v>
+        <v>6.563067570194946</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.811020039667021</v>
+        <v>4.00017076502732</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>5.332195596008432</v>
+        <v>5.506630922160809</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>4.735078846851472</v>
+        <v>4.901421018159041</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>4.921924656819499</v>
+        <v>5.116007463218025</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>3.417042334879682</v>
+        <v>3.319054765115972</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>5.382012700001191</v>
+        <v>5.293072571029548</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>5.656487412483244</v>
+        <v>5.536707056307925</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>6.396981689872213</v>
+        <v>6.604076258739759</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.0285</t>
+          <t>X &lt; -0.02873</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>20.66255845932346</v>
+        <v>20.38375363998755</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>14.44542871979716</v>
+        <v>14.51915874387784</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>14.24579976364544</v>
+        <v>14.40121677873839</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>9.817675465564918</v>
+        <v>10.10511087622648</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>8.444444845333848</v>
+        <v>8.594984834892571</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>7.38917500658652</v>
+        <v>7.825992514964732</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.064431291640261</v>
+        <v>5.179058650880151</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.922865809620113</v>
+        <v>3.022286355619684</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.896030010168353</v>
+        <v>4.076141191229723</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.880878309287141</v>
+        <v>2.354163770084455</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.397173976293786</v>
+        <v>3.860966685923358</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.807865566634618</v>
+        <v>3.275742756143423</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.237498530834394</v>
+        <v>3.395418539927213</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.016419654387803</v>
+        <v>3.147184478494104</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.737158344384888</v>
+        <v>2.156388121300402</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>2.0209862601167</v>
+        <v>2.409050164811418</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.5974029265502168</v>
+        <v>-0.1639660493827222</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.782228419318045</v>
+        <v>2.172285647924809</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.1347657629752845</v>
+        <v>0.5348960232187352</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.253288591576847</v>
+        <v>1.67540839420365</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.5878732840817875</v>
+        <v>0.9856537601928608</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.7581332416758</v>
+        <v>2.148881331116833</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>1.409554994656297</v>
+        <v>1.773320769955589</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.89135514018691</v>
+        <v>3.468766914985011</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.02315</t>
+          <t>X &lt; -0.02337</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>21.17396770138284</v>
+        <v>20.41314722766335</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>14.66635139686019</v>
+        <v>14.93067825884563</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>14.70981382931068</v>
+        <v>14.33948838367667</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>11.52772400739882</v>
+        <v>11.27795038239931</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>9.626721458088312</v>
+        <v>9.273997180571584</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>8.328539129334203</v>
+        <v>8.690190045828921</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>6.071441930592364</v>
+        <v>6.166712971867817</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.813032466037306</v>
+        <v>3.88648388648388</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.844618657852998</v>
+        <v>5.00206711715564</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.586554466965019</v>
+        <v>2.97144772070174</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.850713119027937</v>
+        <v>4.231337056293725</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.581864705678946</v>
+        <v>2.967100780834777</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>3.933950163575311</v>
+        <v>3.580603725112397</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3.46534653465347</v>
+        <v>3.332369663679287</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>2.312153732122418</v>
+        <v>2.650215281794232</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>2.659015901590159</v>
+        <v>2.717692140120064</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.2973759923354535</v>
+        <v>0.3915895061728421</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>2.915307565741998</v>
+        <v>2.974754783727285</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.141099936765336</v>
+        <v>2.201562689885407</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>3.31804475663435</v>
+        <v>3.403803455932042</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>2.186475666524991</v>
+        <v>2.247800098665721</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>3.351324494197776</v>
+        <v>3.410261339086674</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>3.37766024886345</v>
+        <v>3.653895824365051</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>3.549966953456554</v>
+        <v>3.986806335026081</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.0178</t>
+          <t>X &lt; -0.01801</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>20.70372217495756</v>
+        <v>20.2978185409061</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>13.62737234289986</v>
+        <v>14.05533260718926</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>11.81482145866288</v>
+        <v>11.99587847954535</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>9.416474180793173</v>
+        <v>9.541278887813476</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>7.702715736690649</v>
+        <v>7.589743094082863</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.139212879636055</v>
+        <v>7.560456960788578</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.429177891805736</v>
+        <v>5.577529260793554</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.400497403900694</v>
+        <v>4.526340160668518</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4.817219107391381</v>
+        <v>5.027403398710831</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.293834388202924</v>
+        <v>3.485083246775069</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.505980334304816</v>
+        <v>4.69015408227493</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.968375537213234</v>
+        <v>3.853870635266325</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.10085256810148</v>
+        <v>4.909783372049048</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.503833842030829</v>
+        <v>4.287717534915011</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>4.785540168510416</v>
+        <v>4.727058480132762</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>4.628047391205286</v>
+        <v>4.727614835401013</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>2.802400930919546</v>
+        <v>2.941491433021802</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>4.953199324842714</v>
+        <v>5.051597982065815</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.853301232082842</v>
+        <v>3.957648994258314</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>4.228116966862892</v>
+        <v>4.664727301125552</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>3.428572370622796</v>
+        <v>3.841153617882554</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>4.482669912038538</v>
+        <v>4.891694660655226</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>5.322116375933035</v>
+        <v>5.698180928297582</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>5.622931956984708</v>
+        <v>6.098893716372096</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.01245</t>
+          <t>X &lt; -0.01265</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>17.7690745575863</v>
+        <v>17.43776542875215</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>11.29852752424955</v>
+        <v>11.0020423524159</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9.860508475218559</v>
+        <v>9.701202216338508</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>8.364264638543446</v>
+        <v>8.060307225918237</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>6.544148494909628</v>
+        <v>6.343071497352319</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>6.731114681007007</v>
+        <v>6.762128301253412</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>5.305571225874829</v>
+        <v>5.130453615398473</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.765921872625022</v>
+        <v>4.563065980388814</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.938128008788091</v>
+        <v>4.822228485873445</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.034493378503235</v>
+        <v>3.763709799053053</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>4.700709883410255</v>
+        <v>4.560879196859489</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.765525480133356</v>
+        <v>4.546764433989239</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5.998384355685623</v>
+        <v>5.747343395137214</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.039085583951064</v>
+        <v>5.761921423060222</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>5.642722391082565</v>
+        <v>5.342579130531284</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>5.405794511299106</v>
+        <v>5.50966501531677</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>4.485507780612579</v>
+        <v>4.617348335523431</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>5.42915986840346</v>
+        <v>5.667118632464337</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.727620056667241</v>
+        <v>4.961738546863714</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>4.521281069780734</v>
+        <v>4.602633865288766</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>4.193730963086871</v>
+        <v>4.382252674358064</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>4.511585789079341</v>
+        <v>4.834099375064177</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>5.310994884763488</v>
+        <v>5.472990777338602</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>5.235162631540213</v>
+        <v>5.310851783049138</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.007097</t>
+          <t>X &lt; -0.007291</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1147</v>
+        <v>1130</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>15.19595844212359</v>
+        <v>15.43804111020223</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>8.697987199329333</v>
+        <v>9.27215245201667</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>7.086357039187227</v>
+        <v>7.808885010350288</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.158125241966708</v>
+        <v>5.720003938302625</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.354293694026055</v>
+        <v>4.828248615104705</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.888783772391037</v>
+        <v>5.425323066173213</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.682430223166193</v>
+        <v>4.067403677257481</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.491099751480007</v>
+        <v>3.938694687593355</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.27194401419402</v>
+        <v>3.537989236043991</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.846552230425118</v>
+        <v>2.741937740824653</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.207492845653945</v>
+        <v>3.366595662917966</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.764387305765048</v>
+        <v>3.794859523424648</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.119486108474149</v>
+        <v>4.233161044336391</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4.072320275505817</v>
+        <v>4.161293825936781</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>3.414176977925258</v>
+        <v>3.831873130118744</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>3.889746024210773</v>
+        <v>4.393177148938406</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.320667877659766</v>
+        <v>3.936563051146379</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>4.347245798729801</v>
+        <v>4.773696582669089</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.312314619209189</v>
+        <v>3.809007145226296</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>3.412052415239927</v>
+        <v>3.725750845017245</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>2.837002123503062</v>
+        <v>3.036771568757025</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.848340120245666</v>
+        <v>2.96160904680174</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>3.645918581637908</v>
+        <v>3.8241648406566</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.872614663201034</v>
+        <v>3.186841382778645</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001747</t>
+          <t>X &lt; -0.001932</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1690</v>
+        <v>1684</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>11.85004059967797</v>
+        <v>11.78992182986467</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>6.318493735277038</v>
+        <v>6.635494704736765</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>6.174592333304872</v>
+        <v>6.300319770946864</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.755755960920951</v>
+        <v>4.824004784866993</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.750090475390266</v>
+        <v>4.784156721373428</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4.171900687385232</v>
+        <v>4.233960097554188</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.399952003494882</v>
+        <v>3.474248494812137</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.334018133508643</v>
+        <v>3.287252579705395</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.057685397644242</v>
+        <v>2.978686804689787</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.756189874819306</v>
+        <v>2.713608760797882</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.735611921224013</v>
+        <v>2.785274701140459</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.023206009620658</v>
+        <v>2.980947764378726</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.644046836959461</v>
+        <v>2.551529760421182</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.186979759922906</v>
+        <v>2.162156897721843</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2.509705954877155</v>
+        <v>2.484730648224485</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>2.727585960013606</v>
+        <v>2.668776676262752</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.180201605079844</v>
+        <v>2.246363412228796</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>2.998400981466553</v>
+        <v>2.978701892470127</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.772959929387895</v>
+        <v>1.808227016138986</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.959805739355922</v>
+        <v>1.999601387829557</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.749369348525377</v>
+        <v>1.764789164120309</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.791866582382539</v>
+        <v>1.808250604205355</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>2.30302768539714</v>
+        <v>2.38498258289254</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.753822651108784</v>
+        <v>1.90313003390429</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.003604</t>
+          <t>X &lt; 0.003427</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2189</v>
+        <v>2198</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>8.881838911976381</v>
+        <v>8.742829459784616</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.352564921627206</v>
+        <v>5.361940905232075</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.640828214856768</v>
+        <v>4.676483003371708</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.655518317066324</v>
+        <v>3.677209195160231</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.074397288341622</v>
+        <v>3.130403315458722</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.943470649734188</v>
+        <v>2.925673268653917</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.580241311892884</v>
+        <v>2.564186881779527</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.329121012647526</v>
+        <v>2.304494841808264</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.761360332020416</v>
+        <v>1.780459385743995</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.761171928711192</v>
+        <v>1.753638659755424</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.880533154237462</v>
+        <v>1.871630133436049</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.856407719579977</v>
+        <v>1.776125589557786</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.21568448174996</v>
+        <v>1.095700343469886</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.9035723781754683</v>
+        <v>0.738602357632864</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.274713922567685</v>
+        <v>1.126089161113264</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.395906674949956</v>
+        <v>1.261405921929089</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.152994826780436</v>
+        <v>1.048756049606773</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.531855267023751</v>
+        <v>1.397108140261309</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.5439329207936652</v>
+        <v>0.4129530084510122</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.3474088066860901</v>
+        <v>0.2456430238052363</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.1973983128873158</v>
+        <v>0.06868218687454686</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.0576170669192706</v>
+        <v>-0.006480335080738087</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.8346043422153997</v>
+        <v>0.8098938252565446</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.3476254466896904</v>
+        <v>0.3565934502253185</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.008955</t>
+          <t>X &lt; 0.008787</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2560</v>
+        <v>2563</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>6.685239843089775</v>
+        <v>6.759464673903345</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>4.082628515402682</v>
+        <v>4.018517966600101</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.887327912973632</v>
+        <v>3.832741326542013</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.902529233336715</v>
+        <v>2.969021298276431</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.356571366156032</v>
+        <v>2.3672144769684</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.25547651798172</v>
+        <v>2.252725050783468</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.988774627717497</v>
+        <v>2.023200439423285</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.733516582878224</v>
+        <v>1.75706975551816</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.642393534523862</v>
+        <v>1.713718621201402</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.530699173150929</v>
+        <v>1.639111243437725</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.983586717671848</v>
+        <v>2.089661400054965</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.84487878443209</v>
+        <v>1.851914397039977</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.134452924131736</v>
+        <v>1.109741254249933</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.069137287560544</v>
+        <v>1.040190193108835</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1.252628223669738</v>
+        <v>1.236702235310737</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.715026335057516</v>
+        <v>1.666076541635555</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.371044762721276</v>
+        <v>1.352342736705573</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.758003847850709</v>
+        <v>1.749029252824641</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.178525138512974</v>
+        <v>1.16948700048885</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.8426040041281908</v>
+        <v>0.7842302403323416</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.9092528075107538</v>
+        <v>0.8635521649089739</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.7399527510216046</v>
+        <v>0.7339059842529494</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.131614963503651</v>
+        <v>1.157023672251249</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.8604702102803756</v>
+        <v>0.9013904973049662</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.01431</t>
+          <t>X &lt; 0.01415</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2775</v>
+        <v>2785</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>5.098407900894685</v>
+        <v>5.0669989403386</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.31566953142854</v>
+        <v>3.3084707157861</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.952534036679161</v>
+        <v>2.930372048885459</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.081288324403985</v>
+        <v>2.052561359174632</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.76636837365831</v>
+        <v>1.726213851203667</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.472067972892873</v>
+        <v>1.383504345138938</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.094667352130209</v>
+        <v>1.072941347095352</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.052603032351193</v>
+        <v>1.002886002886001</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.115044336458183</v>
+        <v>1.080031469503709</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.131791259129528</v>
+        <v>1.126655585225784</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.355290327197586</v>
+        <v>1.348353965945606</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.456978510162841</v>
+        <v>1.393545340040625</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.9660545597856824</v>
+        <v>0.9077377260661379</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.8168405773383753</v>
+        <v>0.788143863639533</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.7914157489064095</v>
+        <v>0.8073774547044366</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.191935536595729</v>
+        <v>1.211280608645879</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.9719254616708852</v>
+        <v>0.9857031996179515</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.320692364747266</v>
+        <v>1.304306119369627</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.874607196778598</v>
+        <v>0.859467906930405</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.6150601981857093</v>
+        <v>0.5935568522110799</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.6704682009033149</v>
+        <v>0.6571783392157471</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.5443587194900701</v>
+        <v>0.5317980352751306</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.6746892878279667</v>
+        <v>0.7251786884734273</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.3466047823524434</v>
+        <v>0.4050298449892935</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.01966</t>
+          <t>X &lt; 0.01951</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2922</v>
+        <v>2937</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.94418690017347</v>
+        <v>3.914255246864037</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.880449582604072</v>
+        <v>2.909707302220717</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.633311785699654</v>
+        <v>2.587906006036761</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.872041549356467</v>
+        <v>1.826299069495882</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.521950306815867</v>
+        <v>1.502488366408734</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.183706798689684</v>
+        <v>1.151635919597069</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.9567172428647268</v>
+        <v>0.9176463185794574</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.6982686898300372</v>
+        <v>0.666068348995168</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.691365909265258</v>
+        <v>0.6440549764709615</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.8246812117908817</v>
+        <v>0.782705305970623</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.118823286115585</v>
+        <v>1.074711458162533</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.098996357431638</v>
+        <v>1.035498103216497</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.7468788967216611</v>
+        <v>0.6867397118453979</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.5940594059405981</v>
+        <v>0.5604358703678258</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.5026624381654372</v>
+        <v>0.4755151233873463</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.7762046696472851</v>
+        <v>0.751606076693875</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.6628703483990108</v>
+        <v>0.6340579710144922</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.9887427288071819</v>
+        <v>0.929223013424874</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.7467528097449474</v>
+        <v>0.6882728307990362</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.6122030370314775</v>
+        <v>0.54914328743304</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.5006927639188987</v>
+        <v>0.4440687051182053</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.5823926466410398</v>
+        <v>0.5253641389209278</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.4804128758924264</v>
+        <v>0.4830852102879817</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.2334649484733973</v>
+        <v>0.2391281964257104</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.02501</t>
+          <t>X &lt; 0.02486</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3024</v>
+        <v>3040</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.868028626213004</v>
+        <v>2.858418340472028</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.190111043824928</v>
+        <v>2.238908448599773</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.034564865560128</v>
+        <v>2.048275602267807</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.340508282902377</v>
+        <v>1.311084748104228</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.9907221227154679</v>
+        <v>0.9887465931627162</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.8345194837883412</v>
+        <v>0.7859679689449806</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.8196478242561227</v>
+        <v>0.7944647013532702</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.3958542319149174</v>
+        <v>0.3774185384132949</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.522229897237807</v>
+        <v>0.491347996507443</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.5920840149774804</v>
+        <v>0.5653743257612831</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.9513938528890549</v>
+        <v>0.9221451260733033</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.8568628286366504</v>
+        <v>0.828450553499529</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.6766158549465544</v>
+        <v>0.6504169011202663</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4885185088429722</v>
+        <v>0.4871966217849319</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.4439992492376419</v>
+        <v>0.4476716427140204</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.5963096309631055</v>
+        <v>0.6349663697302574</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.5812653915097741</v>
+        <v>0.5834803358494653</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.7935266954488895</v>
+        <v>0.765664537867508</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.666009414829098</v>
+        <v>0.6714282861877834</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.5422665178719441</v>
+        <v>0.5442619170212524</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.5153725760670653</v>
+        <v>0.5221222729140393</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.5256257007570539</v>
+        <v>0.5323995884145702</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.4694125825512643</v>
+        <v>0.5326909054515809</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.261305197052863</v>
+        <v>0.3244170697837632</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.03036</t>
+          <t>X &lt; 0.03022</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3101</v>
+        <v>3120</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.064281091696238</v>
+        <v>2.041210370203117</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.45881020171614</v>
+        <v>1.494725506841164</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.57801836054707</v>
+        <v>1.562948711243962</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.9795948708834104</v>
+        <v>0.9567268233838249</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.7905008655540797</v>
+        <v>0.7947693066320198</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.5785113175642564</v>
+        <v>0.5554970354188953</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.7375417669002289</v>
+        <v>0.7346929165346054</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.1246433959164222</v>
+        <v>0.1291615130900752</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.3130789314421918</v>
+        <v>0.3071648783937491</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.2334785424059902</v>
+        <v>0.2312899922436458</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5905630924534435</v>
+        <v>0.585795568428594</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.4592006707867213</v>
+        <v>0.4553936714265205</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.4484608941594672</v>
+        <v>0.4449353195621697</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.2595467008907448</v>
+        <v>0.2794765149394891</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.2319264043703342</v>
+        <v>0.2554139608184158</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.2985682378987775</v>
+        <v>0.3243354415630293</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.2482854425850576</v>
+        <v>0.2714096311693837</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.5491941428054972</v>
+        <v>0.5414001238851043</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.4301169827998308</v>
+        <v>0.4229947886508327</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.2817783520370796</v>
+        <v>0.2724903246189143</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.2420005580141975</v>
+        <v>0.2362949135650823</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.2822752881064048</v>
+        <v>0.2763220643135824</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.2020257180989447</v>
+        <v>0.2507278882186625</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.03504484534684593</v>
+        <v>0.0114953423883577</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.03571</t>
+          <t>X &lt; 0.03558</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3163</v>
+        <v>3182</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.607424413909328</v>
+        <v>1.589978576101572</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.101395893310958</v>
+        <v>1.142802266397766</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.158684083212385</v>
+        <v>1.15408735146535</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.7151771625566923</v>
+        <v>0.7041577682152749</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.7119360210801631</v>
+        <v>0.7273624483698313</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.4762312356553053</v>
+        <v>0.4644956013844705</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5856171441477116</v>
+        <v>0.5935207320088978</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.1051490832405833</v>
+        <v>0.1188513383635339</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.2277168101879212</v>
+        <v>0.2020424026277468</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.197558478519305</v>
+        <v>0.2060310733493367</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.5214934967820639</v>
+        <v>0.5276333525900156</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.3872284703025812</v>
+        <v>0.3943756867153994</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.2916441165089196</v>
+        <v>0.2998158906133241</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.07056524006232934</v>
+        <v>0.1013755116325044</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.06209907365971645</v>
+        <v>0.09580879131754472</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.1705680981477755</v>
+        <v>0.2055980188305426</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.08704245898211838</v>
+        <v>0.1202865318281496</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.3799569356363648</v>
+        <v>0.382394543939192</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.3305572274091233</v>
+        <v>0.3331698749388821</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.1887531544883529</v>
+        <v>0.1897419367857864</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.1390939873990931</v>
+        <v>0.1431791185143254</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.1770600265511604</v>
+        <v>0.212341044544651</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>0.1669947453563196</v>
+        <v>0.2233878348290617</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.003684172425920451</v>
+        <v>0.07992916082217505</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.04106</t>
+          <t>X &lt; 0.04094</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3214</v>
+        <v>3232</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.354513232995501</v>
+        <v>1.357526881720425</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.7892275733667304</v>
+        <v>0.8519089684535075</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.7918661694874416</v>
+        <v>0.8129051347858081</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.5297497689704898</v>
+        <v>0.5451819436038079</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.5211987968100971</v>
+        <v>0.5637427859123818</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.4160285474209857</v>
+        <v>0.399591755230631</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.4805110902964316</v>
+        <v>0.4835967993702894</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.09617255568927874</v>
+        <v>0.07308304722097603</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.3104501139062279</v>
+        <v>0.2801395638966113</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.2685715058782137</v>
+        <v>0.2410216692652085</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.6227569487210829</v>
+        <v>0.5926907057829709</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.4862370541765983</v>
+        <v>0.4572440272460057</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.3433816095131945</v>
+        <v>0.3161366678608815</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1843759794973963</v>
+        <v>0.1786236906859386</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.1967046833367618</v>
+        <v>0.1934975334998086</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.3750235271974418</v>
+        <v>0.3720131277743803</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.1665008358543005</v>
+        <v>0.1629714675311291</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.3909858358685767</v>
+        <v>0.3572268172184749</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.3768801514047695</v>
+        <v>0.3429601887126168</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.2092077535310608</v>
+        <v>0.1741646700509847</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.1828404114975726</v>
+        <v>0.1504582161003327</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.187900207462171</v>
+        <v>0.186469572154877</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.2445777824208903</v>
+        <v>0.2629674955284571</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.168745529197615</v>
+        <v>0.2120538597785568</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.04641</t>
+          <t>X &lt; 0.0463</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3249</v>
+        <v>3268</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.163314453275497</v>
+        <v>1.151994967422674</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.7534853627820439</v>
+        <v>0.8011320896809764</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.6488187660702636</v>
+        <v>0.6575932525061745</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3818256843693035</v>
+        <v>0.3862679457047093</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3697203903344715</v>
+        <v>0.4015591812701729</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.2676372683850019</v>
+        <v>0.2713085959066959</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.3537946218835515</v>
+        <v>0.3760821584059428</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.03186802218642271</v>
+        <v>0.05804521638869886</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.30560219870938</v>
+        <v>0.3251493627680944</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3172232393637344</v>
+        <v>0.3386808892755511</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.5171418054682348</v>
+        <v>0.5371155565251371</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.4097552295379643</v>
+        <v>0.4305906935116823</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.2870449449601011</v>
+        <v>0.3092811674220499</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.06596606851351083</v>
+        <v>0.1095373133301649</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.1324763049202389</v>
+        <v>0.1777641917050587</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.2538053344504974</v>
+        <v>0.2994313885259814</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.07677925534154184</v>
+        <v>0.1220578880407075</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.2669525058277671</v>
+        <v>0.2821599286400698</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.2552840489034836</v>
+        <v>0.2703861727021675</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.09139096237150568</v>
+        <v>0.1057866126829268</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.05942852012300648</v>
+        <v>0.07607497751403969</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.09435747170488895</v>
+        <v>0.141420693554231</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.1533812762152493</v>
+        <v>0.2197454347161099</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.07754902299197397</v>
+        <v>0.1675933243737262</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.05176</t>
+          <t>X &lt; 0.05166</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3274</v>
+        <v>3294</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.9598209703821823</v>
+        <v>0.9343102631465641</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.7327600493360791</v>
+        <v>0.7651455676692436</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.6787301780507988</v>
+        <v>0.6732127566167279</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.40835742703932</v>
+        <v>0.3993731529872377</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.332991081706183</v>
+        <v>0.3520175492650495</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.3243354242921654</v>
+        <v>0.3145861810946187</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.4343818742217564</v>
+        <v>0.4425089530901474</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.1128122766925443</v>
+        <v>0.1245951094893627</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.3239398705585685</v>
+        <v>0.3301845969805868</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.2991544940910273</v>
+        <v>0.3071247923723632</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.4691812995853368</v>
+        <v>0.4758912566991569</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.3604751893285894</v>
+        <v>0.3680104624462146</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.2910675937826781</v>
+        <v>0.2993799900308716</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.03951949125442411</v>
+        <v>0.06898521385416245</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.1005000766623851</v>
+        <v>0.1312930898475173</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.1644493717664446</v>
+        <v>0.1958385683977326</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.01822181891263597</v>
+        <v>0.04930639705139583</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.2366336580827735</v>
+        <v>0.2373810463535477</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.2266919869682198</v>
+        <v>0.2273767225702059</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.09599178210613246</v>
+        <v>0.09607486621437289</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.09066751014061936</v>
+        <v>0.09245035077009334</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.1247601349556291</v>
+        <v>0.1566926569757428</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.1854291052263122</v>
+        <v>0.2363264498251638</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.1095968520030368</v>
+        <v>0.1833112314173562</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.05711</t>
+          <t>X &lt; 0.05702</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3288</v>
+        <v>3310</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.8633850510178505</v>
+        <v>0.852812815843798</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.7567619364190037</v>
+        <v>0.7732911660774917</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.5754677469912153</v>
+        <v>0.5556915777643781</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3333122481862389</v>
+        <v>0.3103160814316723</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.287007220320703</v>
+        <v>0.2918759785645335</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2792260236367028</v>
+        <v>0.2553609859998645</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2944405247297013</v>
+        <v>0.2886557743035425</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.09416421337314773</v>
+        <v>0.09102276089647177</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.2136337477897428</v>
+        <v>0.2060028824949143</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1854143529536216</v>
+        <v>0.1791849404726449</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.3255674853375581</v>
+        <v>0.318317807734303</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2160444365689642</v>
+        <v>0.209577052008612</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.2024600900911651</v>
+        <v>0.1960809909961654</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1096105970924697</v>
+        <v>-0.09467183565136139</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.08228777513510011</v>
+        <v>-0.06613167679436316</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.0143697981330746</v>
+        <v>0.03088839846400049</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.1318472578584107</v>
+        <v>-0.1154877650487336</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.05467910994167369</v>
+        <v>0.07098853255451587</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.07608784624887477</v>
+        <v>0.09218332560408271</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.08359668371752349</v>
+        <v>-0.06766439091298793</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.06102974501610703</v>
+        <v>-0.04387715236756407</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.05788901319244388</v>
+        <v>-0.01054269783875839</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.003755051676350263</v>
+        <v>0.06983309915565172</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.05393444300430161</v>
+        <v>0.01624009411196425</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.06246</t>
+          <t>X &lt; 0.06238</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.7102519531142519</v>
+        <v>0.7012465534195869</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.602689341230267</v>
+        <v>0.6210329533753622</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.4164263371685522</v>
+        <v>0.3993560663513662</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.2326555815286966</v>
+        <v>0.2124108175078661</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.2153333792743979</v>
+        <v>0.222863461574299</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2686076838374163</v>
+        <v>0.2469428477179108</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.2505793859543033</v>
+        <v>0.2470707747804965</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.04998421551088938</v>
+        <v>0.04900759617740391</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1691345131802251</v>
+        <v>0.1640255605201233</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1681636692375008</v>
+        <v>0.1641653609271216</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.2786439555898497</v>
+        <v>0.2738363901599641</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1684423003154834</v>
+        <v>0.1644280431295542</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1504857144113529</v>
+        <v>0.1466238544198717</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1612276031228461</v>
+        <v>-0.1439779710841904</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.136613356735154</v>
+        <v>-0.1182254278229493</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.06824594188559985</v>
+        <v>-0.0494300305846096</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.2144396282952528</v>
+        <v>-0.1956644144144164</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.02908396960028625</v>
+        <v>-0.0104593279512244</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.006935592960097381</v>
+        <v>0.01146594249699007</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.135015440426514</v>
+        <v>-0.1168858537563651</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.2055147715232835</v>
+        <v>-0.1856227385067513</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.1724440918009336</v>
+        <v>-0.1226799249645438</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.1222191019310657</v>
+        <v>-0.07178360278343376</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.1800127442650776</v>
+        <v>-0.1258438707107103</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.06781</t>
+          <t>X &lt; 0.06774</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3320</v>
+        <v>3343</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.5644806327518097</v>
+        <v>0.5571950187699741</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.4555138127691123</v>
+        <v>0.4759538061706721</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2916580275070899</v>
+        <v>0.2778187076589944</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1645953504814557</v>
+        <v>0.1478967486287601</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1753110788124346</v>
+        <v>0.1863729709961532</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.229374896364142</v>
+        <v>0.2112320637468699</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.176850672905438</v>
+        <v>0.1768540653422335</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.03573794498099403</v>
+        <v>0.03767526839869362</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.1844120853061213</v>
+        <v>0.1825463853855496</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1188076922875538</v>
+        <v>0.1183712304491991</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.200243030002234</v>
+        <v>0.1992000324999665</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.08900584308899795</v>
+        <v>0.08877287518446053</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.0643875316364344</v>
+        <v>0.06440416240121039</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2167514048702159</v>
+        <v>-0.1961454305978094</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1962557150103379</v>
+        <v>-0.17463223875734</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.1247450466200419</v>
+        <v>-0.1029142018231894</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.2408248070050689</v>
+        <v>-0.2190609452736325</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.08728824404943936</v>
+        <v>-0.06562211153166686</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.06399200099986757</v>
+        <v>-0.04256315639098318</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.1601099180388843</v>
+        <v>-0.1390043653341024</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.2334578892846153</v>
+        <v>-0.2107287787288996</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.2010513504233202</v>
+        <v>-0.1486192126456274</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.1494844794352232</v>
+        <v>-0.0965779072186308</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.2073950005629897</v>
+        <v>-0.1512921891547805</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.07316</t>
+          <t>X &lt; 0.0731</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3331</v>
+        <v>3354</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.5357638650883203</v>
+        <v>0.5290345096744176</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.4558890694178572</v>
+        <v>0.4768692797874294</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.2878495765006619</v>
+        <v>0.2752908528124749</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.2185806847191074</v>
+        <v>0.2031371775722732</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.2281740764684201</v>
+        <v>0.2406056508859535</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.2229354706713451</v>
+        <v>0.2065996939111656</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1381693383196847</v>
+        <v>0.1400732598726151</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.003405663131260894</v>
+        <v>0.0003425522713342843</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.08511355936108345</v>
+        <v>0.08578247394906668</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.01715278995521174</v>
+        <v>0.01918825616990461</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1291047930741982</v>
+        <v>0.1303129552696305</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.04721716552098343</v>
+        <v>0.04903119609852524</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.0189694706541772</v>
+        <v>0.02108581195407311</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2021094057924131</v>
+        <v>-0.1799833552135652</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.2137844904423574</v>
+        <v>-0.1905023314479166</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1405565084810334</v>
+        <v>-0.1171871571823857</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.2566997867223719</v>
+        <v>-0.2332980015868316</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1339867253892422</v>
+        <v>-0.1105626765901775</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.1100694247751406</v>
+        <v>-0.08689029619583977</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.2052678444908338</v>
+        <v>-0.1823258538422863</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.2501834036460906</v>
+        <v>-0.2258990138728763</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.2181391519186917</v>
+        <v>-0.1642439064319134</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.1958535238913086</v>
+        <v>-0.1413853430959549</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2238161339105602</v>
+        <v>-0.1666501555245858</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.07851</t>
+          <t>X &lt; 0.07846</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3343</v>
+        <v>3367</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.3858988003867552</v>
+        <v>0.3806771066976609</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.3347209158044251</v>
+        <v>0.3572321487851227</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.2212068756427712</v>
+        <v>0.2106094063128339</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1494291946403834</v>
+        <v>0.1364398136670104</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1576661026866475</v>
+        <v>0.172686773886106</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1233882571041178</v>
+        <v>0.1098519529354363</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1252490970232856</v>
+        <v>0.129150586787695</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.01685856117199336</v>
+        <v>-0.01121813122996684</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.04169494678028229</v>
+        <v>0.0448133919145306</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.02900869793054994</v>
+        <v>-0.02459771840787539</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.05376012217878667</v>
+        <v>0.05754788250455078</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.0008934938036659901</v>
+        <v>0.005087766538046878</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.001796720594327894</v>
+        <v>0.002549649722617175</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2350488553179773</v>
+        <v>-0.2283186527093477</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2192151565564231</v>
+        <v>-0.211817366968269</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.1441225143105171</v>
+        <v>-0.1366288475342472</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.2901812708535445</v>
+        <v>-0.2823367417506404</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.1981532279336591</v>
+        <v>-0.190248345699203</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.1735670138006924</v>
+        <v>-0.1658640488343366</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.2677731917574349</v>
+        <v>-0.2601274580730291</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.3144921199064186</v>
+        <v>-0.3057445733088997</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.2828541435972411</v>
+        <v>-0.2446411057437388</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.2596828833863043</v>
+        <v>-0.2209542497159873</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.2878364192440017</v>
+        <v>-0.2467711658781582</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.08386</t>
+          <t>X &lt; 0.08382</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3355</v>
+        <v>3378</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.2531416339769734</v>
+        <v>0.235673771742384</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.2305372256589777</v>
+        <v>0.2408782008914159</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.05302370585388871</v>
+        <v>0.06121481737721268</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.06783099840482976</v>
+        <v>0.07361086532680616</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1637613761328751</v>
+        <v>0.1677051363931596</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1302726834725263</v>
+        <v>0.1055807015022623</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.01075579080401212</v>
+        <v>0.03387419298091743</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.07254075458941145</v>
+        <v>-0.04812839226511301</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.04373813034807483</v>
+        <v>-0.02134710166087217</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1169683341129542</v>
+        <v>-0.09313415677321757</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.03354407153673122</v>
+        <v>-0.01039213972623543</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.08724167629872426</v>
+        <v>-0.06359953600123447</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.09395262670371807</v>
+        <v>-0.06976839383452216</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.29747105468347</v>
+        <v>-0.3007144239502537</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.2840601104271201</v>
+        <v>-0.2865035450928843</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.2071337820668759</v>
+        <v>-0.2097578536815732</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3234237437952032</v>
+        <v>-0.3258093303791227</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2618615346848543</v>
+        <v>-0.2344650744287478</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2366110486189186</v>
+        <v>-0.2094757995844532</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.3000611742326242</v>
+        <v>-0.3027475658170857</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.3783412146092004</v>
+        <v>-0.3796520875466882</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.3471064722432189</v>
+        <v>-0.3190139553066658</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.3230557754713246</v>
+        <v>-0.2946330918589197</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.3513987353232082</v>
+        <v>-0.3209157338060251</v>
       </c>
     </row>
   </sheetData>
